--- a/data/merged_input_data.xlsx
+++ b/data/merged_input_data.xlsx
@@ -463,5987 +463,5991 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>38361</v>
+        <v>38355</v>
       </c>
       <c r="B2" t="n">
-        <v>43.00666666666667</v>
+        <v>45.91666666666666</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>275.28</v>
+        <v>277.8</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>38382</v>
+        <v>38376</v>
       </c>
       <c r="B3" t="n">
-        <v>45.59666666666667</v>
+        <v>45.28666666666667</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>281.5</v>
+        <v>295.0066666666667</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>38403</v>
+        <v>38397</v>
       </c>
       <c r="B4" t="n">
-        <v>46.6</v>
+        <v>51.99333333333333</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>287.68</v>
+        <v>283.1966666666667</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>38424</v>
+        <v>38418</v>
       </c>
       <c r="B5" t="n">
-        <v>53.47333333333333</v>
+        <v>53.39</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>274.57</v>
+        <v>282.84</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>38445</v>
+        <v>38439</v>
       </c>
       <c r="B6" t="n">
-        <v>56.32333333333333</v>
+        <v>51.05666666666666</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>287.08</v>
+        <v>282.69</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>38466</v>
+        <v>38460</v>
       </c>
       <c r="B7" t="n">
-        <v>54.59</v>
+        <v>51.11666666666667</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>285.18</v>
+        <v>289.1166666666667</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>38487</v>
+        <v>38481</v>
       </c>
       <c r="B8" t="n">
-        <v>48.25333333333333</v>
+        <v>50.715</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>290.2666666666667</v>
+        <v>301.48</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>38508</v>
+        <v>38502</v>
       </c>
       <c r="B9" t="n">
-        <v>53.83666666666667</v>
+        <v>58.13333333333333</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>305.44</v>
+        <v>304.1266666666667</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>38529</v>
+        <v>38523</v>
       </c>
       <c r="B10" t="n">
-        <v>58.98666666666666</v>
+        <v>57.69333333333334</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>307.8566666666667</v>
+        <v>306.28</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>38550</v>
+        <v>38544</v>
       </c>
       <c r="B11" t="n">
-        <v>57.19666666666667</v>
+        <v>60.08333333333333</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>303.3333333333334</v>
+        <v>309.6266666666667</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>38571</v>
+        <v>38565</v>
       </c>
       <c r="B12" t="n">
-        <v>62.15666666666667</v>
+        <v>64.45333333333333</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>314.3933333333333</v>
+        <v>315.0066666666667</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>38592</v>
+        <v>38586</v>
       </c>
       <c r="B13" t="n">
-        <v>66.22</v>
+        <v>62.14666666666667</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>313.5</v>
+        <v>327.0966666666667</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>38613</v>
+        <v>38607</v>
       </c>
       <c r="B14" t="n">
-        <v>64.34333333333333</v>
+        <v>63.02666666666666</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>325.8933333333333</v>
+        <v>329.6366666666667</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>38634</v>
+        <v>38628</v>
       </c>
       <c r="B15" t="n">
-        <v>58.92333333333333</v>
+        <v>58.32</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>319.9966666666667</v>
+        <v>310.5933333333333</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>38655</v>
+        <v>38649</v>
       </c>
       <c r="B16" t="n">
-        <v>58.54</v>
+        <v>54.81666666666666</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>314.12</v>
+        <v>325.4</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>38676</v>
+        <v>38670</v>
       </c>
       <c r="B17" t="n">
-        <v>55.18666666666667</v>
+        <v>57.50333333333333</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>327.45</v>
+        <v>331.4966666666667</v>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>38697</v>
+        <v>38691</v>
       </c>
       <c r="B18" t="n">
-        <v>58.73</v>
+        <v>56.48999999999999</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>334.4133333333334</v>
+        <v>344.97</v>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>38718</v>
+        <v>38712</v>
       </c>
       <c r="B19" t="n">
-        <v>60.165</v>
+        <v>62.70666666666666</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>346.5833333333333</v>
+        <v>357.39</v>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>38739</v>
+        <v>38733</v>
       </c>
       <c r="B20" t="n">
-        <v>66.25</v>
+        <v>63.35</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>356.5533333333333</v>
+        <v>369.9666666666666</v>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>38760</v>
+        <v>38754</v>
       </c>
       <c r="B21" t="n">
-        <v>59.46666666666667</v>
+        <v>61.52666666666667</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>370.8733333333333</v>
+        <v>382.6633333333334</v>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>38781</v>
+        <v>38775</v>
       </c>
       <c r="B22" t="n">
-        <v>62.95333333333334</v>
+        <v>61.98</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
-        <v>379.89</v>
+        <v>386.04</v>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>38802</v>
+        <v>38796</v>
       </c>
       <c r="B23" t="n">
-        <v>63.57666666666667</v>
+        <v>68.26333333333334</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="n">
-        <v>380.6066666666667</v>
+        <v>376.15</v>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>38823</v>
+        <v>38817</v>
       </c>
       <c r="B24" t="n">
-        <v>71.00999999999999</v>
+        <v>73.10000000000001</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="n">
-        <v>389.34</v>
+        <v>388.1133333333333</v>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>38844</v>
+        <v>38838</v>
       </c>
       <c r="B25" t="n">
-        <v>69.84666666666666</v>
+        <v>69.12666666666667</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="n">
-        <v>374.4466666666667</v>
+        <v>374.82</v>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>38865</v>
+        <v>38859</v>
       </c>
       <c r="B26" t="n">
-        <v>70.81999999999999</v>
+        <v>69.44666666666667</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
-        <v>370.06</v>
+        <v>359.4666666666667</v>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>38886</v>
+        <v>38880</v>
       </c>
       <c r="B27" t="n">
-        <v>68.34</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">
-        <v>364.4633333333333</v>
+        <v>374.7166666666666</v>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>38907</v>
+        <v>38901</v>
       </c>
       <c r="B28" t="n">
-        <v>73.09666666666666</v>
+        <v>74.32333333333334</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="n">
-        <v>364.2033333333333</v>
+        <v>391.1733333333333</v>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>38928</v>
+        <v>38922</v>
       </c>
       <c r="B29" t="n">
-        <v>74.56333333333333</v>
+        <v>74.74333333333333</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
-        <v>393.2566666666667</v>
+        <v>399.6166666666667</v>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>38949</v>
+        <v>38943</v>
       </c>
       <c r="B30" t="n">
-        <v>73.02</v>
+        <v>68.19</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="n">
-        <v>402.2366666666667</v>
+        <v>402.5466666666667</v>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>38970</v>
+        <v>38964</v>
       </c>
       <c r="B31" t="n">
-        <v>64.81</v>
+        <v>60.66999999999999</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="n">
-        <v>413.97</v>
+        <v>423.4766666666667</v>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>38991</v>
+        <v>38985</v>
       </c>
       <c r="B32" t="n">
-        <v>61.12666666666667</v>
+        <v>59.81333333333333</v>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="n">
-        <v>425.9966666666667</v>
+        <v>432.3</v>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>39012</v>
+        <v>39006</v>
       </c>
       <c r="B33" t="n">
-        <v>59.36666666666667</v>
+        <v>59.55</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="n">
-        <v>432.8266666666667</v>
+        <v>444.4066666666666</v>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>39033</v>
+        <v>39027</v>
       </c>
       <c r="B34" t="n">
-        <v>59.27</v>
+        <v>60.30333333333333</v>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="n">
-        <v>450.5766666666667</v>
+        <v>448.0966666666667</v>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>39054</v>
+        <v>39048</v>
       </c>
       <c r="B35" t="n">
-        <v>63.84</v>
+        <v>62.58333333333334</v>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="n">
-        <v>459.56</v>
+        <v>461.7766666666666</v>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>39075</v>
+        <v>39069</v>
       </c>
       <c r="B36" t="n">
-        <v>61.76000000000001</v>
+        <v>55.61333333333334</v>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="n">
-        <v>463.51</v>
+        <v>458.7266666666667</v>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>39096</v>
+        <v>39090</v>
       </c>
       <c r="B37" t="n">
-        <v>53.06333333333333</v>
+        <v>54.21666666666667</v>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="n">
-        <v>463.7033333333333</v>
+        <v>480.7566666666667</v>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>39117</v>
+        <v>39111</v>
       </c>
       <c r="B38" t="n">
-        <v>58.20333333333333</v>
+        <v>58.41</v>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="n">
-        <v>479.1033333333334</v>
+        <v>452.6366666666667</v>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>39138</v>
+        <v>39132</v>
       </c>
       <c r="B39" t="n">
-        <v>61.18</v>
+        <v>60.87</v>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="n">
-        <v>458.99</v>
+        <v>469.6633333333334</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>39159</v>
+        <v>39153</v>
       </c>
       <c r="B40" t="n">
-        <v>60.44666666666667</v>
+        <v>68.52666666666666</v>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="n">
-        <v>473.6733333333333</v>
+        <v>491.8166666666667</v>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>39180</v>
+        <v>39174</v>
       </c>
       <c r="B41" t="n">
-        <v>67.0025</v>
+        <v>67.59666666666666</v>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="n">
-        <v>487.6233333333333</v>
+        <v>498.1233333333333</v>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>39201</v>
+        <v>39195</v>
       </c>
       <c r="B42" t="n">
-        <v>67.90333333333334</v>
+        <v>66.83</v>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="n">
-        <v>497.08</v>
+        <v>510.0266666666666</v>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>39222</v>
+        <v>39216</v>
       </c>
       <c r="B43" t="n">
-        <v>70.13333333333333</v>
+        <v>69.95666666666666</v>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="n">
-        <v>521.6233333333333</v>
+        <v>511.87</v>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>39243</v>
+        <v>39237</v>
       </c>
       <c r="B44" t="n">
-        <v>69.23999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="n">
-        <v>504.85</v>
+        <v>504.7533333333333</v>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>39264</v>
+        <v>39258</v>
       </c>
       <c r="B45" t="n">
-        <v>72.22333333333333</v>
+        <v>77.41</v>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="n">
-        <v>507.15</v>
+        <v>480.12</v>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>39285</v>
+        <v>39279</v>
       </c>
       <c r="B46" t="n">
-        <v>77.12</v>
+        <v>72.36333333333333</v>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="n">
-        <v>479.3133333333333</v>
+        <v>477.2433333333333</v>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>39306</v>
+        <v>39300</v>
       </c>
       <c r="B47" t="n">
-        <v>70.28333333333333</v>
+        <v>70.84</v>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="n">
-        <v>484.3466666666666</v>
+        <v>480.4933333333333</v>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>39327</v>
+        <v>39321</v>
       </c>
       <c r="B48" t="n">
-        <v>73.17</v>
+        <v>76.72666666666667</v>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="n">
-        <v>492.5</v>
+        <v>517.4300000000001</v>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>39348</v>
+        <v>39342</v>
       </c>
       <c r="B49" t="n">
-        <v>79.03999999999999</v>
+        <v>77.35333333333334</v>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="n">
-        <v>518.4233333333333</v>
+        <v>529.4599999999999</v>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>39369</v>
+        <v>39363</v>
       </c>
       <c r="B50" t="n">
-        <v>82.01666666666667</v>
+        <v>89.77666666666666</v>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="n">
-        <v>542.7066666666667</v>
+        <v>542.4666666666666</v>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>39390</v>
+        <v>39384</v>
       </c>
       <c r="B51" t="n">
-        <v>91.02</v>
+        <v>92.06</v>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="n">
-        <v>537.11</v>
+        <v>547.6</v>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>39411</v>
+        <v>39405</v>
       </c>
       <c r="B52" t="n">
-        <v>95.46666666666667</v>
+        <v>88.24000000000001</v>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="n">
-        <v>554.3233333333333</v>
+        <v>546.7233333333334</v>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>39432</v>
+        <v>39426</v>
       </c>
       <c r="B53" t="n">
-        <v>91.75</v>
+        <v>93.86</v>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="n">
-        <v>548.0833333333334</v>
+        <v>525.02</v>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>39453</v>
+        <v>39447</v>
       </c>
       <c r="B54" t="n">
-        <v>95.19</v>
+        <v>88.08333333333334</v>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="n">
-        <v>470.3166666666667</v>
+        <v>489.16</v>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>39474</v>
+        <v>39468</v>
       </c>
       <c r="B55" t="n">
-        <v>91.22</v>
+        <v>93</v>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="n">
-        <v>508.0433333333334</v>
+        <v>485.5833333333333</v>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>39495</v>
+        <v>39489</v>
       </c>
       <c r="B56" t="n">
-        <v>94.81666666666666</v>
+        <v>100.3533333333333</v>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="n">
-        <v>472.33</v>
+        <v>454.9633333333333</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>39516</v>
+        <v>39510</v>
       </c>
       <c r="B57" t="n">
-        <v>103.5666666666667</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="n">
-        <v>455.2366666666667</v>
+        <v>462.9366666666667</v>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>39537</v>
+        <v>39531</v>
       </c>
       <c r="B58" t="n">
-        <v>101.4566666666667</v>
+        <v>109.4766666666667</v>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="n">
-        <v>470.6833333333333</v>
+        <v>478.07</v>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>39558</v>
+        <v>39552</v>
       </c>
       <c r="B59" t="n">
-        <v>114.26</v>
+        <v>116.8466666666667</v>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="n">
-        <v>476.0133333333333</v>
+        <v>484.0466666666666</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>39579</v>
+        <v>39573</v>
       </c>
       <c r="B60" t="n">
-        <v>123.74</v>
+        <v>132.1033333333333</v>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="n">
-        <v>494.02</v>
+        <v>471.4166666666667</v>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>39600</v>
+        <v>39594</v>
       </c>
       <c r="B61" t="n">
-        <v>127.94</v>
+        <v>134.5566666666667</v>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="n">
-        <v>462.8366666666666</v>
+        <v>457.1966666666667</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>39621</v>
+        <v>39615</v>
       </c>
       <c r="B62" t="n">
-        <v>135.56</v>
+        <v>142.72</v>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="n">
-        <v>434.6</v>
+        <v>439.8866666666667</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>39642</v>
+        <v>39636</v>
       </c>
       <c r="B63" t="n">
-        <v>144.11</v>
+        <v>125.4</v>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="n">
-        <v>439.7833333333334</v>
+        <v>438.09</v>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>39663</v>
+        <v>39657</v>
       </c>
       <c r="B64" t="n">
-        <v>121.8466666666667</v>
+        <v>112.1433333333333</v>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="n">
-        <v>441.2766666666667</v>
+        <v>420.3633333333333</v>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>39684</v>
+        <v>39678</v>
       </c>
       <c r="B65" t="n">
-        <v>113.9933333333333</v>
+        <v>103.6566666666667</v>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="n">
-        <v>411.03</v>
+        <v>405.2533333333333</v>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>39705</v>
+        <v>39699</v>
       </c>
       <c r="B66" t="n">
-        <v>94.11333333333333</v>
+        <v>97.16666666666667</v>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="n">
-        <v>390.4366666666667</v>
+        <v>361.0233333333333</v>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>39726</v>
+        <v>39720</v>
       </c>
       <c r="B67" t="n">
-        <v>85.87</v>
+        <v>71.22</v>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="n">
-        <v>322.3966666666666</v>
+        <v>372.3533333333333</v>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>39747</v>
+        <v>39741</v>
       </c>
       <c r="B68" t="n">
-        <v>61.62333333333333</v>
+        <v>58.50333333333333</v>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="n">
-        <v>350.2766666666666</v>
+        <v>322.68</v>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>39768</v>
+        <v>39762</v>
       </c>
       <c r="B69" t="n">
-        <v>52.95333333333333</v>
+        <v>49.81</v>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="n">
-        <v>310.5566666666667</v>
+        <v>325.3833333333333</v>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>39789</v>
+        <v>39783</v>
       </c>
       <c r="B70" t="n">
-        <v>42.19333333333334</v>
+        <v>42.3</v>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="n">
-        <v>338.95</v>
+        <v>321.8233333333333</v>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>39810</v>
+        <v>39804</v>
       </c>
       <c r="B71" t="n">
-        <v>39.82333333333333</v>
+        <v>43.41333333333333</v>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="n">
-        <v>310.93</v>
+        <v>328.8166666666667</v>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>39831</v>
+        <v>39825</v>
       </c>
       <c r="B72" t="n">
-        <v>45.19</v>
+        <v>44.50666666666667</v>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="n">
-        <v>310.8933333333333</v>
+        <v>285.7933333333334</v>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>39852</v>
+        <v>39846</v>
       </c>
       <c r="B73" t="n">
-        <v>46.08333333333334</v>
+        <v>41.29</v>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="n">
-        <v>268.0433333333334</v>
+        <v>268.5166666666667</v>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>39873</v>
+        <v>39867</v>
       </c>
       <c r="B74" t="n">
-        <v>43.59</v>
+        <v>44.29666666666667</v>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="n">
-        <v>284.8633333333333</v>
+        <v>283.48</v>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>39894</v>
+        <v>39888</v>
       </c>
       <c r="B75" t="n">
-        <v>52.72</v>
+        <v>52.65</v>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="n">
-        <v>285.37</v>
+        <v>303.8233333333333</v>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>39915</v>
+        <v>39909</v>
       </c>
       <c r="B76" t="n">
-        <v>52.62</v>
+        <v>50.77</v>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="n">
-        <v>302.7</v>
+        <v>308.8633333333333</v>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>39936</v>
+        <v>39930</v>
       </c>
       <c r="B77" t="n">
-        <v>54.00333333333333</v>
+        <v>57.64</v>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="n">
-        <v>314.5566666666667</v>
+        <v>303.5566666666667</v>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>39957</v>
+        <v>39951</v>
       </c>
       <c r="B78" t="n">
-        <v>60.4</v>
+        <v>68.03333333333333</v>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="n">
-        <v>300.58</v>
+        <v>291.8866666666667</v>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>39978</v>
+        <v>39972</v>
       </c>
       <c r="B79" t="n">
-        <v>69.93333333333334</v>
+        <v>70.3</v>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="n">
-        <v>284.5266666666666</v>
-      </c>
-      <c r="E79" t="inlineStr"/>
+        <v>304.03</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.046994</v>
+      </c>
       <c r="F79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>39999</v>
+        <v>39993</v>
       </c>
       <c r="B80" t="n">
-        <v>64.56999999999999</v>
+        <v>66.08666666666666</v>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="n">
-        <v>310.4633333333334</v>
+        <v>309.3133333333333</v>
       </c>
       <c r="E80" t="n">
-        <v>0.046236</v>
+        <v>0.04657233333333333</v>
       </c>
       <c r="F80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>40020</v>
+        <v>40014</v>
       </c>
       <c r="B81" t="n">
-        <v>70.64666666666666</v>
+        <v>73.53</v>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="n">
-        <v>331.1666666666667</v>
+        <v>329.8466666666667</v>
       </c>
       <c r="E81" t="n">
-        <v>0.04647633333333333</v>
+        <v>0.045909</v>
       </c>
       <c r="F81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>40041</v>
+        <v>40035</v>
       </c>
       <c r="B82" t="n">
-        <v>71.16333333333334</v>
+        <v>70.69666666666667</v>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="n">
-        <v>334.8866666666667</v>
+        <v>334.6666666666667</v>
       </c>
       <c r="E82" t="n">
-        <v>0.043763</v>
+        <v>0.04338066666666666</v>
       </c>
       <c r="F82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>40062</v>
+        <v>40056</v>
       </c>
       <c r="B83" t="n">
-        <v>66.62666666666667</v>
+        <v>69.56666666666666</v>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="n">
-        <v>325.96</v>
+        <v>319.7166666666667</v>
       </c>
       <c r="E83" t="n">
-        <v>0.04277266666666667</v>
+        <v>0.04394533333333333</v>
       </c>
       <c r="F83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>40083</v>
+        <v>40077</v>
       </c>
       <c r="B84" t="n">
-        <v>65.39666666666668</v>
+        <v>70.90666666666667</v>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="n">
-        <v>318.36</v>
+        <v>318.97</v>
       </c>
       <c r="E84" t="n">
-        <v>0.042876</v>
+        <v>0.04274466666666666</v>
       </c>
       <c r="F84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>40104</v>
+        <v>40098</v>
       </c>
       <c r="B85" t="n">
-        <v>77.50999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="n">
-        <v>325.8266666666667</v>
+        <v>319.3666666666667</v>
       </c>
       <c r="E85" t="n">
-        <v>0.04344199999999999</v>
+        <v>0.04244033333333333</v>
       </c>
       <c r="F85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>40125</v>
+        <v>40119</v>
       </c>
       <c r="B86" t="n">
-        <v>77.13666666666667</v>
+        <v>77.37333333333333</v>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="n">
-        <v>329.3066666666667</v>
+        <v>333.7166666666666</v>
       </c>
       <c r="E86" t="n">
-        <v>0.04281233333333333</v>
+        <v>0.041447</v>
       </c>
       <c r="F86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>40146</v>
+        <v>40140</v>
       </c>
       <c r="B87" t="n">
-        <v>78.04000000000001</v>
+        <v>71.88666666666667</v>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="n">
-        <v>342.5733333333333</v>
+        <v>342.0766666666667</v>
       </c>
       <c r="E87" t="n">
-        <v>0.040405</v>
+        <v>0.04086466666666667</v>
       </c>
       <c r="F87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>40167</v>
+        <v>40161</v>
       </c>
       <c r="B88" t="n">
-        <v>73.24333333333333</v>
+        <v>79.57250000000001</v>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="n">
-        <v>340.0733333333333</v>
+        <v>328.4966666666667</v>
       </c>
       <c r="E88" t="n">
-        <v>0.04042399999999999</v>
+        <v>0.04243633333333334</v>
       </c>
       <c r="F88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>40188</v>
+        <v>40182</v>
       </c>
       <c r="B89" t="n">
-        <v>81.10333333333334</v>
+        <v>73.40333333333334</v>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="n">
-        <v>317.2666666666667</v>
+        <v>322.5466666666667</v>
       </c>
       <c r="E89" t="n">
-        <v>0.041552</v>
+        <v>0.040587</v>
       </c>
       <c r="F89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>40209</v>
+        <v>40203</v>
       </c>
       <c r="B90" t="n">
-        <v>72.56</v>
+        <v>72.64</v>
       </c>
       <c r="C90" t="n">
-        <v>14.65907142857143</v>
+        <v>13.34357142857143</v>
       </c>
       <c r="D90" t="n">
-        <v>324.7866666666666</v>
+        <v>331.0133333333333</v>
       </c>
       <c r="E90" t="n">
-        <v>0.040619</v>
+        <v>0.04084566666666667</v>
       </c>
       <c r="F90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>40230</v>
+        <v>40224</v>
       </c>
       <c r="B91" t="n">
-        <v>78.47</v>
+        <v>80.27666666666667</v>
       </c>
       <c r="C91" t="n">
-        <v>12.68582142857143</v>
+        <v>12.11590909090909</v>
       </c>
       <c r="D91" t="n">
-        <v>327.9966666666667</v>
+        <v>340.7033333333333</v>
       </c>
       <c r="E91" t="n">
-        <v>0.04129033333333333</v>
+        <v>0.03988966666666666</v>
       </c>
       <c r="F91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>40251</v>
+        <v>40245</v>
       </c>
       <c r="B92" t="n">
-        <v>78.39</v>
+        <v>80.54333333333334</v>
       </c>
       <c r="C92" t="n">
-        <v>12.03806060606061</v>
+        <v>11.88236363636364</v>
       </c>
       <c r="D92" t="n">
-        <v>341.3933333333333</v>
+        <v>325.7066666666667</v>
       </c>
       <c r="E92" t="n">
-        <v>0.03979666666666666</v>
+        <v>0.03966066666666666</v>
       </c>
       <c r="F92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>40272</v>
+        <v>40266</v>
       </c>
       <c r="B93" t="n">
-        <v>85.41249999999999</v>
+        <v>84.81666666666666</v>
       </c>
       <c r="C93" t="n">
-        <v>12.1758</v>
+        <v>13.3196</v>
       </c>
       <c r="D93" t="n">
-        <v>303.8366666666666</v>
+        <v>297.1733333333333</v>
       </c>
       <c r="E93" t="n">
-        <v>0.03925933333333333</v>
+        <v>0.03897533333333333</v>
       </c>
       <c r="F93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>40293</v>
+        <v>40287</v>
       </c>
       <c r="B94" t="n">
-        <v>86.97</v>
+        <v>79.50333333333333</v>
       </c>
       <c r="C94" t="n">
-        <v>13.8915</v>
+        <v>14.89283870967742</v>
       </c>
       <c r="D94" t="n">
-        <v>302.5066666666667</v>
+        <v>301.7966666666667</v>
       </c>
       <c r="E94" t="n">
-        <v>0.03912166666666667</v>
+        <v>0.038558</v>
       </c>
       <c r="F94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>40314</v>
+        <v>40308</v>
       </c>
       <c r="B95" t="n">
-        <v>75.79333333333334</v>
+        <v>74.44</v>
       </c>
       <c r="C95" t="n">
-        <v>15.35393548387097</v>
+        <v>16.27612903225806</v>
       </c>
       <c r="D95" t="n">
-        <v>310.48</v>
+        <v>285.96</v>
       </c>
       <c r="E95" t="n">
-        <v>0.038129</v>
+        <v>0.03794</v>
       </c>
       <c r="F95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>40335</v>
+        <v>40329</v>
       </c>
       <c r="B96" t="n">
-        <v>72.11</v>
+        <v>78.61999999999999</v>
       </c>
       <c r="C96" t="n">
-        <v>17.12</v>
+        <v>18.93533333333333</v>
       </c>
       <c r="D96" t="n">
-        <v>299.1566666666666</v>
+        <v>300.77</v>
       </c>
       <c r="E96" t="n">
-        <v>0.03766433333333333</v>
+        <v>0.03933433333333333</v>
       </c>
       <c r="F96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>40356</v>
+        <v>40350</v>
       </c>
       <c r="B97" t="n">
-        <v>77.76666666666667</v>
+        <v>74.72</v>
       </c>
       <c r="C97" t="n">
-        <v>19.843</v>
+        <v>19.59583333333333</v>
       </c>
       <c r="D97" t="n">
-        <v>304.2866666666667</v>
+        <v>309.0366666666667</v>
       </c>
       <c r="E97" t="n">
-        <v>0.03816866666666667</v>
+        <v>0.03844366666666667</v>
       </c>
       <c r="F97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>40377</v>
+        <v>40371</v>
       </c>
       <c r="B98" t="n">
-        <v>75.53666666666668</v>
+        <v>79.94</v>
       </c>
       <c r="C98" t="n">
-        <v>19.191</v>
+        <v>18.491375</v>
       </c>
       <c r="D98" t="n">
-        <v>304.17</v>
+        <v>309.1666666666667</v>
       </c>
       <c r="E98" t="n">
-        <v>0.03875566666666667</v>
+        <v>0.03757166666666667</v>
       </c>
       <c r="F98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>40398</v>
+        <v>40392</v>
       </c>
       <c r="B99" t="n">
-        <v>80.71333333333332</v>
+        <v>73.83333333333334</v>
       </c>
       <c r="C99" t="n">
-        <v>18.4716875</v>
+        <v>18.4323125</v>
       </c>
       <c r="D99" t="n">
-        <v>317.1333333333333</v>
+        <v>304.2433333333333</v>
       </c>
       <c r="E99" t="n">
-        <v>0.03578666666666667</v>
+        <v>0.03344466666666667</v>
       </c>
       <c r="F99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>40419</v>
+        <v>40413</v>
       </c>
       <c r="B100" t="n">
-        <v>76.61666666666666</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="C100" t="n">
-        <v>18.412625</v>
+        <v>18.7242</v>
       </c>
       <c r="D100" t="n">
-        <v>300.29</v>
+        <v>307.7766666666666</v>
       </c>
       <c r="E100" t="n">
-        <v>0.03268233333333333</v>
+        <v>0.03498266666666667</v>
       </c>
       <c r="F100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>40440</v>
+        <v>40434</v>
       </c>
       <c r="B101" t="n">
-        <v>78.94999999999999</v>
+        <v>83.43666666666667</v>
       </c>
       <c r="C101" t="n">
-        <v>18.90923333333333</v>
+        <v>19.15934482758621</v>
       </c>
       <c r="D101" t="n">
-        <v>312.1633333333334</v>
+        <v>317.96</v>
       </c>
       <c r="E101" t="n">
-        <v>0.035645</v>
+        <v>0.03477466666666666</v>
       </c>
       <c r="F101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>40461</v>
+        <v>40455</v>
       </c>
       <c r="B102" t="n">
-        <v>83.82333333333334</v>
+        <v>83.34666666666666</v>
       </c>
       <c r="C102" t="n">
-        <v>19.06448275862069</v>
+        <v>18.87475862068965</v>
       </c>
       <c r="D102" t="n">
-        <v>316.1733333333333</v>
+        <v>308.21</v>
       </c>
       <c r="E102" t="n">
-        <v>0.03455733333333334</v>
+        <v>0.03659766666666667</v>
       </c>
       <c r="F102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>40482</v>
+        <v>40476</v>
       </c>
       <c r="B103" t="n">
-        <v>84.13000000000001</v>
+        <v>86.58</v>
       </c>
       <c r="C103" t="n">
-        <v>18.9915</v>
+        <v>20.283</v>
       </c>
       <c r="D103" t="n">
-        <v>304.65</v>
+        <v>311.2266666666667</v>
       </c>
       <c r="E103" t="n">
-        <v>0.03686966666666667</v>
+        <v>0.03760133333333333</v>
       </c>
       <c r="F103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>40503</v>
+        <v>40497</v>
       </c>
       <c r="B104" t="n">
-        <v>84.08666666666666</v>
+        <v>91.44</v>
       </c>
       <c r="C104" t="n">
-        <v>20.92875</v>
+        <v>22.14674193548387</v>
       </c>
       <c r="D104" t="n">
-        <v>319.5733333333333</v>
+        <v>315.9366666666667</v>
       </c>
       <c r="E104" t="n">
-        <v>0.038945</v>
+        <v>0.04082233333333333</v>
       </c>
       <c r="F104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>40524</v>
+        <v>40518</v>
       </c>
       <c r="B105" t="n">
-        <v>90.95333333333333</v>
+        <v>93.82333333333332</v>
       </c>
       <c r="C105" t="n">
-        <v>22.68958064516129</v>
+        <v>23.77525806451613</v>
       </c>
       <c r="D105" t="n">
-        <v>319.83</v>
+        <v>324.58</v>
       </c>
       <c r="E105" t="n">
-        <v>0.042566</v>
+        <v>0.04230933333333333</v>
       </c>
       <c r="F105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>40545</v>
+        <v>40539</v>
       </c>
       <c r="B106" t="n">
-        <v>94.81</v>
+        <v>97.84666666666668</v>
       </c>
       <c r="C106" t="n">
-        <v>23.94848387096774</v>
+        <v>22.44687096774194</v>
       </c>
       <c r="D106" t="n">
-        <v>328.1933333333333</v>
+        <v>336.27</v>
       </c>
       <c r="E106" t="n">
-        <v>0.041526</v>
+        <v>0.04325433333333333</v>
       </c>
       <c r="F106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>40566</v>
+        <v>40560</v>
       </c>
       <c r="B107" t="n">
-        <v>96.94</v>
+        <v>99.44333333333333</v>
       </c>
       <c r="C107" t="n">
-        <v>21.69606451612903</v>
+        <v>21.12621428571429</v>
       </c>
       <c r="D107" t="n">
-        <v>326.8633333333333</v>
+        <v>317.7133333333334</v>
       </c>
       <c r="E107" t="n">
-        <v>0.04406833333333333</v>
+        <v>0.04458400000000001</v>
       </c>
       <c r="F107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>40587</v>
+        <v>40581</v>
       </c>
       <c r="B108" t="n">
-        <v>102.53</v>
+        <v>111.9133333333333</v>
       </c>
       <c r="C108" t="n">
-        <v>21.46246428571429</v>
+        <v>22.13496428571429</v>
       </c>
       <c r="D108" t="n">
-        <v>306.4166666666667</v>
+        <v>320.3633333333333</v>
       </c>
       <c r="E108" t="n">
-        <v>0.04449066666666666</v>
+        <v>0.04349766666666667</v>
       </c>
       <c r="F108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>40608</v>
+        <v>40602</v>
       </c>
       <c r="B109" t="n">
-        <v>115.35</v>
+        <v>114.6166666666667</v>
       </c>
       <c r="C109" t="n">
-        <v>22.68448387096774</v>
+        <v>23.85461290322581</v>
       </c>
       <c r="D109" t="n">
-        <v>321.97</v>
+        <v>322.0633333333333</v>
       </c>
       <c r="E109" t="n">
-        <v>0.044942</v>
+        <v>0.04427200000000001</v>
       </c>
       <c r="F109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>40629</v>
+        <v>40623</v>
       </c>
       <c r="B110" t="n">
-        <v>115.0633333333333</v>
+        <v>124.87</v>
       </c>
       <c r="C110" t="n">
-        <v>24.43967741935484</v>
+        <v>24.194</v>
       </c>
       <c r="D110" t="n">
-        <v>327.56</v>
+        <v>315.15</v>
       </c>
       <c r="E110" t="n">
-        <v>0.044596</v>
+        <v>0.04605433333333334</v>
       </c>
       <c r="F110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>40650</v>
+        <v>40644</v>
       </c>
       <c r="B111" t="n">
-        <v>122.2233333333333</v>
+        <v>125.3766666666667</v>
       </c>
       <c r="C111" t="n">
-        <v>23.788</v>
+        <v>23.131125</v>
       </c>
       <c r="D111" t="n">
-        <v>310.94</v>
+        <v>303.81</v>
       </c>
       <c r="E111" t="n">
-        <v>0.04414266666666666</v>
-      </c>
-      <c r="F111" t="inlineStr"/>
+        <v>0.04355833333333334</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.036733125</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>40671</v>
+        <v>40665</v>
       </c>
       <c r="B112" t="n">
-        <v>113.6433333333333</v>
+        <v>110.8633333333333</v>
       </c>
       <c r="C112" t="n">
-        <v>23.2680625</v>
+        <v>23.5419375</v>
       </c>
       <c r="D112" t="n">
-        <v>305.14</v>
+        <v>296.8333333333334</v>
       </c>
       <c r="E112" t="n">
-        <v>0.04240633333333334</v>
+        <v>0.04160766666666667</v>
       </c>
       <c r="F112" t="n">
-        <v>0.0362540625</v>
+        <v>0.0352959375</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>40692</v>
+        <v>40686</v>
       </c>
       <c r="B113" t="n">
-        <v>114.7966666666667</v>
+        <v>118.9933333333333</v>
       </c>
       <c r="C113" t="n">
-        <v>23.678875</v>
+        <v>23.164</v>
       </c>
       <c r="D113" t="n">
-        <v>305.5733333333333</v>
+        <v>288.4133333333334</v>
       </c>
       <c r="E113" t="n">
-        <v>0.04121233333333334</v>
+        <v>0.04135933333333333</v>
       </c>
       <c r="F113" t="n">
-        <v>0.034816875</v>
+        <v>0.035036</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>40713</v>
+        <v>40707</v>
       </c>
       <c r="B114" t="n">
-        <v>112.1966666666667</v>
+        <v>111.5166666666667</v>
       </c>
       <c r="C114" t="n">
-        <v>22.84083333333333</v>
+        <v>22.32224137931034</v>
       </c>
       <c r="D114" t="n">
-        <v>298.79</v>
+        <v>257.0866666666666</v>
       </c>
       <c r="E114" t="n">
-        <v>0.04191166666666667</v>
+        <v>0.04306833333333333</v>
       </c>
       <c r="F114" t="n">
-        <v>0.03524366666666667</v>
+        <v>0.03527931034482758</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>40734</v>
+        <v>40728</v>
       </c>
       <c r="B115" t="n">
-        <v>117.6033333333333</v>
+        <v>118.1833333333333</v>
       </c>
       <c r="C115" t="n">
-        <v>22.29713793103448</v>
+        <v>22.24693103448276</v>
       </c>
       <c r="D115" t="n">
-        <v>259.02</v>
+        <v>255.5433333333333</v>
       </c>
       <c r="E115" t="n">
-        <v>0.04113333333333333</v>
+        <v>0.04229266666666667</v>
       </c>
       <c r="F115" t="n">
-        <v>0.03460103448275862</v>
+        <v>0.03324448275862069</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>40755</v>
+        <v>40749</v>
       </c>
       <c r="B116" t="n">
-        <v>116.7866666666667</v>
+        <v>109.2833333333333</v>
       </c>
       <c r="C116" t="n">
-        <v>22.50754545454545</v>
+        <v>24.45736363636363</v>
       </c>
       <c r="D116" t="n">
-        <v>244.2666666666667</v>
+        <v>259.2866666666667</v>
       </c>
       <c r="E116" t="n">
-        <v>0.04011766666666666</v>
+        <v>0.04092166666666667</v>
       </c>
       <c r="F116" t="n">
-        <v>0.03256606060606061</v>
+        <v>0.03120848484848485</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>40776</v>
+        <v>40770</v>
       </c>
       <c r="B117" t="n">
-        <v>108.4466666666667</v>
+        <v>110.83</v>
       </c>
       <c r="C117" t="n">
-        <v>25.43227272727272</v>
+        <v>26.8054</v>
       </c>
       <c r="D117" t="n">
-        <v>261.9733333333334</v>
+        <v>276.5766666666667</v>
       </c>
       <c r="E117" t="n">
-        <v>0.039966</v>
+        <v>0.038202</v>
       </c>
       <c r="F117" t="n">
-        <v>0.03052969696969697</v>
+        <v>0.029304</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>40797</v>
+        <v>40791</v>
       </c>
       <c r="B118" t="n">
-        <v>112.4233333333333</v>
+        <v>103.95</v>
       </c>
       <c r="C118" t="n">
-        <v>26.7711</v>
+        <v>26.7025</v>
       </c>
       <c r="D118" t="n">
-        <v>270.9533333333333</v>
+        <v>262.7033333333333</v>
       </c>
       <c r="E118" t="n">
-        <v>0.03798566666666667</v>
+        <v>0.038032</v>
       </c>
       <c r="F118" t="n">
-        <v>0.028856</v>
+        <v>0.02796</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>40818</v>
+        <v>40812</v>
       </c>
       <c r="B119" t="n">
-        <v>102.06</v>
+        <v>111.6666666666667</v>
       </c>
       <c r="C119" t="n">
-        <v>26.6098064516129</v>
+        <v>26.13245161290322</v>
       </c>
       <c r="D119" t="n">
-        <v>264.7033333333333</v>
+        <v>250.15</v>
       </c>
       <c r="E119" t="n">
-        <v>0.04002033333333334</v>
+        <v>0.04124666666666667</v>
       </c>
       <c r="F119" t="n">
-        <v>0.02774129032258064</v>
+        <v>0.02845032258064516</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>40839</v>
+        <v>40833</v>
       </c>
       <c r="B120" t="n">
-        <v>110.82</v>
+        <v>113.6966666666667</v>
       </c>
       <c r="C120" t="n">
-        <v>25.89377419354838</v>
+        <v>25.287</v>
       </c>
       <c r="D120" t="n">
-        <v>258.7566666666667</v>
+        <v>255.3066666666667</v>
       </c>
       <c r="E120" t="n">
-        <v>0.04143133333333333</v>
+        <v>0.038524</v>
       </c>
       <c r="F120" t="n">
-        <v>0.02880483870967742</v>
+        <v>0.030216</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>40860</v>
+        <v>40854</v>
       </c>
       <c r="B121" t="n">
-        <v>112.6466666666667</v>
+        <v>108.1333333333333</v>
       </c>
       <c r="C121" t="n">
-        <v>24.89733333333333</v>
+        <v>24.118</v>
       </c>
       <c r="D121" t="n">
-        <v>252.91</v>
+        <v>266.2</v>
       </c>
       <c r="E121" t="n">
-        <v>0.03615599999999999</v>
+        <v>0.03973533333333333</v>
       </c>
       <c r="F121" t="n">
-        <v>0.03138966666666666</v>
+        <v>0.033737</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>40881</v>
+        <v>40875</v>
       </c>
       <c r="B122" t="n">
-        <v>109.8533333333333</v>
+        <v>103.5433333333333</v>
       </c>
       <c r="C122" t="n">
-        <v>23.73926666666667</v>
+        <v>22.9982</v>
       </c>
       <c r="D122" t="n">
-        <v>261.0666666666667</v>
+        <v>254.15</v>
       </c>
       <c r="E122" t="n">
-        <v>0.03874</v>
+        <v>0.03603133333333333</v>
       </c>
       <c r="F122" t="n">
-        <v>0.03353466666666666</v>
+        <v>0.031066</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>40902</v>
+        <v>40896</v>
       </c>
       <c r="B123" t="n">
-        <v>108.615</v>
+        <v>112.6533333333333</v>
       </c>
       <c r="C123" t="n">
-        <v>22.62766666666667</v>
+        <v>22.5458125</v>
       </c>
       <c r="D123" t="n">
-        <v>262.7866666666667</v>
+        <v>263.3366666666666</v>
       </c>
       <c r="E123" t="n">
-        <v>0.036396</v>
+        <v>0.034397</v>
       </c>
       <c r="F123" t="n">
-        <v>0.02983166666666667</v>
+        <v>0.0287221875</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>40923</v>
+        <v>40917</v>
       </c>
       <c r="B124" t="n">
-        <v>110.9466666666667</v>
+        <v>110.9866666666667</v>
       </c>
       <c r="C124" t="n">
-        <v>22.688</v>
+        <v>22.972375</v>
       </c>
       <c r="D124" t="n">
-        <v>263.4033333333333</v>
+        <v>265.9</v>
       </c>
       <c r="E124" t="n">
-        <v>0.034015</v>
+        <v>0.034386</v>
       </c>
       <c r="F124" t="n">
-        <v>0.028545</v>
+        <v>0.028190625</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>40944</v>
+        <v>40938</v>
       </c>
       <c r="B125" t="n">
-        <v>115.48</v>
+        <v>119.8933333333333</v>
       </c>
       <c r="C125" t="n">
-        <v>23.24696551724138</v>
+        <v>23.90206896551724</v>
       </c>
       <c r="D125" t="n">
-        <v>271.8733333333333</v>
+        <v>267.9533333333333</v>
       </c>
       <c r="E125" t="n">
-        <v>0.035058</v>
+        <v>0.03598633333333334</v>
       </c>
       <c r="F125" t="n">
-        <v>0.02806931034482759</v>
+        <v>0.02787137931034483</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>40965</v>
+        <v>40959</v>
       </c>
       <c r="B126" t="n">
-        <v>124.6033333333333</v>
+        <v>125.5533333333333</v>
       </c>
       <c r="C126" t="n">
-        <v>24.22962068965517</v>
+        <v>24.68826666666667</v>
       </c>
       <c r="D126" t="n">
-        <v>262.1366666666667</v>
+        <v>257.7566666666667</v>
       </c>
       <c r="E126" t="n">
-        <v>0.03426766666666667</v>
+        <v>0.03216266666666667</v>
       </c>
       <c r="F126" t="n">
-        <v>0.02777241379310345</v>
+        <v>0.02749166666666667</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>40986</v>
+        <v>40980</v>
       </c>
       <c r="B127" t="n">
-        <v>125.7433333333333</v>
+        <v>124.58</v>
       </c>
       <c r="C127" t="n">
-        <v>24.8908</v>
+        <v>25.23554838709677</v>
       </c>
       <c r="D127" t="n">
-        <v>257.3233333333333</v>
+        <v>254.6433333333333</v>
       </c>
       <c r="E127" t="n">
-        <v>0.03419266666666667</v>
+        <v>0.03243366666666667</v>
       </c>
       <c r="F127" t="n">
-        <v>0.02734</v>
+        <v>0.02706774193548387</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>41007</v>
+        <v>41001</v>
       </c>
       <c r="B128" t="n">
-        <v>122.86</v>
+        <v>118.7266666666667</v>
       </c>
       <c r="C128" t="n">
-        <v>25.22696774193548</v>
+        <v>25.2098064516129</v>
       </c>
       <c r="D128" t="n">
-        <v>245.5633333333333</v>
+        <v>238.53</v>
       </c>
       <c r="E128" t="n">
-        <v>0.031528</v>
+        <v>0.03115366666666667</v>
       </c>
       <c r="F128" t="n">
-        <v>0.02702483870967742</v>
+        <v>0.02693903225806452</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>41028</v>
+        <v>41022</v>
       </c>
       <c r="B129" t="n">
-        <v>119.59</v>
+        <v>111.8</v>
       </c>
       <c r="C129" t="n">
-        <v>25.20122580645161</v>
+        <v>24.55754838709677</v>
       </c>
       <c r="D129" t="n">
-        <v>242.3166666666667</v>
+        <v>251.4133333333333</v>
       </c>
       <c r="E129" t="n">
-        <v>0.031087</v>
+        <v>0.029234</v>
       </c>
       <c r="F129" t="n">
-        <v>0.02689612903225807</v>
+        <v>0.02478903225806452</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>41049</v>
+        <v>41043</v>
       </c>
       <c r="B130" t="n">
-        <v>108.2533333333333</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="C130" t="n">
-        <v>24.21161290322581</v>
+        <v>23.6971724137931</v>
       </c>
       <c r="D130" t="n">
-        <v>259.21</v>
+        <v>260.8566666666667</v>
       </c>
       <c r="E130" t="n">
-        <v>0.02939833333333334</v>
+        <v>0.02682233333333333</v>
       </c>
       <c r="F130" t="n">
-        <v>0.02365774193548387</v>
+        <v>0.02216758620689655</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>41070</v>
+        <v>41064</v>
       </c>
       <c r="B131" t="n">
-        <v>98.48999999999999</v>
+        <v>91</v>
       </c>
       <c r="C131" t="n">
-        <v>23.76524137931034</v>
+        <v>23.90137931034483</v>
       </c>
       <c r="D131" t="n">
-        <v>255.4266666666667</v>
+        <v>254.3566666666667</v>
       </c>
       <c r="E131" t="n">
-        <v>0.02770233333333333</v>
+        <v>0.029016</v>
       </c>
       <c r="F131" t="n">
-        <v>0.02283862068965517</v>
+        <v>0.02418068965517241</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>41091</v>
+        <v>41085</v>
       </c>
       <c r="B132" t="n">
-        <v>97.49333333333334</v>
+        <v>103.1666666666667</v>
       </c>
       <c r="C132" t="n">
-        <v>23.959375</v>
+        <v>24.025</v>
       </c>
       <c r="D132" t="n">
-        <v>260.6</v>
+        <v>263.2566666666667</v>
       </c>
       <c r="E132" t="n">
-        <v>0.02881466666666667</v>
+        <v>0.025059</v>
       </c>
       <c r="F132" t="n">
-        <v>0.02442</v>
+        <v>0.02274</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>41112</v>
+        <v>41106</v>
       </c>
       <c r="B133" t="n">
-        <v>104.45</v>
+        <v>109.3466666666667</v>
       </c>
       <c r="C133" t="n">
-        <v>24.0578125</v>
+        <v>24.32370967741936</v>
       </c>
       <c r="D133" t="n">
-        <v>264.3433333333333</v>
+        <v>277.4566666666667</v>
       </c>
       <c r="E133" t="n">
-        <v>0.02418433333333333</v>
+        <v>0.02479666666666666</v>
       </c>
       <c r="F133" t="n">
-        <v>0.0219</v>
+        <v>0.02057483870967742</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>41133</v>
+        <v>41127</v>
       </c>
       <c r="B134" t="n">
-        <v>113.3833333333333</v>
+        <v>112.7033333333333</v>
       </c>
       <c r="C134" t="n">
-        <v>24.63690322580645</v>
+        <v>25.26329032258064</v>
       </c>
       <c r="D134" t="n">
-        <v>277.0233333333334</v>
+        <v>271.5133333333334</v>
       </c>
       <c r="E134" t="n">
-        <v>0.024047</v>
+        <v>0.02321366666666667</v>
       </c>
       <c r="F134" t="n">
-        <v>0.0202316129032258</v>
+        <v>0.01954516129032258</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>41154</v>
+        <v>41148</v>
       </c>
       <c r="B135" t="n">
-        <v>115.3766666666667</v>
+        <v>114.7466666666667</v>
       </c>
       <c r="C135" t="n">
-        <v>25.55757142857143</v>
+        <v>26.05157142857143</v>
       </c>
       <c r="D135" t="n">
-        <v>267.96</v>
+        <v>268.7633333333333</v>
       </c>
       <c r="E135" t="n">
-        <v>0.023189</v>
+        <v>0.02690266666666667</v>
       </c>
       <c r="F135" t="n">
-        <v>0.01933214285714285</v>
+        <v>0.01955714285714286</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>41175</v>
+        <v>41169</v>
       </c>
       <c r="B136" t="n">
-        <v>110.3466666666667</v>
+        <v>111.8866666666667</v>
       </c>
       <c r="C136" t="n">
-        <v>26.29857142857143</v>
+        <v>26.69318181818182</v>
       </c>
       <c r="D136" t="n">
-        <v>270.0566666666667</v>
+        <v>249</v>
       </c>
       <c r="E136" t="n">
-        <v>0.02668133333333333</v>
+        <v>0.02629666666666667</v>
       </c>
       <c r="F136" t="n">
-        <v>0.01966964285714286</v>
+        <v>0.01971454545454545</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>41196</v>
+        <v>41190</v>
       </c>
       <c r="B137" t="n">
-        <v>115.4066666666667</v>
+        <v>109.4766666666667</v>
       </c>
       <c r="C137" t="n">
-        <v>26.86287878787879</v>
+        <v>27.20227272727272</v>
       </c>
       <c r="D137" t="n">
-        <v>255.4533333333333</v>
+        <v>253.95</v>
       </c>
       <c r="E137" t="n">
-        <v>0.02613933333333333</v>
+        <v>0.025968</v>
       </c>
       <c r="F137" t="n">
-        <v>0.0196869696969697</v>
+        <v>0.01963181818181818</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>41217</v>
+        <v>41211</v>
       </c>
       <c r="B138" t="n">
-        <v>107.0466666666667</v>
+        <v>110.7833333333333</v>
       </c>
       <c r="C138" t="n">
-        <v>27.325</v>
+        <v>27.5</v>
       </c>
       <c r="D138" t="n">
-        <v>257.5066666666667</v>
+        <v>261.9866666666667</v>
       </c>
       <c r="E138" t="n">
-        <v>0.025091</v>
+        <v>0.024136</v>
       </c>
       <c r="F138" t="n">
-        <v>0.01946666666666667</v>
+        <v>0.01893</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>41238</v>
+        <v>41232</v>
       </c>
       <c r="B139" t="n">
-        <v>111.0733333333333</v>
+        <v>107.2266666666667</v>
       </c>
       <c r="C139" t="n">
-        <v>27.5875</v>
+        <v>27.27867741935484</v>
       </c>
       <c r="D139" t="n">
-        <v>261.0833333333333</v>
+        <v>254.9266666666667</v>
       </c>
       <c r="E139" t="n">
-        <v>0.02477366666666667</v>
+        <v>0.02369933333333333</v>
       </c>
       <c r="F139" t="n">
-        <v>0.01866166666666667</v>
+        <v>0.01808387096774194</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>41259</v>
+        <v>41253</v>
       </c>
       <c r="B140" t="n">
-        <v>108.1433333333333</v>
+        <v>110.9466666666667</v>
       </c>
       <c r="C140" t="n">
-        <v>26.98987096774193</v>
+        <v>26.41225806451613</v>
       </c>
       <c r="D140" t="n">
-        <v>254.2733333333333</v>
+        <v>250.36</v>
       </c>
       <c r="E140" t="n">
-        <v>0.02424733333333333</v>
+        <v>0.02375366666666667</v>
       </c>
       <c r="F140" t="n">
-        <v>0.01778354838709677</v>
+        <v>0.01718290322580645</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>41280</v>
+        <v>41274</v>
       </c>
       <c r="B141" t="n">
-        <v>111.37</v>
+        <v>111.77</v>
       </c>
       <c r="C141" t="n">
-        <v>26.21616129032258</v>
+        <v>25.85487096774193</v>
       </c>
       <c r="D141" t="n">
-        <v>248.9166666666667</v>
+        <v>252.4533333333333</v>
       </c>
       <c r="E141" t="n">
-        <v>0.02559133333333333</v>
+        <v>0.02563433333333333</v>
       </c>
       <c r="F141" t="n">
-        <v>0.01784645161290322</v>
+        <v>0.01949483870967742</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>41301</v>
+        <v>41295</v>
       </c>
       <c r="B142" t="n">
-        <v>113.4133333333333</v>
+        <v>118.3866666666667</v>
       </c>
       <c r="C142" t="n">
-        <v>25.67422580645161</v>
+        <v>25.80028571428571</v>
       </c>
       <c r="D142" t="n">
-        <v>250.8366666666667</v>
+        <v>254.0866666666667</v>
       </c>
       <c r="E142" t="n">
-        <v>0.026809</v>
+        <v>0.02640266666666667</v>
       </c>
       <c r="F142" t="n">
-        <v>0.02031903225806452</v>
+        <v>0.02022571428571429</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>41322</v>
+        <v>41316</v>
       </c>
       <c r="B143" t="n">
-        <v>117.4733333333333</v>
+        <v>110.1933333333333</v>
       </c>
       <c r="C143" t="n">
-        <v>25.96078571428572</v>
+        <v>26.32544827586207</v>
       </c>
       <c r="D143" t="n">
-        <v>257.9766666666667</v>
+        <v>257.45</v>
       </c>
       <c r="E143" t="n">
-        <v>0.02647366666666667</v>
+        <v>0.02442166666666666</v>
       </c>
       <c r="F143" t="n">
-        <v>0.01983071428571429</v>
+        <v>0.01914172413793104</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>41343</v>
+        <v>41337</v>
       </c>
       <c r="B144" t="n">
-        <v>110.43</v>
+        <v>108</v>
       </c>
       <c r="C144" t="n">
-        <v>26.5878275862069</v>
+        <v>27.11258620689655</v>
       </c>
       <c r="D144" t="n">
-        <v>266.7966666666667</v>
+        <v>270.8933333333334</v>
       </c>
       <c r="E144" t="n">
-        <v>0.02507833333333333</v>
+        <v>0.02318933333333333</v>
       </c>
       <c r="F144" t="n">
-        <v>0.01898241379310345</v>
+        <v>0.01866379310344828</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>41364</v>
+        <v>41358</v>
       </c>
       <c r="B145" t="n">
-        <v>110.815</v>
+        <v>101.2966666666667</v>
       </c>
       <c r="C145" t="n">
-        <v>27.2445625</v>
+        <v>26.8565</v>
       </c>
       <c r="D145" t="n">
-        <v>272.5466666666667</v>
+        <v>264.71</v>
       </c>
       <c r="E145" t="n">
-        <v>0.02277933333333333</v>
+        <v>0.02235366666666667</v>
       </c>
       <c r="F145" t="n">
-        <v>0.018389375</v>
+        <v>0.017265</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>41385</v>
+        <v>41379</v>
       </c>
       <c r="B146" t="n">
-        <v>100.1433333333333</v>
+        <v>105.0366666666667</v>
       </c>
       <c r="C146" t="n">
-        <v>26.66246875</v>
+        <v>26.398</v>
       </c>
       <c r="D146" t="n">
-        <v>258.35</v>
+        <v>248.87</v>
       </c>
       <c r="E146" t="n">
-        <v>0.022195</v>
+        <v>0.02182566666666667</v>
       </c>
       <c r="F146" t="n">
-        <v>0.0167028125</v>
+        <v>0.01639129032258065</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>41406</v>
+        <v>41400</v>
       </c>
       <c r="B147" t="n">
-        <v>103.1833333333333</v>
+        <v>102.6266666666667</v>
       </c>
       <c r="C147" t="n">
-        <v>26.377</v>
+        <v>26.335</v>
       </c>
       <c r="D147" t="n">
-        <v>249.95</v>
+        <v>249.8</v>
       </c>
       <c r="E147" t="n">
-        <v>0.02258266666666667</v>
+        <v>0.02267266666666667</v>
       </c>
       <c r="F147" t="n">
-        <v>0.01696709677419355</v>
+        <v>0.01811870967741936</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>41427</v>
+        <v>41421</v>
       </c>
       <c r="B148" t="n">
-        <v>101.5033333333333</v>
+        <v>105.6233333333333</v>
       </c>
       <c r="C148" t="n">
-        <v>26.315</v>
+        <v>26.28</v>
       </c>
       <c r="D148" t="n">
-        <v>254.3533333333333</v>
+        <v>262.1766666666667</v>
       </c>
       <c r="E148" t="n">
-        <v>0.023377</v>
+        <v>0.023851</v>
       </c>
       <c r="F148" t="n">
-        <v>0.01872071428571429</v>
+        <v>0.02005571428571429</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>41448</v>
+        <v>41442</v>
       </c>
       <c r="B149" t="n">
-        <v>101.0766666666667</v>
+        <v>107.5266666666667</v>
       </c>
       <c r="C149" t="n">
-        <v>26.2625</v>
+        <v>26.20636363636364</v>
       </c>
       <c r="D149" t="n">
-        <v>262.2633333333333</v>
+        <v>259.2566666666667</v>
       </c>
       <c r="E149" t="n">
-        <v>0.02706133333333333</v>
+        <v>0.02598</v>
       </c>
       <c r="F149" t="n">
-        <v>0.02072321428571429</v>
+        <v>0.02117545454545455</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>41469</v>
+        <v>41463</v>
       </c>
       <c r="B150" t="n">
-        <v>108.9966666666667</v>
+        <v>107.3566666666667</v>
       </c>
       <c r="C150" t="n">
-        <v>26.17242424242424</v>
+        <v>26.10454545454546</v>
       </c>
       <c r="D150" t="n">
-        <v>256.4566666666666</v>
+        <v>271.9266666666667</v>
       </c>
       <c r="E150" t="n">
-        <v>0.02493066666666667</v>
+        <v>0.025672</v>
       </c>
       <c r="F150" t="n">
-        <v>0.02115636363636364</v>
+        <v>0.02111818181818182</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>41490</v>
+        <v>41484</v>
       </c>
       <c r="B151" t="n">
-        <v>108.7833333333333</v>
+        <v>110.0666666666667</v>
       </c>
       <c r="C151" t="n">
-        <v>26.09253333333333</v>
+        <v>26.1014</v>
       </c>
       <c r="D151" t="n">
-        <v>274.3566666666667</v>
+        <v>271.82</v>
       </c>
       <c r="E151" t="n">
-        <v>0.02551433333333333</v>
+        <v>0.02715733333333333</v>
       </c>
       <c r="F151" t="n">
-        <v>0.02128066666666667</v>
+        <v>0.021878</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>41511</v>
+        <v>41505</v>
       </c>
       <c r="B152" t="n">
-        <v>110.8333333333333</v>
+        <v>114.52</v>
       </c>
       <c r="C152" t="n">
-        <v>26.10583333333334</v>
+        <v>26.38045161290323</v>
       </c>
       <c r="D152" t="n">
-        <v>277.4</v>
+        <v>277.69</v>
       </c>
       <c r="E152" t="n">
-        <v>0.02746366666666667</v>
+        <v>0.02801233333333333</v>
       </c>
       <c r="F152" t="n">
-        <v>0.02217666666666667</v>
+        <v>0.02216354838709677</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>41532</v>
+        <v>41526</v>
       </c>
       <c r="B153" t="n">
-        <v>110.9733333333333</v>
+        <v>108.4566666666667</v>
       </c>
       <c r="C153" t="n">
-        <v>26.59158064516129</v>
+        <v>27.01383870967742</v>
       </c>
       <c r="D153" t="n">
-        <v>279.0433333333334</v>
+        <v>279.32</v>
       </c>
       <c r="E153" t="n">
-        <v>0.027495</v>
+        <v>0.026029</v>
       </c>
       <c r="F153" t="n">
-        <v>0.02198741935483871</v>
+        <v>0.02163516129032258</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>41553</v>
+        <v>41547</v>
       </c>
       <c r="B154" t="n">
-        <v>109.6066666666667</v>
+        <v>109.74</v>
       </c>
       <c r="C154" t="n">
-        <v>27.05</v>
+        <v>27.064</v>
       </c>
       <c r="D154" t="n">
-        <v>280.6033333333334</v>
+        <v>268.9233333333333</v>
       </c>
       <c r="E154" t="n">
-        <v>0.02632966666666666</v>
+        <v>0.02663033333333333</v>
       </c>
       <c r="F154" t="n">
-        <v>0.02136612903225807</v>
+        <v>0.02079709677419355</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>41574</v>
+        <v>41568</v>
       </c>
       <c r="B155" t="n">
-        <v>108.7166666666667</v>
+        <v>105.9733333333333</v>
       </c>
       <c r="C155" t="n">
-        <v>27.071</v>
+        <v>27.4901724137931</v>
       </c>
       <c r="D155" t="n">
-        <v>266.7466666666667</v>
+        <v>278.0366666666666</v>
       </c>
       <c r="E155" t="n">
-        <v>0.02592033333333333</v>
+        <v>0.02578033333333333</v>
       </c>
       <c r="F155" t="n">
-        <v>0.02051258064516129</v>
+        <v>0.02035</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>41595</v>
+        <v>41589</v>
       </c>
       <c r="B156" t="n">
-        <v>108.48</v>
+        <v>110.8633333333333</v>
       </c>
       <c r="C156" t="n">
-        <v>27.78079310344827</v>
+        <v>28.2334375</v>
       </c>
       <c r="D156" t="n">
-        <v>275.7833333333334</v>
+        <v>283.0033333333333</v>
       </c>
       <c r="E156" t="n">
-        <v>0.02532166666666667</v>
+        <v>0.02580733333333333</v>
       </c>
       <c r="F156" t="n">
-        <v>0.02035</v>
+        <v>0.020473125</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>41616</v>
+        <v>41610</v>
       </c>
       <c r="B157" t="n">
-        <v>110.13</v>
+        <v>111.63</v>
       </c>
       <c r="C157" t="n">
-        <v>28.07396875</v>
+        <v>27.75503125</v>
       </c>
       <c r="D157" t="n">
-        <v>275.9633333333333</v>
+        <v>285.04</v>
       </c>
       <c r="E157" t="n">
-        <v>0.02690533333333333</v>
+        <v>0.027379</v>
       </c>
       <c r="F157" t="n">
-        <v>0.0209040625</v>
+        <v>0.0217659375</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>41637</v>
+        <v>41631</v>
       </c>
       <c r="B158" t="n">
-        <v>111.5333333333333</v>
+        <v>106.9166666666667</v>
       </c>
       <c r="C158" t="n">
-        <v>27.5955625</v>
+        <v>26.58341935483871</v>
       </c>
       <c r="D158" t="n">
-        <v>291.36</v>
+        <v>298.91</v>
       </c>
       <c r="E158" t="n">
-        <v>0.02800833333333333</v>
+        <v>0.02667866666666667</v>
       </c>
       <c r="F158" t="n">
-        <v>0.022196875</v>
+        <v>0.02135225806451613</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>41658</v>
+        <v>41652</v>
       </c>
       <c r="B159" t="n">
-        <v>106.3933333333333</v>
+        <v>106.16</v>
       </c>
       <c r="C159" t="n">
-        <v>26.01958064516129</v>
+        <v>24.91307142857143</v>
       </c>
       <c r="D159" t="n">
-        <v>298.69</v>
+        <v>302.83</v>
       </c>
       <c r="E159" t="n">
-        <v>0.02593333333333333</v>
+        <v>0.024483</v>
       </c>
       <c r="F159" t="n">
-        <v>0.02078774193548387</v>
+        <v>0.01979928571428571</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>41679</v>
+        <v>41673</v>
       </c>
       <c r="B160" t="n">
-        <v>108.9433333333333</v>
+        <v>110.3766666666667</v>
       </c>
       <c r="C160" t="n">
-        <v>24.42332142857143</v>
+        <v>23.44382142857143</v>
       </c>
       <c r="D160" t="n">
-        <v>306.8133333333333</v>
+        <v>303.21</v>
       </c>
       <c r="E160" t="n">
-        <v>0.02474566666666667</v>
+        <v>0.024772</v>
       </c>
       <c r="F160" t="n">
-        <v>0.01972678571428571</v>
+        <v>0.01958178571428571</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>41700</v>
+        <v>41694</v>
       </c>
       <c r="B161" t="n">
-        <v>110.49</v>
+        <v>107.0166666666667</v>
       </c>
       <c r="C161" t="n">
-        <v>22.96974193548387</v>
+        <v>22.09993548387097</v>
       </c>
       <c r="D161" t="n">
-        <v>301.9533333333333</v>
+        <v>307.7633333333333</v>
       </c>
       <c r="E161" t="n">
-        <v>0.02408066666666667</v>
+        <v>0.023681</v>
       </c>
       <c r="F161" t="n">
-        <v>0.01948870967741936</v>
+        <v>0.01919967741935484</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>41721</v>
+        <v>41715</v>
       </c>
       <c r="B162" t="n">
-        <v>106.8466666666667</v>
+        <v>106.12</v>
       </c>
       <c r="C162" t="n">
-        <v>21.66503225806452</v>
+        <v>20.8752</v>
       </c>
       <c r="D162" t="n">
-        <v>306.6933333333333</v>
+        <v>316.52</v>
       </c>
       <c r="E162" t="n">
-        <v>0.02420033333333333</v>
+        <v>0.02358966666666667</v>
       </c>
       <c r="F162" t="n">
-        <v>0.01905516129032258</v>
+        <v>0.018716</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>41742</v>
+        <v>41736</v>
       </c>
       <c r="B163" t="n">
-        <v>108.49</v>
+        <v>108.6066666666667</v>
       </c>
       <c r="C163" t="n">
-        <v>20.5336</v>
+        <v>19.8504</v>
       </c>
       <c r="D163" t="n">
-        <v>318.8933333333333</v>
+        <v>325.4833333333333</v>
       </c>
       <c r="E163" t="n">
-        <v>0.023337</v>
+        <v>0.02305533333333333</v>
       </c>
       <c r="F163" t="n">
-        <v>0.018513</v>
+        <v>0.018107</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>41763</v>
+        <v>41757</v>
       </c>
       <c r="B164" t="n">
-        <v>108.01</v>
+        <v>109.4966666666667</v>
       </c>
       <c r="C164" t="n">
-        <v>19.61306666666667</v>
+        <v>19.2948</v>
       </c>
       <c r="D164" t="n">
-        <v>321.6166666666667</v>
+        <v>314.62</v>
       </c>
       <c r="E164" t="n">
-        <v>0.02244566666666667</v>
+        <v>0.02112966666666667</v>
       </c>
       <c r="F164" t="n">
-        <v>0.01779333333333333</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>41784</v>
+        <v>41778</v>
       </c>
       <c r="B165" t="n">
-        <v>110.3933333333333</v>
+        <v>109.53</v>
       </c>
       <c r="C165" t="n">
-        <v>19.13566666666667</v>
+        <v>18.51945161290323</v>
       </c>
       <c r="D165" t="n">
-        <v>317.42</v>
+        <v>312.4833333333333</v>
       </c>
       <c r="E165" t="n">
-        <v>0.02127666666666667</v>
+        <v>0.02089833333333333</v>
       </c>
       <c r="F165" t="n">
-        <v>0.01660333333333333</v>
+        <v>0.01591354838709677</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>41805</v>
+        <v>41799</v>
       </c>
       <c r="B166" t="n">
-        <v>113.0966666666667</v>
+        <v>112.6733333333333</v>
       </c>
       <c r="C166" t="n">
-        <v>18.12858064516129</v>
+        <v>17.34683870967742</v>
       </c>
       <c r="D166" t="n">
-        <v>302.2233333333333</v>
+        <v>313.8866666666667</v>
       </c>
       <c r="E166" t="n">
-        <v>0.02077733333333334</v>
+        <v>0.01998866666666667</v>
       </c>
       <c r="F166" t="n">
-        <v>0.01559741935483871</v>
+        <v>0.01496516129032258</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>41826</v>
+        <v>41820</v>
       </c>
       <c r="B167" t="n">
-        <v>110.3733333333333</v>
+        <v>107.5333333333333</v>
       </c>
       <c r="C167" t="n">
-        <v>17.53041935483871</v>
+        <v>18.08906451612903</v>
       </c>
       <c r="D167" t="n">
-        <v>318.23</v>
+        <v>322.0433333333334</v>
       </c>
       <c r="E167" t="n">
-        <v>0.01987433333333333</v>
+        <v>0.01905</v>
       </c>
       <c r="F167" t="n">
-        <v>0.01471870967741935</v>
+        <v>0.01424903225806451</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>41847</v>
+        <v>41841</v>
       </c>
       <c r="B168" t="n">
-        <v>107.8433333333333</v>
+        <v>104.7933333333333</v>
       </c>
       <c r="C168" t="n">
-        <v>18.36838709677419</v>
+        <v>19.73558620689655</v>
       </c>
       <c r="D168" t="n">
-        <v>323.33</v>
+        <v>315.7133333333334</v>
       </c>
       <c r="E168" t="n">
-        <v>0.01897633333333333</v>
+        <v>0.01818633333333333</v>
       </c>
       <c r="F168" t="n">
-        <v>0.0140141935483871</v>
+        <v>0.01280413793103448</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>41868</v>
+        <v>41862</v>
       </c>
       <c r="B169" t="n">
-        <v>102.2433333333333</v>
+        <v>102.9233333333333</v>
       </c>
       <c r="C169" t="n">
-        <v>20.58089655172414</v>
+        <v>22.1573125</v>
       </c>
       <c r="D169" t="n">
-        <v>307.2666666666667</v>
+        <v>308.1733333333333</v>
       </c>
       <c r="E169" t="n">
-        <v>0.01762833333333333</v>
+        <v>0.01638233333333334</v>
       </c>
       <c r="F169" t="n">
-        <v>0.01205103448275862</v>
+        <v>0.010793125</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>41889</v>
+        <v>41883</v>
       </c>
       <c r="B170" t="n">
-        <v>100.4066666666667</v>
+        <v>97.44333333333333</v>
       </c>
       <c r="C170" t="n">
-        <v>22.60290625</v>
+        <v>23.49409375</v>
       </c>
       <c r="D170" t="n">
-        <v>318.0133333333333</v>
+        <v>309</v>
       </c>
       <c r="E170" t="n">
-        <v>0.016301</v>
+        <v>0.01666433333333333</v>
       </c>
       <c r="F170" t="n">
-        <v>0.0109090625</v>
+        <v>0.0111409375</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>41910</v>
+        <v>41904</v>
       </c>
       <c r="B171" t="n">
-        <v>97.13333333333334</v>
+        <v>89.33</v>
       </c>
       <c r="C171" t="n">
-        <v>23.9396875</v>
+        <v>23.59667741935484</v>
       </c>
       <c r="D171" t="n">
-        <v>314.26</v>
+        <v>327.3933333333333</v>
       </c>
       <c r="E171" t="n">
-        <v>0.01626333333333333</v>
+        <v>0.015762</v>
       </c>
       <c r="F171" t="n">
-        <v>0.011256875</v>
+        <v>0.01096483870967742</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>41931</v>
+        <v>41925</v>
       </c>
       <c r="B172" t="n">
-        <v>85.65333333333334</v>
+        <v>85.14</v>
       </c>
       <c r="C172" t="n">
-        <v>23.32232258064516</v>
+        <v>22.94878571428572</v>
       </c>
       <c r="D172" t="n">
-        <v>310.1066666666667</v>
+        <v>315.6133333333333</v>
       </c>
       <c r="E172" t="n">
-        <v>0.015726</v>
+        <v>0.01543166666666667</v>
       </c>
       <c r="F172" t="n">
-        <v>0.01077516129032258</v>
+        <v>0.01034285714285714</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>41952</v>
+        <v>41946</v>
       </c>
       <c r="B173" t="n">
-        <v>82.69</v>
+        <v>79.90666666666667</v>
       </c>
       <c r="C173" t="n">
-        <v>23.28753571428571</v>
+        <v>23.96503571428572</v>
       </c>
       <c r="D173" t="n">
-        <v>302.4633333333333</v>
+        <v>315.22</v>
       </c>
       <c r="E173" t="n">
-        <v>0.01499466666666666</v>
+        <v>0.01466633333333334</v>
       </c>
       <c r="F173" t="n">
-        <v>0.009967857142857143</v>
+        <v>0.009217857142857142</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>41973</v>
+        <v>41967</v>
       </c>
       <c r="B174" t="n">
-        <v>71.74333333333334</v>
+        <v>61.32333333333334</v>
       </c>
       <c r="C174" t="n">
-        <v>24.03057575757576</v>
+        <v>22.79560606060606</v>
       </c>
       <c r="D174" t="n">
-        <v>330.34</v>
+        <v>321.2366666666667</v>
       </c>
       <c r="E174" t="n">
-        <v>0.01438766666666667</v>
+        <v>0.01367066666666667</v>
       </c>
       <c r="F174" t="n">
-        <v>0.00887121212121212</v>
+        <v>0.00831969696969697</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>41994</v>
+        <v>41988</v>
       </c>
       <c r="B175" t="n">
-        <v>60.53333333333333</v>
+        <v>54.21333333333333</v>
       </c>
       <c r="C175" t="n">
-        <v>22.17812121212121</v>
+        <v>21.15853333333333</v>
       </c>
       <c r="D175" t="n">
-        <v>319.9066666666667</v>
+        <v>325.7833333333333</v>
       </c>
       <c r="E175" t="n">
-        <v>0.013253</v>
+        <v>0.012489</v>
       </c>
       <c r="F175" t="n">
-        <v>0.008043939393939395</v>
+        <v>0.007372666666666667</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>42015</v>
+        <v>42009</v>
       </c>
       <c r="B176" t="n">
-        <v>48.32333333333333</v>
+        <v>48.37</v>
       </c>
       <c r="C176" t="n">
-        <v>20.91796666666666</v>
+        <v>20.43683333333333</v>
       </c>
       <c r="D176" t="n">
-        <v>323.16</v>
+        <v>330.39</v>
       </c>
       <c r="E176" t="n">
-        <v>0.0121</v>
+        <v>0.01107533333333333</v>
       </c>
       <c r="F176" t="n">
-        <v>0.006887333333333334</v>
+        <v>0.005916666666666667</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>42036</v>
+        <v>42030</v>
       </c>
       <c r="B177" t="n">
-        <v>54.16333333333333</v>
+        <v>61.44</v>
       </c>
       <c r="C177" t="n">
-        <v>20.46435714285714</v>
+        <v>21.85985714285714</v>
       </c>
       <c r="D177" t="n">
-        <v>325.7433333333333</v>
+        <v>335.5933333333333</v>
       </c>
       <c r="E177" t="n">
-        <v>0.010564</v>
+        <v>0.01033666666666667</v>
       </c>
       <c r="F177" t="n">
-        <v>0.005505714285714286</v>
+        <v>0.005055714285714286</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>42057</v>
+        <v>42051</v>
       </c>
       <c r="B178" t="n">
-        <v>59.34</v>
+        <v>58.93</v>
       </c>
       <c r="C178" t="n">
-        <v>22.55760714285714</v>
+        <v>22.63721875</v>
       </c>
       <c r="D178" t="n">
-        <v>337.4366666666667</v>
+        <v>329.62</v>
       </c>
       <c r="E178" t="n">
-        <v>0.01031</v>
+        <v>0.010146</v>
       </c>
       <c r="F178" t="n">
-        <v>0.004830714285714286</v>
+        <v>0.0040034375</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>42078</v>
+        <v>42072</v>
       </c>
       <c r="B179" t="n">
-        <v>53.85</v>
+        <v>56.33</v>
       </c>
       <c r="C179" t="n">
-        <v>22.3115</v>
+        <v>21.6600625</v>
       </c>
       <c r="D179" t="n">
-        <v>332.8366666666667</v>
+        <v>337.1766666666667</v>
       </c>
       <c r="E179" t="n">
-        <v>0.01010366666666667</v>
+        <v>0.01015466666666667</v>
       </c>
       <c r="F179" t="n">
-        <v>0.003485</v>
+        <v>0.002448125</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>42099</v>
+        <v>42093</v>
       </c>
       <c r="B180" t="n">
-        <v>57.3275</v>
+        <v>63.45</v>
       </c>
       <c r="C180" t="n">
-        <v>21.3855</v>
+        <v>20.8773</v>
       </c>
       <c r="D180" t="n">
-        <v>321.2266666666667</v>
+        <v>319.0866666666666</v>
       </c>
       <c r="E180" t="n">
-        <v>0.009894999999999999</v>
+        <v>0.009574666666666667</v>
       </c>
       <c r="F180" t="n">
-        <v>0.002606666666666666</v>
+        <v>0.003465333333333333</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>42120</v>
+        <v>42114</v>
       </c>
       <c r="B181" t="n">
-        <v>64.98</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="C181" t="n">
-        <v>20.6232</v>
+        <v>20.39731034482759</v>
       </c>
       <c r="D181" t="n">
-        <v>325</v>
+        <v>317.1433333333333</v>
       </c>
       <c r="E181" t="n">
-        <v>0.010265</v>
+        <v>0.013294</v>
       </c>
       <c r="F181" t="n">
-        <v>0.003894666666666667</v>
+        <v>0.004946896551724138</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>42141</v>
+        <v>42135</v>
       </c>
       <c r="B182" t="n">
-        <v>66.45</v>
+        <v>65.10666666666667</v>
       </c>
       <c r="C182" t="n">
-        <v>20.3408275862069</v>
+        <v>20.257125</v>
       </c>
       <c r="D182" t="n">
-        <v>329.5166666666667</v>
+        <v>321.8966666666666</v>
       </c>
       <c r="E182" t="n">
-        <v>0.013885</v>
+        <v>0.01313233333333333</v>
       </c>
       <c r="F182" t="n">
-        <v>0.005511724137931035</v>
+        <v>0.006700625</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>42162</v>
+        <v>42156</v>
       </c>
       <c r="B183" t="n">
-        <v>62.89666666666667</v>
+        <v>63.23333333333333</v>
       </c>
       <c r="C183" t="n">
-        <v>20.3030625</v>
+        <v>20.3949375</v>
       </c>
       <c r="D183" t="n">
-        <v>325.7966666666667</v>
+        <v>305.57</v>
       </c>
       <c r="E183" t="n">
-        <v>0.016596</v>
+        <v>0.017324</v>
       </c>
       <c r="F183" t="n">
-        <v>0.0074728125</v>
+        <v>0.009017187499999999</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>42183</v>
+        <v>42177</v>
       </c>
       <c r="B184" t="n">
-        <v>62.42666666666666</v>
+        <v>58.14333333333333</v>
       </c>
       <c r="C184" t="n">
-        <v>20.440875</v>
+        <v>20.47567741935484</v>
       </c>
       <c r="D184" t="n">
-        <v>299.32</v>
+        <v>290.0733333333333</v>
       </c>
       <c r="E184" t="n">
-        <v>0.01753566666666667</v>
+        <v>0.01774633333333333</v>
       </c>
       <c r="F184" t="n">
-        <v>0.009789374999999998</v>
+        <v>0.009247419354838709</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>42204</v>
+        <v>42198</v>
       </c>
       <c r="B185" t="n">
-        <v>56.8</v>
+        <v>50.41666666666667</v>
       </c>
       <c r="C185" t="n">
-        <v>20.48832258064516</v>
+        <v>20.42870967741936</v>
       </c>
       <c r="D185" t="n">
-        <v>289.2066666666666</v>
+        <v>290.4966666666667</v>
       </c>
       <c r="E185" t="n">
-        <v>0.01619</v>
+        <v>0.014725</v>
       </c>
       <c r="F185" t="n">
-        <v>0.00880258064516129</v>
+        <v>0.008085806451612904</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>42225</v>
+        <v>42219</v>
       </c>
       <c r="B186" t="n">
-        <v>49.81</v>
+        <v>43.61333333333333</v>
       </c>
       <c r="C186" t="n">
-        <v>20.1441935483871</v>
+        <v>19.57516129032258</v>
       </c>
       <c r="D186" t="n">
-        <v>302.3633333333333</v>
+        <v>314.6733333333333</v>
       </c>
       <c r="E186" t="n">
-        <v>0.01479466666666667</v>
+        <v>0.01453533333333333</v>
       </c>
       <c r="F186" t="n">
-        <v>0.008246129032258066</v>
+        <v>0.008566774193548388</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>42246</v>
+        <v>42240</v>
       </c>
       <c r="B187" t="n">
-        <v>52.78333333333333</v>
+        <v>46.96</v>
       </c>
       <c r="C187" t="n">
-        <v>19.29064516129032</v>
+        <v>18.99736666666667</v>
       </c>
       <c r="D187" t="n">
-        <v>311.97</v>
+        <v>304.3433333333333</v>
       </c>
       <c r="E187" t="n">
-        <v>0.016024</v>
+        <v>0.015567</v>
       </c>
       <c r="F187" t="n">
-        <v>0.00872709677419355</v>
+        <v>0.008594000000000001</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>42267</v>
+        <v>42261</v>
       </c>
       <c r="B188" t="n">
-        <v>48.43666666666667</v>
+        <v>48.87666666666667</v>
       </c>
       <c r="C188" t="n">
-        <v>18.86133333333333</v>
+        <v>18.5766</v>
       </c>
       <c r="D188" t="n">
-        <v>313.8833333333333</v>
+        <v>304.63</v>
       </c>
       <c r="E188" t="n">
-        <v>0.01613866666666667</v>
+        <v>0.01584566666666667</v>
       </c>
       <c r="F188" t="n">
-        <v>0.00851</v>
+        <v>0.008307333333333333</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>42288</v>
+        <v>42282</v>
       </c>
       <c r="B189" t="n">
-        <v>50.79</v>
+        <v>47.69</v>
       </c>
       <c r="C189" t="n">
-        <v>18.4184</v>
+        <v>18.102</v>
       </c>
       <c r="D189" t="n">
-        <v>298.9066666666666</v>
+        <v>302.52</v>
       </c>
       <c r="E189" t="n">
-        <v>0.015983</v>
+        <v>0.01517033333333333</v>
       </c>
       <c r="F189" t="n">
-        <v>0.008162666666666667</v>
+        <v>0.007873333333333333</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>42309</v>
+        <v>42303</v>
       </c>
       <c r="B190" t="n">
-        <v>49.04666666666667</v>
+        <v>44.24333333333333</v>
       </c>
       <c r="C190" t="n">
-        <v>17.99132258064516</v>
+        <v>18.00758064516129</v>
       </c>
       <c r="D190" t="n">
-        <v>298.92</v>
+        <v>284.9433333333333</v>
       </c>
       <c r="E190" t="n">
-        <v>0.015372</v>
+        <v>0.01486466666666667</v>
       </c>
       <c r="F190" t="n">
-        <v>0.007722903225806451</v>
+        <v>0.007393225806451613</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>42330</v>
+        <v>42324</v>
       </c>
       <c r="B191" t="n">
-        <v>44.77333333333333</v>
+        <v>41.48666666666666</v>
       </c>
       <c r="C191" t="n">
-        <v>18.01570967741936</v>
+        <v>17.39809677419355</v>
       </c>
       <c r="D191" t="n">
-        <v>291.7766666666666</v>
+        <v>277.09</v>
       </c>
       <c r="E191" t="n">
-        <v>0.01445966666666667</v>
+        <v>0.015702</v>
       </c>
       <c r="F191" t="n">
-        <v>0.007228387096774193</v>
+        <v>0.007295483870967742</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>42351</v>
+        <v>42345</v>
       </c>
       <c r="B192" t="n">
-        <v>37.92333333333333</v>
+        <v>36.9375</v>
       </c>
       <c r="C192" t="n">
-        <v>16.66670967741936</v>
+        <v>15.20393548387097</v>
       </c>
       <c r="D192" t="n">
-        <v>279</v>
+        <v>282.4433333333333</v>
       </c>
       <c r="E192" t="n">
-        <v>0.01498066666666667</v>
+        <v>0.01563725</v>
       </c>
       <c r="F192" t="n">
-        <v>0.007593548387096773</v>
+        <v>0.008189677419354838</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>42372</v>
+        <v>42366</v>
       </c>
       <c r="B193" t="n">
-        <v>37.235</v>
+        <v>28.68</v>
       </c>
       <c r="C193" t="n">
-        <v>14.64013793103448</v>
+        <v>13.95944827586207</v>
       </c>
       <c r="D193" t="n">
-        <v>279.8033333333333</v>
+        <v>287.2266666666666</v>
       </c>
       <c r="E193" t="n">
-        <v>0.01563475</v>
+        <v>0.01579566666666667</v>
       </c>
       <c r="F193" t="n">
-        <v>0.008083793103448275</v>
+        <v>0.006794827586206896</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>42393</v>
+        <v>42387</v>
       </c>
       <c r="B194" t="n">
-        <v>31.06</v>
+        <v>33.27333333333333</v>
       </c>
       <c r="C194" t="n">
-        <v>13.61910344827586</v>
+        <v>13.03254838709677</v>
       </c>
       <c r="D194" t="n">
-        <v>289.4533333333333</v>
+        <v>290.9666666666667</v>
       </c>
       <c r="E194" t="n">
-        <v>0.015014</v>
+        <v>0.01365066666666667</v>
       </c>
       <c r="F194" t="n">
-        <v>0.006150344827586206</v>
+        <v>0.005164516129032258</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>42414</v>
+        <v>42408</v>
       </c>
       <c r="B195" t="n">
-        <v>33.38</v>
+        <v>35.68</v>
       </c>
       <c r="C195" t="n">
-        <v>12.76541935483871</v>
+        <v>12.23116129032258</v>
       </c>
       <c r="D195" t="n">
-        <v>293.91</v>
+        <v>289.0333333333334</v>
       </c>
       <c r="E195" t="n">
-        <v>0.013869</v>
+        <v>0.01289833333333333</v>
       </c>
       <c r="F195" t="n">
-        <v>0.004755806451612903</v>
+        <v>0.003938387096774193</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>42435</v>
+        <v>42429</v>
       </c>
       <c r="B196" t="n">
-        <v>40.13333333333333</v>
+        <v>41.42666666666667</v>
       </c>
       <c r="C196" t="n">
-        <v>12.14345161290323</v>
+        <v>12.02783870967742</v>
       </c>
       <c r="D196" t="n">
-        <v>287.9533333333333</v>
+        <v>296.6833333333333</v>
       </c>
       <c r="E196" t="n">
-        <v>0.01361633333333333</v>
+        <v>0.01214133333333333</v>
       </c>
       <c r="F196" t="n">
-        <v>0.003969032258064517</v>
+        <v>0.004176774193548387</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>42456</v>
+        <v>42450</v>
       </c>
       <c r="B197" t="n">
-        <v>40.3125</v>
+        <v>42.53333333333333</v>
       </c>
       <c r="C197" t="n">
-        <v>11.97003225806452</v>
+        <v>12.22734482758621</v>
       </c>
       <c r="D197" t="n">
-        <v>290.1833333333333</v>
+        <v>280.24</v>
       </c>
       <c r="E197" t="n">
-        <v>0.0112608</v>
+        <v>0.010107</v>
       </c>
       <c r="F197" t="n">
-        <v>0.004280645161290323</v>
+        <v>0.004746896551724138</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>42477</v>
+        <v>42471</v>
       </c>
       <c r="B198" t="n">
-        <v>42.97333333333333</v>
+        <v>46.59666666666666</v>
       </c>
       <c r="C198" t="n">
-        <v>12.43058620689655</v>
+        <v>12.8701875</v>
       </c>
       <c r="D198" t="n">
-        <v>295.5633333333333</v>
+        <v>288.3</v>
       </c>
       <c r="E198" t="n">
-        <v>0.01030366666666667</v>
+        <v>0.01142066666666667</v>
       </c>
       <c r="F198" t="n">
-        <v>0.005031724137931035</v>
+        <v>0.005436875000000001</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>42498</v>
+        <v>42492</v>
       </c>
       <c r="B199" t="n">
-        <v>44.21</v>
+        <v>48.47333333333334</v>
       </c>
       <c r="C199" t="n">
-        <v>13.18934375</v>
+        <v>13.82765625</v>
       </c>
       <c r="D199" t="n">
-        <v>297.8733333333333</v>
+        <v>300.33</v>
       </c>
       <c r="E199" t="n">
-        <v>0.01034933333333334</v>
+        <v>0.01151866666666667</v>
       </c>
       <c r="F199" t="n">
-        <v>0.0051459375</v>
+        <v>0.0045640625</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>42519</v>
+        <v>42513</v>
       </c>
       <c r="B200" t="n">
-        <v>49.61333333333333</v>
+        <v>50.41333333333333</v>
       </c>
       <c r="C200" t="n">
-        <v>14.1468125</v>
+        <v>14.2928</v>
       </c>
       <c r="D200" t="n">
-        <v>294.0433333333334</v>
+        <v>287.5733333333333</v>
       </c>
       <c r="E200" t="n">
-        <v>0.01125766666666667</v>
+        <v>0.009699666666666667</v>
       </c>
       <c r="F200" t="n">
-        <v>0.004273125</v>
+        <v>0.003466</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>42540</v>
+        <v>42534</v>
       </c>
       <c r="B201" t="n">
-        <v>50.15666666666667</v>
+        <v>50.18333333333334</v>
       </c>
       <c r="C201" t="n">
-        <v>14.32476666666667</v>
+        <v>14.38358620689655</v>
       </c>
       <c r="D201" t="n">
-        <v>287.3033333333333</v>
+        <v>295.0466666666667</v>
       </c>
       <c r="E201" t="n">
-        <v>0.009649</v>
+        <v>0.007558</v>
       </c>
       <c r="F201" t="n">
-        <v>0.003043666666666667</v>
+        <v>0.002217586206896552</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>42561</v>
+        <v>42555</v>
       </c>
       <c r="B202" t="n">
-        <v>46.42</v>
+        <v>45.04333333333333</v>
       </c>
       <c r="C202" t="n">
-        <v>14.40362068965517</v>
+        <v>14.44368965517241</v>
       </c>
       <c r="D202" t="n">
-        <v>283.95</v>
+        <v>288.6</v>
       </c>
       <c r="E202" t="n">
-        <v>0.006464</v>
+        <v>0.005619333333333333</v>
       </c>
       <c r="F202" t="n">
-        <v>0.001838620689655172</v>
+        <v>0.001080689655172414</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>42582</v>
+        <v>42576</v>
       </c>
       <c r="B203" t="n">
-        <v>42.24666666666667</v>
+        <v>47.89</v>
       </c>
       <c r="C203" t="n">
-        <v>14.34981818181818</v>
+        <v>13.59254545454545</v>
       </c>
       <c r="D203" t="n">
-        <v>277.52</v>
+        <v>282.94</v>
       </c>
       <c r="E203" t="n">
-        <v>0.005294666666666666</v>
+        <v>0.005426333333333334</v>
       </c>
       <c r="F203" t="n">
-        <v>0.000783939393939394</v>
+        <v>0.0006015151515151515</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>42603</v>
+        <v>42597</v>
       </c>
       <c r="B204" t="n">
-        <v>49.73333333333333</v>
+        <v>47.36333333333334</v>
       </c>
       <c r="C204" t="n">
-        <v>13.21390909090909</v>
+        <v>13.02993333333333</v>
       </c>
       <c r="D204" t="n">
-        <v>280.8133333333333</v>
+        <v>262.3166666666667</v>
       </c>
       <c r="E204" t="n">
-        <v>0.005640999999999999</v>
+        <v>0.005917333333333333</v>
       </c>
       <c r="F204" t="n">
-        <v>0.0005103030303030303</v>
+        <v>0.0003333333333333333</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>42624</v>
+        <v>42618</v>
       </c>
       <c r="B205" t="n">
-        <v>48.21666666666667</v>
+        <v>46.86333333333334</v>
       </c>
       <c r="C205" t="n">
-        <v>13.65456666666667</v>
+        <v>14.90383333333333</v>
       </c>
       <c r="D205" t="n">
-        <v>257.7433333333333</v>
+        <v>258.5833333333333</v>
       </c>
       <c r="E205" t="n">
-        <v>0.006686666666666667</v>
+        <v>0.005890333333333333</v>
       </c>
       <c r="F205" t="n">
-        <v>0.0002516666666666666</v>
+        <v>8.833333333333333e-05</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>42645</v>
+        <v>42639</v>
       </c>
       <c r="B206" t="n">
-        <v>50.28</v>
+        <v>51.66333333333333</v>
       </c>
       <c r="C206" t="n">
-        <v>15.50748387096774</v>
+        <v>16.60987096774194</v>
       </c>
       <c r="D206" t="n">
-        <v>262.8633333333333</v>
+        <v>273.3833333333333</v>
       </c>
       <c r="E206" t="n">
-        <v>0.005838</v>
+        <v>0.007365666666666666</v>
       </c>
       <c r="F206" t="n">
-        <v>0.0001725806451612903</v>
+        <v>0.001170645161290323</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>42666</v>
+        <v>42660</v>
       </c>
       <c r="B207" t="n">
-        <v>51.56666666666667</v>
+        <v>45.96</v>
       </c>
       <c r="C207" t="n">
-        <v>17.16106451612903</v>
+        <v>17.8754</v>
       </c>
       <c r="D207" t="n">
-        <v>276.5333333333333</v>
+        <v>271.9933333333333</v>
       </c>
       <c r="E207" t="n">
-        <v>0.007114000000000001</v>
+        <v>0.008413333333333333</v>
       </c>
       <c r="F207" t="n">
-        <v>0.001669677419354839</v>
+        <v>0.002624</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>42687</v>
+        <v>42681</v>
       </c>
       <c r="B208" t="n">
-        <v>44.53666666666667</v>
+        <v>47.90666666666667</v>
       </c>
       <c r="C208" t="n">
-        <v>17.97386666666667</v>
+        <v>18.1708</v>
       </c>
       <c r="D208" t="n">
-        <v>271.38</v>
+        <v>265.4233333333333</v>
       </c>
       <c r="E208" t="n">
-        <v>0.010485</v>
+        <v>0.010613</v>
       </c>
       <c r="F208" t="n">
-        <v>0.003072</v>
+        <v>0.003967999999999999</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>42708</v>
+        <v>42702</v>
       </c>
       <c r="B209" t="n">
-        <v>54.78</v>
+        <v>55.01666666666667</v>
       </c>
       <c r="C209" t="n">
-        <v>18.39006666666667</v>
+        <v>19.0098</v>
       </c>
       <c r="D209" t="n">
-        <v>274.3</v>
+        <v>276.68</v>
       </c>
       <c r="E209" t="n">
-        <v>0.01215333333333333</v>
+        <v>0.011563</v>
       </c>
       <c r="F209" t="n">
-        <v>0.004156</v>
+        <v>0.004142</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>42729</v>
+        <v>42723</v>
       </c>
       <c r="B210" t="n">
-        <v>55.625</v>
+        <v>55.66</v>
       </c>
       <c r="C210" t="n">
-        <v>19.31966666666667</v>
+        <v>19.88075</v>
       </c>
       <c r="D210" t="n">
-        <v>281.9166666666667</v>
+        <v>280.51</v>
       </c>
       <c r="E210" t="n">
-        <v>0.011174</v>
+        <v>0.011834</v>
       </c>
       <c r="F210" t="n">
-        <v>0.004135</v>
+        <v>0.00458</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>42750</v>
+        <v>42744</v>
       </c>
       <c r="B211" t="n">
-        <v>55.72333333333334</v>
+        <v>55.32666666666667</v>
       </c>
       <c r="C211" t="n">
-        <v>20.145</v>
+        <v>20.6735</v>
       </c>
       <c r="D211" t="n">
-        <v>285.6733333333333</v>
+        <v>293.9066666666666</v>
       </c>
       <c r="E211" t="n">
-        <v>0.011763</v>
+        <v>0.013358</v>
       </c>
       <c r="F211" t="n">
-        <v>0.00493</v>
+        <v>0.00563</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>42771</v>
+        <v>42765</v>
       </c>
       <c r="B212" t="n">
-        <v>56.08333333333334</v>
+        <v>56.05666666666666</v>
       </c>
       <c r="C212" t="n">
-        <v>20.06096428571428</v>
+        <v>18.13446428571429</v>
       </c>
       <c r="D212" t="n">
-        <v>291.37</v>
+        <v>289.4966666666667</v>
       </c>
       <c r="E212" t="n">
-        <v>0.012508</v>
+        <v>0.01192466666666667</v>
       </c>
       <c r="F212" t="n">
-        <v>0.005510357142857143</v>
+        <v>0.004895357142857143</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>42792</v>
+        <v>42786</v>
       </c>
       <c r="B213" t="n">
-        <v>55.95</v>
+        <v>51.35666666666667</v>
       </c>
       <c r="C213" t="n">
-        <v>17.17121428571429</v>
+        <v>16.47212903225806</v>
       </c>
       <c r="D213" t="n">
-        <v>299.39</v>
+        <v>305.82</v>
       </c>
       <c r="E213" t="n">
-        <v>0.01075633333333333</v>
+        <v>0.01393333333333333</v>
       </c>
       <c r="F213" t="n">
-        <v>0.004587857142857144</v>
+        <v>0.004887096774193549</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>42813</v>
+        <v>42807</v>
       </c>
       <c r="B214" t="n">
-        <v>51.66666666666666</v>
+        <v>53.02333333333333</v>
       </c>
       <c r="C214" t="n">
-        <v>16.22487096774194</v>
+        <v>15.82821428571429</v>
       </c>
       <c r="D214" t="n">
-        <v>305.7966666666667</v>
+        <v>304.7233333333333</v>
       </c>
       <c r="E214" t="n">
-        <v>0.01367266666666667</v>
+        <v>0.012493</v>
       </c>
       <c r="F214" t="n">
-        <v>0.005112903225806452</v>
+        <v>0.005505</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>42834</v>
+        <v>42828</v>
       </c>
       <c r="B215" t="n">
-        <v>55.73333333333333</v>
+        <v>51.72</v>
       </c>
       <c r="C215" t="n">
-        <v>15.92346428571429</v>
+        <v>16.11396428571429</v>
       </c>
       <c r="D215" t="n">
-        <v>307.7066666666667</v>
+        <v>291.7433333333333</v>
       </c>
       <c r="E215" t="n">
-        <v>0.01164433333333333</v>
+        <v>0.01252633333333333</v>
       </c>
       <c r="F215" t="n">
-        <v>0.0055225</v>
+        <v>0.0055575</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>42855</v>
+        <v>42849</v>
       </c>
       <c r="B216" t="n">
-        <v>51.59</v>
+        <v>51.49333333333333</v>
       </c>
       <c r="C216" t="n">
-        <v>16.12824242424242</v>
+        <v>15.75193939393939</v>
       </c>
       <c r="D216" t="n">
-        <v>288.91</v>
+        <v>290.4866666666666</v>
       </c>
       <c r="E216" t="n">
-        <v>0.0119625</v>
+        <v>0.01247366666666667</v>
       </c>
       <c r="F216" t="n">
-        <v>0.00555969696969697</v>
+        <v>0.005487575757575758</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>42876</v>
+        <v>42870</v>
       </c>
       <c r="B217" t="n">
-        <v>53.78333333333333</v>
+        <v>49.63</v>
       </c>
       <c r="C217" t="n">
-        <v>15.56378787878788</v>
+        <v>15.23433333333333</v>
       </c>
       <c r="D217" t="n">
-        <v>292.09</v>
+        <v>299.9666666666667</v>
       </c>
       <c r="E217" t="n">
-        <v>0.01247566666666667</v>
+        <v>0.01146066666666667</v>
       </c>
       <c r="F217" t="n">
-        <v>0.005451515151515152</v>
+        <v>0.005554666666666667</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>42897</v>
+        <v>42891</v>
       </c>
       <c r="B218" t="n">
-        <v>48.24333333333333</v>
+        <v>45.73333333333333</v>
       </c>
       <c r="C218" t="n">
-        <v>15.12816666666667</v>
+        <v>14.91583333333333</v>
       </c>
       <c r="D218" t="n">
-        <v>301.8733333333333</v>
+        <v>301.8333333333333</v>
       </c>
       <c r="E218" t="n">
-        <v>0.011297</v>
+        <v>0.01131666666666667</v>
       </c>
       <c r="F218" t="n">
-        <v>0.005825333333333333</v>
+        <v>0.006366666666666666</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>42918</v>
+        <v>42912</v>
       </c>
       <c r="B219" t="n">
-        <v>49.09333333333333</v>
+        <v>48.58333333333334</v>
       </c>
       <c r="C219" t="n">
-        <v>14.84812903225806</v>
+        <v>14.90503225806452</v>
       </c>
       <c r="D219" t="n">
-        <v>306.49</v>
+        <v>301.48</v>
       </c>
       <c r="E219" t="n">
-        <v>0.01341066666666667</v>
+        <v>0.01315633333333333</v>
       </c>
       <c r="F219" t="n">
-        <v>0.006589677419354839</v>
+        <v>0.006797419354838709</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>42939</v>
+        <v>42933</v>
       </c>
       <c r="B220" t="n">
-        <v>48.42</v>
+        <v>52.38666666666666</v>
       </c>
       <c r="C220" t="n">
-        <v>14.93348387096774</v>
+        <v>15.25341935483871</v>
       </c>
       <c r="D220" t="n">
-        <v>300.4533333333333</v>
+        <v>302.7733333333333</v>
       </c>
       <c r="E220" t="n">
-        <v>0.012286</v>
+        <v>0.01173633333333333</v>
       </c>
       <c r="F220" t="n">
-        <v>0.006901290322580645</v>
+        <v>0.006694838709677419</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>42960</v>
+        <v>42954</v>
       </c>
       <c r="B221" t="n">
-        <v>51.18666666666667</v>
+        <v>52.06333333333333</v>
       </c>
       <c r="C221" t="n">
-        <v>15.58874193548387</v>
+        <v>16.25938709677419</v>
       </c>
       <c r="D221" t="n">
-        <v>304.6133333333333</v>
+        <v>310.41</v>
       </c>
       <c r="E221" t="n">
-        <v>0.01114733333333333</v>
+        <v>0.010994</v>
       </c>
       <c r="F221" t="n">
-        <v>0.006315483870967742</v>
+        <v>0.005556774193548387</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>42981</v>
+        <v>42975</v>
       </c>
       <c r="B222" t="n">
-        <v>52.47666666666667</v>
+        <v>55.52666666666666</v>
       </c>
       <c r="C222" t="n">
-        <v>16.54731034482759</v>
+        <v>16.99675862068966</v>
       </c>
       <c r="D222" t="n">
-        <v>301.7833333333334</v>
+        <v>299.1133333333333</v>
       </c>
       <c r="E222" t="n">
-        <v>0.01125833333333333</v>
+        <v>0.01224066666666667</v>
       </c>
       <c r="F222" t="n">
-        <v>0.005441379310344828</v>
+        <v>0.005914482758620689</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>43002</v>
+        <v>42996</v>
       </c>
       <c r="B223" t="n">
-        <v>58.3</v>
+        <v>55.73333333333333</v>
       </c>
       <c r="C223" t="n">
-        <v>17.22148275862069</v>
+        <v>17.61515625</v>
       </c>
       <c r="D223" t="n">
-        <v>303.6333333333333</v>
+        <v>297.0566666666667</v>
       </c>
       <c r="E223" t="n">
-        <v>0.011963</v>
+        <v>0.012218</v>
       </c>
       <c r="F223" t="n">
-        <v>0.006151034482758621</v>
+        <v>0.006002187500000001</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>43023</v>
+        <v>43017</v>
       </c>
       <c r="B224" t="n">
-        <v>57.60333333333333</v>
+        <v>60.74666666666666</v>
       </c>
       <c r="C224" t="n">
-        <v>17.7965</v>
+        <v>18.1591875</v>
       </c>
       <c r="D224" t="n">
-        <v>292.43</v>
+        <v>291.41</v>
       </c>
       <c r="E224" t="n">
-        <v>0.011448</v>
+        <v>0.01091566666666667</v>
       </c>
       <c r="F224" t="n">
-        <v>0.005755</v>
+        <v>0.005260625</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>43044</v>
+        <v>43038</v>
       </c>
       <c r="B225" t="n">
-        <v>63.53666666666666</v>
+        <v>62.38666666666666</v>
       </c>
       <c r="C225" t="n">
-        <v>18.55983333333333</v>
+        <v>19.53656666666667</v>
       </c>
       <c r="D225" t="n">
-        <v>293.54</v>
+        <v>279.6166666666667</v>
       </c>
       <c r="E225" t="n">
-        <v>0.01029733333333333</v>
+        <v>0.010942</v>
       </c>
       <c r="F225" t="n">
-        <v>0.005176666666666667</v>
+        <v>0.005139333333333333</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>43065</v>
+        <v>43059</v>
       </c>
       <c r="B226" t="n">
-        <v>63.84666666666667</v>
+        <v>64.25999999999999</v>
       </c>
       <c r="C226" t="n">
-        <v>20.02493333333333</v>
+        <v>20.06986206896552</v>
       </c>
       <c r="D226" t="n">
-        <v>264.38</v>
+        <v>273.05</v>
       </c>
       <c r="E226" t="n">
-        <v>0.01093866666666667</v>
+        <v>0.01040133333333333</v>
       </c>
       <c r="F226" t="n">
-        <v>0.005120666666666667</v>
+        <v>0.005282413793103448</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>43086</v>
+        <v>43080</v>
       </c>
       <c r="B227" t="n">
-        <v>63.34999999999999</v>
+        <v>66.72</v>
       </c>
       <c r="C227" t="n">
-        <v>19.90596551724138</v>
+        <v>19.52348484848485</v>
       </c>
       <c r="D227" t="n">
-        <v>265.64</v>
+        <v>279.4566666666666</v>
       </c>
       <c r="E227" t="n">
-        <v>0.01065666666666667</v>
+        <v>0.012081</v>
       </c>
       <c r="F227" t="n">
-        <v>0.005403103448275862</v>
+        <v>0.005782121212121212</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>43107</v>
+        <v>43101</v>
       </c>
       <c r="B228" t="n">
-        <v>67.72666666666667</v>
+        <v>68.89</v>
       </c>
       <c r="C228" t="n">
-        <v>19.16818181818182</v>
+        <v>18.45757575757576</v>
       </c>
       <c r="D228" t="n">
-        <v>274.2166666666666</v>
+        <v>286.5766666666667</v>
       </c>
       <c r="E228" t="n">
-        <v>0.011835</v>
+        <v>0.01244533333333333</v>
       </c>
       <c r="F228" t="n">
-        <v>0.006384545454545454</v>
+        <v>0.007589393939393939</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>43128</v>
+        <v>43122</v>
       </c>
       <c r="B229" t="n">
-        <v>69.81333333333333</v>
+        <v>62.65666666666667</v>
       </c>
       <c r="C229" t="n">
-        <v>18.10227272727273</v>
+        <v>17.71428571428572</v>
       </c>
       <c r="D229" t="n">
-        <v>290.0566666666667</v>
+        <v>298.0233333333334</v>
       </c>
       <c r="E229" t="n">
-        <v>0.01354366666666667</v>
+        <v>0.01414566666666667</v>
       </c>
       <c r="F229" t="n">
-        <v>0.008191818181818182</v>
+        <v>0.008528571428571429</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>43149</v>
+        <v>43143</v>
       </c>
       <c r="B230" t="n">
-        <v>65.39333333333333</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="C230" t="n">
-        <v>17.56428571428572</v>
+        <v>17.46413333333333</v>
       </c>
       <c r="D230" t="n">
-        <v>302.6966666666667</v>
+        <v>301.0933333333334</v>
       </c>
       <c r="E230" t="n">
-        <v>0.01400566666666667</v>
+        <v>0.01332433333333333</v>
       </c>
       <c r="F230" t="n">
-        <v>0.008578571428571428</v>
+        <v>0.008483333333333332</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>43170</v>
+        <v>43164</v>
       </c>
       <c r="B231" t="n">
-        <v>65.13</v>
+        <v>70.23</v>
       </c>
       <c r="C231" t="n">
-        <v>17.66386666666667</v>
+        <v>18.06333333333333</v>
       </c>
       <c r="D231" t="n">
-        <v>290.3766666666667</v>
+        <v>290.2466666666667</v>
       </c>
       <c r="E231" t="n">
-        <v>0.01346</v>
+        <v>0.01326233333333333</v>
       </c>
       <c r="F231" t="n">
-        <v>0.008191666666666667</v>
+        <v>0.007608333333333333</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>43191</v>
+        <v>43185</v>
       </c>
       <c r="B232" t="n">
-        <v>68.2975</v>
+        <v>71.80666666666667</v>
       </c>
       <c r="C232" t="n">
-        <v>18.36070967741935</v>
+        <v>19.44367741935484</v>
       </c>
       <c r="D232" t="n">
-        <v>291.1933333333333</v>
+        <v>294.38</v>
       </c>
       <c r="E232" t="n">
-        <v>0.0130736</v>
+        <v>0.01316333333333333</v>
       </c>
       <c r="F232" t="n">
-        <v>0.007418064516129033</v>
+        <v>0.007544516129032258</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>43212</v>
+        <v>43206</v>
       </c>
       <c r="B233" t="n">
-        <v>74.49333333333333</v>
+        <v>75.73666666666666</v>
       </c>
       <c r="C233" t="n">
-        <v>19.98516129032258</v>
+        <v>20.99032258064516</v>
       </c>
       <c r="D233" t="n">
-        <v>299.17</v>
+        <v>293.3033333333333</v>
       </c>
       <c r="E233" t="n">
-        <v>0.01397766666666667</v>
+        <v>0.01316933333333333</v>
       </c>
       <c r="F233" t="n">
-        <v>0.007607741935483871</v>
+        <v>0.007561935483870968</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>43233</v>
+        <v>43227</v>
       </c>
       <c r="B234" t="n">
-        <v>77.86</v>
+        <v>75.67999999999999</v>
       </c>
       <c r="C234" t="n">
-        <v>21.44103225806452</v>
+        <v>22.34245161290323</v>
       </c>
       <c r="D234" t="n">
-        <v>294.3166666666667</v>
+        <v>289.41</v>
       </c>
       <c r="E234" t="n">
-        <v>0.01383666666666667</v>
+        <v>0.01292533333333333</v>
       </c>
       <c r="F234" t="n">
-        <v>0.007424193548387097</v>
+        <v>0.007148709677419355</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
-        <v>43254</v>
+        <v>43248</v>
       </c>
       <c r="B235" t="n">
-        <v>75.79000000000001</v>
+        <v>74.70666666666666</v>
       </c>
       <c r="C235" t="n">
-        <v>22.52448275862069</v>
+        <v>22.17206896551724</v>
       </c>
       <c r="D235" t="n">
-        <v>289.4733333333334</v>
+        <v>284.4633333333333</v>
       </c>
       <c r="E235" t="n">
-        <v>0.01376166666666667</v>
+        <v>0.01357033333333333</v>
       </c>
       <c r="F235" t="n">
-        <v>0.007059655172413793</v>
+        <v>0.007011379310344827</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
-        <v>43275</v>
+        <v>43269</v>
       </c>
       <c r="B236" t="n">
-        <v>75.00333333333333</v>
+        <v>77.75</v>
       </c>
       <c r="C236" t="n">
-        <v>21.99586206896552</v>
+        <v>21.93834375</v>
       </c>
       <c r="D236" t="n">
-        <v>288.8033333333333</v>
+        <v>282.4933333333333</v>
       </c>
       <c r="E236" t="n">
-        <v>0.01292233333333333</v>
+        <v>0.01291233333333333</v>
       </c>
       <c r="F236" t="n">
-        <v>0.006987241379310344</v>
+        <v>0.00716125</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>43296</v>
+        <v>43290</v>
       </c>
       <c r="B237" t="n">
-        <v>73.00333333333333</v>
+        <v>74.74333333333334</v>
       </c>
       <c r="C237" t="n">
-        <v>21.9915</v>
+        <v>22.0978125</v>
       </c>
       <c r="D237" t="n">
-        <v>283.84</v>
+        <v>275.5166666666667</v>
       </c>
       <c r="E237" t="n">
-        <v>0.012708</v>
+        <v>0.013165</v>
       </c>
       <c r="F237" t="n">
-        <v>0.007310000000000001</v>
+        <v>0.007607500000000001</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
-        <v>43317</v>
+        <v>43311</v>
       </c>
       <c r="B238" t="n">
-        <v>73.56999999999999</v>
+        <v>72.08333333333333</v>
       </c>
       <c r="C238" t="n">
-        <v>22.71364516129032</v>
+        <v>24.39545161290323</v>
       </c>
       <c r="D238" t="n">
-        <v>277.4733333333334</v>
+        <v>282.8433333333334</v>
       </c>
       <c r="E238" t="n">
-        <v>0.01273</v>
+        <v>0.011835</v>
       </c>
       <c r="F238" t="n">
-        <v>0.007537096774193549</v>
+        <v>0.007220967741935484</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
-        <v>43338</v>
+        <v>43332</v>
       </c>
       <c r="B239" t="n">
-        <v>76.08</v>
+        <v>77.19</v>
       </c>
       <c r="C239" t="n">
-        <v>25.23635483870968</v>
+        <v>26.31657142857143</v>
       </c>
       <c r="D239" t="n">
         <v>289.96</v>
       </c>
       <c r="E239" t="n">
-        <v>0.01259766666666667</v>
+        <v>0.013933</v>
       </c>
       <c r="F239" t="n">
-        <v>0.007062903225806451</v>
+        <v>0.007329285714285714</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
-        <v>43359</v>
+        <v>43353</v>
       </c>
       <c r="B240" t="n">
-        <v>78.06333333333333</v>
+        <v>84.22666666666667</v>
       </c>
       <c r="C240" t="n">
-        <v>26.68957142857143</v>
+        <v>27.14742424242424</v>
       </c>
       <c r="D240" t="n">
-        <v>287.0933333333333</v>
+        <v>289.0033333333333</v>
       </c>
       <c r="E240" t="n">
-        <v>0.01434666666666667</v>
+        <v>0.01437766666666667</v>
       </c>
       <c r="F240" t="n">
-        <v>0.007624285714285715</v>
+        <v>0.008113636363636365</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
-        <v>43380</v>
+        <v>43374</v>
       </c>
       <c r="B241" t="n">
-        <v>83.99333333333333</v>
+        <v>79.81333333333333</v>
       </c>
       <c r="C241" t="n">
-        <v>26.51190909090909</v>
+        <v>25.24087878787878</v>
       </c>
       <c r="D241" t="n">
-        <v>282.5666666666667</v>
+        <v>294.1866666666667</v>
       </c>
       <c r="E241" t="n">
-        <v>0.01501233333333333</v>
+        <v>0.014102</v>
       </c>
       <c r="F241" t="n">
-        <v>0.008056363636363636</v>
+        <v>0.007941818181818182</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
-        <v>43401</v>
+        <v>43395</v>
       </c>
       <c r="B242" t="n">
-        <v>77.43333333333334</v>
+        <v>70.14</v>
       </c>
       <c r="C242" t="n">
-        <v>24.60536363636363</v>
+        <v>24.46426666666667</v>
       </c>
       <c r="D242" t="n">
-        <v>299.3366666666666</v>
+        <v>306.86</v>
       </c>
       <c r="E242" t="n">
-        <v>0.01369133333333333</v>
+        <v>0.014055</v>
       </c>
       <c r="F242" t="n">
-        <v>0.007884545454545455</v>
+        <v>0.007724333333333334</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
-        <v>43422</v>
+        <v>43416</v>
       </c>
       <c r="B243" t="n">
-        <v>66.78</v>
+        <v>60.69666666666667</v>
       </c>
       <c r="C243" t="n">
-        <v>24.5478</v>
+        <v>24.51622580645161</v>
       </c>
       <c r="D243" t="n">
-        <v>307.4533333333333</v>
+        <v>309.1</v>
       </c>
       <c r="E243" t="n">
-        <v>0.01440933333333333</v>
+        <v>0.01434866666666667</v>
       </c>
       <c r="F243" t="n">
-        <v>0.007638000000000001</v>
+        <v>0.007468709677419355</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
-        <v>43443</v>
+        <v>43437</v>
       </c>
       <c r="B244" t="n">
-        <v>60.53666666666667</v>
+        <v>51.58666666666667</v>
       </c>
       <c r="C244" t="n">
-        <v>23.90451612903226</v>
+        <v>22.68109677419355</v>
       </c>
       <c r="D244" t="n">
-        <v>308.4433333333333</v>
+        <v>314.55</v>
       </c>
       <c r="E244" t="n">
-        <v>0.01429333333333333</v>
+        <v>0.01413066666666667</v>
       </c>
       <c r="F244" t="n">
-        <v>0.007394193548387096</v>
+        <v>0.00724516129032258</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
-        <v>43464</v>
+        <v>43458</v>
       </c>
       <c r="B245" t="n">
-        <v>53.26666666666667</v>
+        <v>59.48666666666666</v>
       </c>
       <c r="C245" t="n">
-        <v>22.06938709677419</v>
+        <v>21.08877419354839</v>
       </c>
       <c r="D245" t="n">
-        <v>317.81</v>
+        <v>316.0266666666667</v>
       </c>
       <c r="E245" t="n">
-        <v>0.01410266666666667</v>
+        <v>0.013941</v>
       </c>
       <c r="F245" t="n">
-        <v>0.007170645161290322</v>
+        <v>0.006694516129032258</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
-        <v>43485</v>
+        <v>43479</v>
       </c>
       <c r="B246" t="n">
-        <v>62.72666666666667</v>
+        <v>62.59</v>
       </c>
       <c r="C246" t="n">
-        <v>20.6078064516129</v>
+        <v>19.63364285714286</v>
       </c>
       <c r="D246" t="n">
-        <v>315.9233333333333</v>
+        <v>312.1733333333333</v>
       </c>
       <c r="E246" t="n">
-        <v>0.014009</v>
+        <v>0.012601</v>
       </c>
       <c r="F246" t="n">
-        <v>0.006443870967741935</v>
+        <v>0.006071428571428571</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
-        <v>43506</v>
+        <v>43500</v>
       </c>
       <c r="B247" t="n">
-        <v>61.70666666666666</v>
+        <v>65.54666666666667</v>
       </c>
       <c r="C247" t="n">
-        <v>19.12414285714286</v>
+        <v>18.10514285714286</v>
       </c>
       <c r="D247" t="n">
-        <v>312.56</v>
+        <v>312.8566666666667</v>
       </c>
       <c r="E247" t="n">
-        <v>0.01146533333333333</v>
+        <v>0.01143066666666667</v>
       </c>
       <c r="F247" t="n">
-        <v>0.006121428571428571</v>
+        <v>0.006221428571428571</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
-        <v>43527</v>
+        <v>43521</v>
       </c>
       <c r="B248" t="n">
-        <v>65.47</v>
+        <v>67.41333333333334</v>
       </c>
       <c r="C248" t="n">
-        <v>17.44148275862069</v>
+        <v>15.70306896551724</v>
       </c>
       <c r="D248" t="n">
-        <v>313.0566666666667</v>
+        <v>313.32</v>
       </c>
       <c r="E248" t="n">
-        <v>0.01194833333333333</v>
+        <v>0.01074533333333333</v>
       </c>
       <c r="F248" t="n">
-        <v>0.006004827586206897</v>
+        <v>0.004860689655172414</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
-        <v>43548</v>
+        <v>43542</v>
       </c>
       <c r="B249" t="n">
-        <v>67.14999999999999</v>
+        <v>70.84666666666666</v>
       </c>
       <c r="C249" t="n">
-        <v>14.83386206896552</v>
+        <v>14.2625</v>
       </c>
       <c r="D249" t="n">
-        <v>321.2566666666667</v>
+        <v>321.6533333333333</v>
       </c>
       <c r="E249" t="n">
-        <v>0.009765000000000001</v>
+        <v>0.009608333333333333</v>
       </c>
       <c r="F249" t="n">
-        <v>0.004288620689655172</v>
+        <v>0.0039671875</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
-        <v>43569</v>
+        <v>43563</v>
       </c>
       <c r="B250" t="n">
-        <v>71.30333333333334</v>
+        <v>72.07666666666667</v>
       </c>
       <c r="C250" t="n">
-        <v>14.301</v>
+        <v>14.378</v>
       </c>
       <c r="D250" t="n">
-        <v>329.0433333333334</v>
+        <v>323.0133333333333</v>
       </c>
       <c r="E250" t="n">
-        <v>0.009862666666666667</v>
+        <v>0.008746333333333333</v>
       </c>
       <c r="F250" t="n">
-        <v>0.004035</v>
+        <v>0.004170625</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
-        <v>43590</v>
+        <v>43584</v>
       </c>
       <c r="B251" t="n">
-        <v>71.11</v>
+        <v>72.05</v>
       </c>
       <c r="C251" t="n">
-        <v>13.87545161290323</v>
+        <v>12.43751612903226</v>
       </c>
       <c r="D251" t="n">
-        <v>324.13</v>
+        <v>316.2766666666666</v>
       </c>
       <c r="E251" t="n">
-        <v>0.008728000000000001</v>
+        <v>0.008503</v>
       </c>
       <c r="F251" t="n">
-        <v>0.003899677419354839</v>
+        <v>0.003086774193548387</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
-        <v>43611</v>
+        <v>43605</v>
       </c>
       <c r="B252" t="n">
-        <v>69.63666666666667</v>
+        <v>62.62333333333333</v>
       </c>
       <c r="C252" t="n">
-        <v>11.71854838709677</v>
+        <v>10.85528571428572</v>
       </c>
       <c r="D252" t="n">
-        <v>317.4733333333333</v>
+        <v>325.9033333333334</v>
       </c>
       <c r="E252" t="n">
-        <v>0.008495000000000001</v>
+        <v>0.007746</v>
       </c>
       <c r="F252" t="n">
-        <v>0.002680322580645161</v>
+        <v>0.001833928571428571</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
-        <v>43632</v>
+        <v>43626</v>
       </c>
       <c r="B253" t="n">
-        <v>61.29666666666667</v>
+        <v>65.55666666666667</v>
       </c>
       <c r="C253" t="n">
-        <v>10.58328571428572</v>
+        <v>10.17039393939394</v>
       </c>
       <c r="D253" t="n">
-        <v>333.4033333333333</v>
+        <v>331.7733333333333</v>
       </c>
       <c r="E253" t="n">
-        <v>0.007402000000000001</v>
+        <v>0.005529</v>
       </c>
       <c r="F253" t="n">
-        <v>0.001401428571428571</v>
+        <v>0.0005612121212121212</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n">
-        <v>43653</v>
+        <v>43647</v>
       </c>
       <c r="B254" t="n">
-        <v>64.15000000000001</v>
+        <v>62.99666666666666</v>
       </c>
       <c r="C254" t="n">
-        <v>10.35727272727273</v>
+        <v>10.7310303030303</v>
       </c>
       <c r="D254" t="n">
-        <v>339.67</v>
+        <v>338.0866666666666</v>
       </c>
       <c r="E254" t="n">
-        <v>0.005183666666666666</v>
+        <v>0.004748666666666667</v>
       </c>
       <c r="F254" t="n">
-        <v>0.0002154545454545455</v>
+        <v>-0.0004760606060606059</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n">
-        <v>43674</v>
+        <v>43668</v>
       </c>
       <c r="B255" t="n">
-        <v>63.62666666666667</v>
+        <v>58.55666666666666</v>
       </c>
       <c r="C255" t="n">
-        <v>10.91790909090909</v>
+        <v>11.65763333333333</v>
       </c>
       <c r="D255" t="n">
-        <v>342.4166666666666</v>
+        <v>341.6866666666667</v>
       </c>
       <c r="E255" t="n">
-        <v>0.003579333333333333</v>
+        <v>0.002659</v>
       </c>
       <c r="F255" t="n">
-        <v>-0.0008218181818181818</v>
+        <v>-0.001993</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
-        <v>43695</v>
+        <v>43689</v>
       </c>
       <c r="B256" t="n">
-        <v>59.37333333333333</v>
+        <v>59.25</v>
       </c>
       <c r="C256" t="n">
-        <v>12.0774</v>
+        <v>13.02893548387097</v>
       </c>
       <c r="D256" t="n">
-        <v>341.9466666666667</v>
+        <v>342.4166666666667</v>
       </c>
       <c r="E256" t="n">
-        <v>0.002136666666666667</v>
+        <v>0.001826</v>
       </c>
       <c r="F256" t="n">
-        <v>-0.002644</v>
+        <v>-0.003681935483870967</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n">
-        <v>43716</v>
+        <v>43710</v>
       </c>
       <c r="B257" t="n">
-        <v>62.24</v>
+        <v>64.60666666666667</v>
       </c>
       <c r="C257" t="n">
-        <v>13.84070967741935</v>
+        <v>15.46425806451613</v>
       </c>
       <c r="D257" t="n">
-        <v>343.4233333333333</v>
+        <v>340.88</v>
       </c>
       <c r="E257" t="n">
-        <v>0.003155666666666666</v>
+        <v>0.003577333333333333</v>
       </c>
       <c r="F257" t="n">
-        <v>-0.003408709677419355</v>
+        <v>-0.002862258064516129</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
-        <v>43737</v>
+        <v>43731</v>
       </c>
       <c r="B258" t="n">
-        <v>61.15666666666667</v>
+        <v>59.73666666666666</v>
       </c>
       <c r="C258" t="n">
-        <v>16.27603225806451</v>
+        <v>16.28338709677419</v>
       </c>
       <c r="D258" t="n">
-        <v>355.5266666666666</v>
+        <v>357.51</v>
       </c>
       <c r="E258" t="n">
-        <v>0.003400333333333333</v>
+        <v>0.004267333333333333</v>
       </c>
       <c r="F258" t="n">
-        <v>-0.002589032258064516</v>
+        <v>-0.00177</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n">
-        <v>43758</v>
+        <v>43752</v>
       </c>
       <c r="B259" t="n">
-        <v>59.11333333333334</v>
+        <v>61.98333333333333</v>
       </c>
       <c r="C259" t="n">
-        <v>16.22490322580645</v>
+        <v>16.15337931034483</v>
       </c>
       <c r="D259" t="n">
-        <v>356.2666666666667</v>
+        <v>384.1266666666667</v>
       </c>
       <c r="E259" t="n">
-        <v>0.005004666666666667</v>
+        <v>0.004251</v>
       </c>
       <c r="F259" t="n">
-        <v>-0.00135</v>
+        <v>-0.0006393103448275862</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n">
-        <v>43779</v>
+        <v>43773</v>
       </c>
       <c r="B260" t="n">
-        <v>62.29</v>
+        <v>63.56333333333333</v>
       </c>
       <c r="C260" t="n">
-        <v>16.20093103448276</v>
+        <v>16.29603448275862</v>
       </c>
       <c r="D260" t="n">
-        <v>385.21</v>
+        <v>402.1966666666667</v>
       </c>
       <c r="E260" t="n">
-        <v>0.005149666666666667</v>
+        <v>0.00491</v>
       </c>
       <c r="F260" t="n">
-        <v>-0.0005210344827586207</v>
+        <v>-0.0002844827586206896</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n">
-        <v>43800</v>
+        <v>43794</v>
       </c>
       <c r="B261" t="n">
-        <v>61.42333333333333</v>
+        <v>65.3</v>
       </c>
       <c r="C261" t="n">
-        <v>16.0625625</v>
+        <v>14.1905</v>
       </c>
       <c r="D261" t="n">
-        <v>413.2866666666667</v>
+        <v>384.8633333333333</v>
       </c>
       <c r="E261" t="n">
-        <v>0.005360666666666667</v>
+        <v>0.005252000000000001</v>
       </c>
       <c r="F261" t="n">
-        <v>-0.00010625</v>
+        <v>0.00055</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n">
-        <v>43821</v>
+        <v>43815</v>
       </c>
       <c r="B262" t="n">
-        <v>66.30666666666667</v>
+        <v>68.80666666666666</v>
       </c>
       <c r="C262" t="n">
-        <v>13.25446875</v>
+        <v>11.68067741935484</v>
       </c>
       <c r="D262" t="n">
-        <v>290.25</v>
+        <v>308.41</v>
       </c>
       <c r="E262" t="n">
-        <v>0.00543</v>
+        <v>0.004964333333333334</v>
       </c>
       <c r="F262" t="n">
-        <v>0.0008781250000000001</v>
+        <v>0.0008596774193548387</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n">
-        <v>43842</v>
+        <v>43836</v>
       </c>
       <c r="B263" t="n">
-        <v>64.46000000000001</v>
+        <v>59.77666666666666</v>
       </c>
       <c r="C263" t="n">
-        <v>11.16222580645161</v>
+        <v>10.12532258064516</v>
       </c>
       <c r="D263" t="n">
-        <v>297.01</v>
+        <v>302.4133333333334</v>
       </c>
       <c r="E263" t="n">
-        <v>0.005753333333333333</v>
+        <v>0.003802666666666666</v>
       </c>
       <c r="F263" t="n">
-        <v>0.0002432258064516129</v>
+        <v>-0.0009896774193548386</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n">
-        <v>43863</v>
+        <v>43857</v>
       </c>
       <c r="B264" t="n">
-        <v>55.68666666666667</v>
+        <v>57.55333333333333</v>
       </c>
       <c r="C264" t="n">
-        <v>9.692071428571429</v>
+        <v>9.251571428571429</v>
       </c>
       <c r="D264" t="n">
-        <v>312.41</v>
+        <v>315.0666666666667</v>
       </c>
       <c r="E264" t="n">
-        <v>0.003231666666666667</v>
+        <v>0.003469333333333333</v>
       </c>
       <c r="F264" t="n">
-        <v>-0.001512142857142857</v>
+        <v>-0.002087142857142857</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="n">
-        <v>43884</v>
+        <v>43878</v>
       </c>
       <c r="B265" t="n">
-        <v>57.03333333333333</v>
+        <v>37.99666666666667</v>
       </c>
       <c r="C265" t="n">
-        <v>9.031321428571429</v>
+        <v>8.319375000000001</v>
       </c>
       <c r="D265" t="n">
-        <v>313.8666666666667</v>
+        <v>339.8033333333333</v>
       </c>
       <c r="E265" t="n">
-        <v>0.002994333333333333</v>
+        <v>0.003203</v>
       </c>
       <c r="F265" t="n">
-        <v>-0.002374642857142857</v>
+        <v>-0.00169125</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n">
-        <v>43905</v>
+        <v>43899</v>
       </c>
       <c r="B266" t="n">
-        <v>31.31666666666667</v>
+        <v>23.48333333333333</v>
       </c>
       <c r="C266" t="n">
-        <v>7.888</v>
+        <v>7.02525</v>
       </c>
       <c r="D266" t="n">
-        <v>348.83</v>
+        <v>351.8</v>
       </c>
       <c r="E266" t="n">
-        <v>0.008252000000000001</v>
+        <v>0.01253733333333333</v>
       </c>
       <c r="F266" t="n">
-        <v>-0.001</v>
+        <v>0.0003825</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n">
-        <v>43926</v>
+        <v>43920</v>
       </c>
       <c r="B267" t="n">
-        <v>33.40333333333333</v>
+        <v>26.40666666666667</v>
       </c>
       <c r="C267" t="n">
-        <v>6.7885</v>
+        <v>6.4707</v>
       </c>
       <c r="D267" t="n">
-        <v>347.9366666666667</v>
+        <v>353.7666666666667</v>
       </c>
       <c r="E267" t="n">
-        <v>0.01323366666666667</v>
+        <v>0.010108</v>
       </c>
       <c r="F267" t="n">
-        <v>0.0003366666666666666</v>
+        <v>-0.0003446666666666666</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n">
-        <v>43947</v>
+        <v>43941</v>
       </c>
       <c r="B268" t="n">
-        <v>20.47333333333333</v>
+        <v>30.07666666666666</v>
       </c>
       <c r="C268" t="n">
-        <v>6.3118</v>
+        <v>5.587896551724138</v>
       </c>
       <c r="D268" t="n">
-        <v>366.6733333333333</v>
+        <v>358.86</v>
       </c>
       <c r="E268" t="n">
-        <v>0.008635666666666666</v>
+        <v>0.007742333333333334</v>
       </c>
       <c r="F268" t="n">
-        <v>-0.0006853333333333334</v>
+        <v>-0.0008317241379310345</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n">
-        <v>43968</v>
+        <v>43962</v>
       </c>
       <c r="B269" t="n">
-        <v>34.04</v>
+        <v>37.32333333333333</v>
       </c>
       <c r="C269" t="n">
-        <v>5.144724137931035</v>
+        <v>4.496125</v>
       </c>
       <c r="D269" t="n">
-        <v>359.15</v>
+        <v>355.4766666666667</v>
       </c>
       <c r="E269" t="n">
-        <v>0.008710333333333334</v>
+        <v>0.007699333333333333</v>
       </c>
       <c r="F269" t="n">
-        <v>-0.0007979310344827585</v>
+        <v>-0.0007943749999999999</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n">
-        <v>43989</v>
+        <v>43983</v>
       </c>
       <c r="B270" t="n">
-        <v>41.3</v>
+        <v>42.78333333333333</v>
       </c>
       <c r="C270" t="n">
-        <v>4.8850625</v>
+        <v>5.6629375</v>
       </c>
       <c r="D270" t="n">
-        <v>349.47</v>
+        <v>346.1266666666667</v>
       </c>
       <c r="E270" t="n">
-        <v>0.005714333333333333</v>
+        <v>0.005242333333333333</v>
       </c>
       <c r="F270" t="n">
-        <v>-0.0009846874999999999</v>
+        <v>-0.0013653125</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="n">
-        <v>44010</v>
+        <v>44004</v>
       </c>
       <c r="B271" t="n">
-        <v>41.48</v>
+        <v>42.89333333333333</v>
       </c>
       <c r="C271" t="n">
-        <v>6.051875000000001</v>
+        <v>6.108806451612903</v>
       </c>
       <c r="D271" t="n">
-        <v>339.23</v>
+        <v>354.3</v>
       </c>
       <c r="E271" t="n">
-        <v>0.005323666666666668</v>
+        <v>0.005683333333333334</v>
       </c>
       <c r="F271" t="n">
-        <v>-0.001555625</v>
+        <v>-0.001803548387096774</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n">
-        <v>44031</v>
+        <v>44025</v>
       </c>
       <c r="B272" t="n">
-        <v>43.23333333333333</v>
+        <v>43.86666666666667</v>
       </c>
       <c r="C272" t="n">
-        <v>6.077193548387097</v>
+        <v>6.359516129032258</v>
       </c>
       <c r="D272" t="n">
-        <v>364.04</v>
+        <v>355.1633333333334</v>
       </c>
       <c r="E272" t="n">
-        <v>0.004770333333333334</v>
+        <v>0.003734</v>
       </c>
       <c r="F272" t="n">
-        <v>-0.001916451612903226</v>
+        <v>-0.002039032258064516</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n">
-        <v>44052</v>
+        <v>44046</v>
       </c>
       <c r="B273" t="n">
-        <v>44.79333333333334</v>
+        <v>44.87</v>
       </c>
       <c r="C273" t="n">
-        <v>7.537322580645162</v>
+        <v>9.892935483870968</v>
       </c>
       <c r="D273" t="n">
-        <v>341.9733333333334</v>
+        <v>374.46</v>
       </c>
       <c r="E273" t="n">
-        <v>0.003442666666666667</v>
+        <v>0.003201666666666666</v>
       </c>
       <c r="F273" t="n">
-        <v>-0.001790645161290322</v>
+        <v>-0.001293870967741936</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n">
-        <v>44073</v>
+        <v>44067</v>
       </c>
       <c r="B274" t="n">
-        <v>45.20333333333333</v>
+        <v>39.68333333333333</v>
       </c>
       <c r="C274" t="n">
-        <v>11.07074193548387</v>
+        <v>12.12603333333333</v>
       </c>
       <c r="D274" t="n">
-        <v>374.82</v>
+        <v>368.5533333333333</v>
       </c>
       <c r="E274" t="n">
-        <v>0.004024666666666667</v>
+        <v>0.003331666666666667</v>
       </c>
       <c r="F274" t="n">
-        <v>-0.001045483870967742</v>
+        <v>-0.001434666666666667</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n">
-        <v>44094</v>
+        <v>44088</v>
       </c>
       <c r="B275" t="n">
-        <v>42.01</v>
+        <v>40.61666666666667</v>
       </c>
       <c r="C275" t="n">
-        <v>12.60366666666667</v>
+        <v>13.38933333333333</v>
       </c>
       <c r="D275" t="n">
-        <v>369.52</v>
+        <v>387.04</v>
       </c>
       <c r="E275" t="n">
-        <v>0.003001333333333333</v>
+        <v>0.003055666666666667</v>
       </c>
       <c r="F275" t="n">
-        <v>-0.001663333333333333</v>
+        <v>-0.002182</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n">
-        <v>44115</v>
+        <v>44109</v>
       </c>
       <c r="B276" t="n">
-        <v>42.09666666666666</v>
+        <v>40.89666666666667</v>
       </c>
       <c r="C276" t="n">
-        <v>13.57016666666667</v>
+        <v>13.93183333333333</v>
       </c>
       <c r="D276" t="n">
-        <v>395.6366666666667</v>
+        <v>393.8733333333333</v>
       </c>
       <c r="E276" t="n">
-        <v>0.002443666666666666</v>
+        <v>0.002086</v>
       </c>
       <c r="F276" t="n">
-        <v>-0.002518</v>
+        <v>-0.00319</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n">
-        <v>44136</v>
+        <v>44130</v>
       </c>
       <c r="B277" t="n">
-        <v>38.46666666666667</v>
+        <v>43.47333333333334</v>
       </c>
       <c r="C277" t="n">
-        <v>14.13048387096774</v>
+        <v>14.61687096774194</v>
       </c>
       <c r="D277" t="n">
-        <v>385.38</v>
+        <v>375.3733333333333</v>
       </c>
       <c r="E277" t="n">
-        <v>0.001825</v>
+        <v>0.001583333333333334</v>
       </c>
       <c r="F277" t="n">
-        <v>-0.003459677419354839</v>
+        <v>-0.00366741935483871</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n">
-        <v>44157</v>
+        <v>44151</v>
       </c>
       <c r="B278" t="n">
-        <v>45.69333333333334</v>
+        <v>48.94333333333334</v>
       </c>
       <c r="C278" t="n">
-        <v>14.86006451612903</v>
+        <v>15.90929032258065</v>
       </c>
       <c r="D278" t="n">
-        <v>373.8766666666667</v>
+        <v>351.31</v>
       </c>
       <c r="E278" t="n">
-        <v>0.001209666666666667</v>
+        <v>0.001334333333333333</v>
       </c>
       <c r="F278" t="n">
-        <v>-0.003771290322580645</v>
+        <v>-0.003920967741935484</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n">
-        <v>44178</v>
+        <v>44172</v>
       </c>
       <c r="B279" t="n">
-        <v>50.18333333333333</v>
+        <v>50.9675</v>
       </c>
       <c r="C279" t="n">
-        <v>16.80912903225806</v>
+        <v>18.6088064516129</v>
       </c>
       <c r="D279" t="n">
-        <v>366.3366666666666</v>
+        <v>375.57</v>
       </c>
       <c r="E279" t="n">
-        <v>0.0008863333333333333</v>
+        <v>0.0016925</v>
       </c>
       <c r="F279" t="n">
-        <v>-0.003957096774193549</v>
+        <v>-0.004029354838709678</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n">
-        <v>44199</v>
+        <v>44193</v>
       </c>
       <c r="B280" t="n">
-        <v>51.2675</v>
+        <v>54.86666666666667</v>
       </c>
       <c r="C280" t="n">
-        <v>19.195</v>
+        <v>19.531</v>
       </c>
       <c r="D280" t="n">
-        <v>380.25</v>
+        <v>389.62</v>
       </c>
       <c r="E280" t="n">
-        <v>0.001294</v>
+        <v>0.001408</v>
       </c>
       <c r="F280" t="n">
-        <v>-0.00399</v>
+        <v>-0.00371</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="n">
-        <v>44220</v>
+        <v>44214</v>
       </c>
       <c r="B281" t="n">
-        <v>55.72333333333334</v>
+        <v>60.15333333333334</v>
       </c>
       <c r="C281" t="n">
-        <v>19.699</v>
+        <v>18.49310714285714</v>
       </c>
       <c r="D281" t="n">
-        <v>389.75</v>
+        <v>383.29</v>
       </c>
       <c r="E281" t="n">
-        <v>0.001398666666666667</v>
+        <v>0.002125333333333334</v>
       </c>
       <c r="F281" t="n">
-        <v>-0.00357</v>
+        <v>-0.002624642857142857</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n">
-        <v>44241</v>
+        <v>44235</v>
       </c>
       <c r="B282" t="n">
-        <v>63.01</v>
+        <v>64.50333333333333</v>
       </c>
       <c r="C282" t="n">
-        <v>17.46185714285714</v>
+        <v>15.894</v>
       </c>
       <c r="D282" t="n">
-        <v>380.27</v>
+        <v>387.0466666666667</v>
       </c>
       <c r="E282" t="n">
-        <v>0.002479666666666667</v>
+        <v>0.003493333333333333</v>
       </c>
       <c r="F282" t="n">
-        <v>-0.001967142857142857</v>
+        <v>-0.0008315151515151516</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="n">
-        <v>44262</v>
+        <v>44256</v>
       </c>
       <c r="B283" t="n">
-        <v>68.61333333333333</v>
+        <v>64.59</v>
       </c>
       <c r="C283" t="n">
-        <v>16.594</v>
+        <v>17.994</v>
       </c>
       <c r="D283" t="n">
-        <v>378.58</v>
+        <v>386.0266666666666</v>
       </c>
       <c r="E283" t="n">
-        <v>0.003527333333333334</v>
+        <v>0.003452666666666667</v>
       </c>
       <c r="F283" t="n">
-        <v>-0.0008018181818181819</v>
+        <v>-0.0007424242424242425</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n">
-        <v>44283</v>
+        <v>44277</v>
       </c>
       <c r="B284" t="n">
-        <v>64.84333333333333</v>
+        <v>63.17</v>
       </c>
       <c r="C284" t="n">
-        <v>18.694</v>
+        <v>20.56736666666666</v>
       </c>
       <c r="D284" t="n">
-        <v>376.6433333333333</v>
+        <v>381.975</v>
       </c>
       <c r="E284" t="n">
-        <v>0.003492666666666666</v>
+        <v>0.003639666666666666</v>
       </c>
       <c r="F284" t="n">
-        <v>-0.0007127272727272729</v>
+        <v>-0.000392</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="n">
-        <v>44304</v>
+        <v>44298</v>
       </c>
       <c r="B285" t="n">
-        <v>66.95666666666666</v>
+        <v>67.45666666666666</v>
       </c>
       <c r="C285" t="n">
-        <v>21.5686</v>
+        <v>23.40358064516129</v>
       </c>
       <c r="D285" t="n">
-        <v>382.5666666666667</v>
+        <v>382.9966666666667</v>
       </c>
       <c r="E285" t="n">
-        <v>0.004040333333333333</v>
+        <v>0.004332666666666667</v>
       </c>
       <c r="F285" t="n">
-        <v>-0.000196</v>
+        <v>0.0001748387096774194</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n">
-        <v>44325</v>
+        <v>44319</v>
       </c>
       <c r="B286" t="n">
-        <v>68.30666666666666</v>
+        <v>67.78666666666666</v>
       </c>
       <c r="C286" t="n">
-        <v>23.81861290322581</v>
+        <v>24.64867741935484</v>
       </c>
       <c r="D286" t="n">
-        <v>380.5566666666667</v>
+        <v>394.0866666666666</v>
       </c>
       <c r="E286" t="n">
-        <v>0.004185666666666667</v>
+        <v>0.005069666666666667</v>
       </c>
       <c r="F286" t="n">
-        <v>0.0002967741935483871</v>
+        <v>0.0005406451612903226</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="n">
-        <v>44346</v>
+        <v>44340</v>
       </c>
       <c r="B287" t="n">
-        <v>69.42333333333333</v>
+        <v>72.80333333333333</v>
       </c>
       <c r="C287" t="n">
-        <v>25.06370967741936</v>
+        <v>29.23923333333333</v>
       </c>
       <c r="D287" t="n">
-        <v>396.4933333333333</v>
+        <v>389.73</v>
       </c>
       <c r="E287" t="n">
-        <v>0.004740333333333333</v>
+        <v>0.004084333333333333</v>
       </c>
       <c r="F287" t="n">
-        <v>0.0006625806451612903</v>
+        <v>0.000615</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n">
-        <v>44367</v>
+        <v>44361</v>
       </c>
       <c r="B288" t="n">
-        <v>74.43666666666667</v>
+        <v>76.83</v>
       </c>
       <c r="C288" t="n">
-        <v>31.45566666666667</v>
+        <v>35.43986666666667</v>
       </c>
       <c r="D288" t="n">
-        <v>382.84</v>
+        <v>365.14</v>
       </c>
       <c r="E288" t="n">
-        <v>0.004530333333333333</v>
+        <v>0.004342666666666667</v>
       </c>
       <c r="F288" t="n">
-        <v>0.00058</v>
+        <v>0.000246</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="n">
-        <v>44388</v>
+        <v>44382</v>
       </c>
       <c r="B289" t="n">
-        <v>75.28999999999999</v>
+        <v>74.36666666666666</v>
       </c>
       <c r="C289" t="n">
-        <v>36.87113333333333</v>
+        <v>39.73366666666666</v>
       </c>
       <c r="D289" t="n">
-        <v>366.8233333333333</v>
+        <v>382.31</v>
       </c>
       <c r="E289" t="n">
-        <v>0.003697</v>
+        <v>0.002676</v>
       </c>
       <c r="F289" t="n">
-        <v>-0.000251</v>
+        <v>-0.001245</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n">
-        <v>44409</v>
+        <v>44403</v>
       </c>
       <c r="B290" t="n">
-        <v>74.03666666666666</v>
+        <v>69.87</v>
       </c>
       <c r="C290" t="n">
-        <v>41.354875</v>
+        <v>45.547</v>
       </c>
       <c r="D290" t="n">
-        <v>384.6566666666667</v>
+        <v>386.8633333333333</v>
       </c>
       <c r="E290" t="n">
-        <v>0.002099666666666667</v>
+        <v>0.002305</v>
       </c>
       <c r="F290" t="n">
-        <v>-0.0015775</v>
+        <v>-0.00142</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="n">
-        <v>44430</v>
+        <v>44424</v>
       </c>
       <c r="B291" t="n">
-        <v>67.56</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="C291" t="n">
-        <v>47.6430625</v>
+        <v>58.244</v>
       </c>
       <c r="D291" t="n">
-        <v>392.56</v>
+        <v>386.2866666666667</v>
       </c>
       <c r="E291" t="n">
-        <v>0.002179333333333333</v>
+        <v>0.003327</v>
       </c>
       <c r="F291" t="n">
-        <v>-0.00134125</v>
+        <v>-0.0009283333333333333</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="n">
-        <v>44451</v>
+        <v>44445</v>
       </c>
       <c r="B292" t="n">
-        <v>73.31333333333333</v>
+        <v>79.05</v>
       </c>
       <c r="C292" t="n">
-        <v>69.3124</v>
+        <v>91.44919999999999</v>
       </c>
       <c r="D292" t="n">
-        <v>392.5966666666667</v>
+        <v>396.45</v>
       </c>
       <c r="E292" t="n">
-        <v>0.003680666666666667</v>
+        <v>0.004749</v>
       </c>
       <c r="F292" t="n">
-        <v>-0.000492</v>
+        <v>0.0003806666666666667</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="n">
-        <v>44472</v>
+        <v>44466</v>
       </c>
       <c r="B293" t="n">
-        <v>80.60000000000001</v>
+        <v>84.50666666666666</v>
       </c>
       <c r="C293" t="n">
-        <v>94.36951724137931</v>
+        <v>78.48193103448276</v>
       </c>
       <c r="D293" t="n">
-        <v>403.42</v>
+        <v>394.4233333333333</v>
       </c>
       <c r="E293" t="n">
-        <v>0.004731666666666667</v>
+        <v>0.005678666666666666</v>
       </c>
       <c r="F293" t="n">
-        <v>0.0007427586206896552</v>
+        <v>0.001268965517241379</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="n">
-        <v>44493</v>
+        <v>44487</v>
       </c>
       <c r="B294" t="n">
-        <v>85.83666666666666</v>
+        <v>83.2</v>
       </c>
       <c r="C294" t="n">
-        <v>70.53813793103448</v>
+        <v>72.64028125</v>
       </c>
       <c r="D294" t="n">
-        <v>395.84</v>
+        <v>396.43</v>
       </c>
       <c r="E294" t="n">
-        <v>0.006154000000000001</v>
+        <v>0.004699333333333333</v>
       </c>
       <c r="F294" t="n">
-        <v>0.001532068965517241</v>
+        <v>0.001253125</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="n">
-        <v>44514</v>
+        <v>44508</v>
       </c>
       <c r="B295" t="n">
-        <v>82.09</v>
+        <v>73.2</v>
       </c>
       <c r="C295" t="n">
-        <v>78.6885</v>
+        <v>90.78493750000001</v>
       </c>
       <c r="D295" t="n">
-        <v>383.7033333333334</v>
+        <v>378.7533333333333</v>
       </c>
       <c r="E295" t="n">
-        <v>0.004999333333333333</v>
+        <v>0.006180333333333334</v>
       </c>
       <c r="F295" t="n">
-        <v>0.0008899999999999999</v>
+        <v>0.0001637500000000001</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="n">
-        <v>44535</v>
+        <v>44529</v>
       </c>
       <c r="B296" t="n">
-        <v>72.01333333333334</v>
+        <v>72.18666666666667</v>
       </c>
       <c r="C296" t="n">
-        <v>88.9371935483871</v>
+        <v>78.92493548387097</v>
       </c>
       <c r="D296" t="n">
-        <v>390.5266666666666</v>
+        <v>378.4833333333333</v>
       </c>
       <c r="E296" t="n">
-        <v>0.004903333333333334</v>
+        <v>0.004617</v>
       </c>
       <c r="F296" t="n">
-        <v>0.0002890322580645161</v>
+        <v>0.0009303225806451613</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="n">
-        <v>44556</v>
+        <v>44550</v>
       </c>
       <c r="B297" t="n">
-        <v>77.78</v>
+        <v>81.16333333333334</v>
       </c>
       <c r="C297" t="n">
-        <v>73.91880645161291</v>
+        <v>74.50303225806452</v>
       </c>
       <c r="D297" t="n">
-        <v>381.9866666666666</v>
+        <v>397.44</v>
       </c>
       <c r="E297" t="n">
-        <v>0.005879666666666668</v>
+        <v>0.007433333333333333</v>
       </c>
       <c r="F297" t="n">
-        <v>0.001250967741935484</v>
+        <v>0.002028709677419355</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="n">
-        <v>44577</v>
+        <v>44571</v>
       </c>
       <c r="B298" t="n">
-        <v>86.34</v>
+        <v>90.81666666666666</v>
       </c>
       <c r="C298" t="n">
-        <v>77.7386129032258</v>
+        <v>84.20977419354838</v>
       </c>
       <c r="D298" t="n">
-        <v>397.52</v>
+        <v>399.2333333333333</v>
       </c>
       <c r="E298" t="n">
-        <v>0.008059333333333333</v>
+        <v>0.008683333333333335</v>
       </c>
       <c r="F298" t="n">
-        <v>0.002455483870967742</v>
+        <v>0.003309032258064516</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="n">
-        <v>44598</v>
+        <v>44592</v>
       </c>
       <c r="B299" t="n">
-        <v>92.88333333333333</v>
+        <v>94.77333333333334</v>
       </c>
       <c r="C299" t="n">
-        <v>87.6555</v>
+        <v>94.617</v>
       </c>
       <c r="D299" t="n">
-        <v>391.09</v>
+        <v>396.2433333333333</v>
       </c>
       <c r="E299" t="n">
-        <v>0.01219966666666667</v>
+        <v>0.01197166666666667</v>
       </c>
       <c r="F299" t="n">
-        <v>0.00409</v>
+        <v>0.005770000000000001</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="n">
-        <v>44619</v>
+        <v>44613</v>
       </c>
       <c r="B300" t="n">
-        <v>99.97</v>
+        <v>108.8233333333333</v>
       </c>
       <c r="C300" t="n">
-        <v>98.09775</v>
+        <v>110.048</v>
       </c>
       <c r="D300" t="n">
-        <v>401.0333333333334</v>
+        <v>383.9933333333333</v>
       </c>
       <c r="E300" t="n">
-        <v>0.01307966666666667</v>
+        <v>0.01527</v>
       </c>
       <c r="F300" t="n">
-        <v>0.00661</v>
+        <v>0.008386451612903226</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="n">
-        <v>44640</v>
+        <v>44634</v>
       </c>
       <c r="B301" t="n">
-        <v>113.0566666666667</v>
+        <v>106.4833333333333</v>
       </c>
       <c r="C301" t="n">
-        <v>116.215</v>
+        <v>123.1691724137931</v>
       </c>
       <c r="D301" t="n">
-        <v>358.7633333333334</v>
+        <v>354.22</v>
       </c>
       <c r="E301" t="n">
-        <v>0.015266</v>
+        <v>0.016363</v>
       </c>
       <c r="F301" t="n">
-        <v>0.009278387096774194</v>
+        <v>0.01116413793103448</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="n">
-        <v>44661</v>
+        <v>44655</v>
       </c>
       <c r="B302" t="n">
-        <v>99.91333333333334</v>
+        <v>103.7633333333333</v>
       </c>
       <c r="C302" t="n">
-        <v>116.7832413793104</v>
+        <v>104.0113793103448</v>
       </c>
       <c r="D302" t="n">
-        <v>359.7666666666667</v>
+        <v>359.33</v>
       </c>
       <c r="E302" t="n">
-        <v>0.01856733333333333</v>
+        <v>0.01990433333333333</v>
       </c>
       <c r="F302" t="n">
-        <v>0.01229379310344828</v>
+        <v>0.01455310344827586</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="n">
-        <v>44682</v>
+        <v>44676</v>
       </c>
       <c r="B303" t="n">
-        <v>108.1666666666667</v>
+        <v>113.3433333333333</v>
       </c>
       <c r="C303" t="n">
-        <v>99.10962500000001</v>
+        <v>96.727</v>
       </c>
       <c r="D303" t="n">
-        <v>371.18</v>
+        <v>381.1933333333333</v>
       </c>
       <c r="E303" t="n">
-        <v>0.02081266666666667</v>
+        <v>0.02187066666666667</v>
       </c>
       <c r="F303" t="n">
-        <v>0.015460625</v>
+        <v>0.016165</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="n">
-        <v>44703</v>
+        <v>44697</v>
       </c>
       <c r="B304" t="n">
-        <v>113.13</v>
+        <v>119.58</v>
       </c>
       <c r="C304" t="n">
-        <v>95.53568750000001</v>
+        <v>102.4223333333333</v>
       </c>
       <c r="D304" t="n">
-        <v>387.03</v>
+        <v>354.8833333333333</v>
       </c>
       <c r="E304" t="n">
-        <v>0.023101</v>
+        <v>0.02586833333333333</v>
       </c>
       <c r="F304" t="n">
-        <v>0.0165171875</v>
+        <v>0.01760166666666666</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="n">
-        <v>44724</v>
+        <v>44718</v>
       </c>
       <c r="B305" t="n">
-        <v>122.1833333333333</v>
+        <v>114.4333333333333</v>
       </c>
       <c r="C305" t="n">
-        <v>114.208</v>
+        <v>137.7793333333333</v>
       </c>
       <c r="D305" t="n">
-        <v>363.8866666666667</v>
+        <v>355.82</v>
       </c>
       <c r="E305" t="n">
-        <v>0.03042</v>
+        <v>0.030201</v>
       </c>
       <c r="F305" t="n">
-        <v>0.018486</v>
+        <v>0.02025466666666667</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="n">
-        <v>44745</v>
+        <v>44739</v>
       </c>
       <c r="B306" t="n">
-        <v>112.8766666666667</v>
+        <v>104.5666666666667</v>
       </c>
       <c r="C306" t="n">
-        <v>149.3141034482759</v>
+        <v>171.7145862068965</v>
       </c>
       <c r="D306" t="n">
-        <v>325.6233333333333</v>
+        <v>310.29</v>
       </c>
       <c r="E306" t="n">
-        <v>0.028227</v>
+        <v>0.026411</v>
       </c>
       <c r="F306" t="n">
-        <v>0.02020655172413793</v>
+        <v>0.01762379310344828</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="n">
-        <v>44766</v>
+        <v>44760</v>
       </c>
       <c r="B307" t="n">
-        <v>104.5</v>
+        <v>96.07333333333334</v>
       </c>
       <c r="C307" t="n">
-        <v>182.9148275862069</v>
+        <v>204.2764545454546</v>
       </c>
       <c r="D307" t="n">
-        <v>321.9466666666667</v>
+        <v>342.01</v>
       </c>
       <c r="E307" t="n">
-        <v>0.023649</v>
+        <v>0.02252666666666667</v>
       </c>
       <c r="F307" t="n">
-        <v>0.01633241379310345</v>
+        <v>0.01745272727272727</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="n">
-        <v>44787</v>
+        <v>44781</v>
       </c>
       <c r="B308" t="n">
-        <v>96.11666666666666</v>
+        <v>103.7233333333333</v>
       </c>
       <c r="C308" t="n">
-        <v>214.668696969697</v>
+        <v>235.4531818181818</v>
       </c>
       <c r="D308" t="n">
-        <v>357.3833333333333</v>
+        <v>369.6866666666667</v>
       </c>
       <c r="E308" t="n">
-        <v>0.02272833333333333</v>
+        <v>0.03009366666666667</v>
       </c>
       <c r="F308" t="n">
-        <v>0.01904151515151515</v>
+        <v>0.02221909090909091</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="n">
-        <v>44808</v>
+        <v>44802</v>
       </c>
       <c r="B309" t="n">
-        <v>94.83333333333333</v>
+        <v>91.78333333333333</v>
       </c>
       <c r="C309" t="n">
-        <v>233.0927333333333</v>
+        <v>209.2428</v>
       </c>
       <c r="D309" t="n">
-        <v>371.26</v>
+        <v>368.8533333333334</v>
       </c>
       <c r="E309" t="n">
-        <v>0.031595</v>
+        <v>0.03388366666666667</v>
       </c>
       <c r="F309" t="n">
-        <v>0.02375333333333333</v>
+        <v>0.02674</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="n">
-        <v>44829</v>
+        <v>44823</v>
       </c>
       <c r="B310" t="n">
-        <v>84.75666666666667</v>
+        <v>96.76666666666667</v>
       </c>
       <c r="C310" t="n">
-        <v>197.3178333333333</v>
+        <v>169.7989677419355</v>
       </c>
       <c r="D310" t="n">
-        <v>363.0266666666667</v>
+        <v>367.4233333333333</v>
       </c>
       <c r="E310" t="n">
-        <v>0.03760666666666666</v>
+        <v>0.03957433333333334</v>
       </c>
       <c r="F310" t="n">
-        <v>0.02823333333333334</v>
+        <v>0.02931741935483871</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="n">
-        <v>44850</v>
+        <v>44844</v>
       </c>
       <c r="B311" t="n">
-        <v>91.62333333333333</v>
+        <v>95.14333333333333</v>
       </c>
       <c r="C311" t="n">
-        <v>155.0203870967742</v>
+        <v>125.4632258064516</v>
       </c>
       <c r="D311" t="n">
-        <v>373.4</v>
+        <v>369.6533333333334</v>
       </c>
       <c r="E311" t="n">
-        <v>0.04002233333333333</v>
+        <v>0.03926166666666667</v>
       </c>
       <c r="F311" t="n">
-        <v>0.02933096774193548</v>
+        <v>0.02935806451612903</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="n">
-        <v>44871</v>
+        <v>44865</v>
       </c>
       <c r="B312" t="n">
-        <v>98.13666666666667</v>
+        <v>87.50666666666667</v>
       </c>
       <c r="C312" t="n">
-        <v>127.961</v>
+        <v>138.7153333333333</v>
       </c>
       <c r="D312" t="n">
-        <v>367.6</v>
+        <v>370.5566666666667</v>
       </c>
       <c r="E312" t="n">
-        <v>0.040024</v>
+        <v>0.03552133333333334</v>
       </c>
       <c r="F312" t="n">
-        <v>0.028706</v>
+        <v>0.02718</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="n">
-        <v>44892</v>
+        <v>44886</v>
       </c>
       <c r="B313" t="n">
-        <v>83.33666666666666</v>
+        <v>77.36</v>
       </c>
       <c r="C313" t="n">
-        <v>144.0925</v>
+        <v>120.7002666666667</v>
       </c>
       <c r="D313" t="n">
-        <v>370.5133333333333</v>
+        <v>366.4133333333334</v>
       </c>
       <c r="E313" t="n">
-        <v>0.03492700000000001</v>
+        <v>0.03354466666666667</v>
       </c>
       <c r="F313" t="n">
-        <v>0.026417</v>
+        <v>0.028147</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="n">
-        <v>44913</v>
+        <v>44907</v>
       </c>
       <c r="B314" t="n">
-        <v>79.54666666666667</v>
+        <v>85.91</v>
       </c>
       <c r="C314" t="n">
-        <v>104.3478</v>
+        <v>75.1298125</v>
       </c>
       <c r="D314" t="n">
-        <v>365.8266666666667</v>
+        <v>383.5366666666666</v>
       </c>
       <c r="E314" t="n">
-        <v>0.03613666666666667</v>
+        <v>0.03883233333333334</v>
       </c>
       <c r="F314" t="n">
-        <v>0.029456</v>
+        <v>0.031530625</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="n">
-        <v>44934</v>
+        <v>44928</v>
       </c>
       <c r="B315" t="n">
-        <v>79.29000000000001</v>
+        <v>88.00333333333333</v>
       </c>
       <c r="C315" t="n">
-        <v>70.98165625</v>
+        <v>62.68534375</v>
       </c>
       <c r="D315" t="n">
-        <v>395.5833333333334</v>
+        <v>397.21</v>
       </c>
       <c r="E315" t="n">
-        <v>0.03598633333333334</v>
+        <v>0.03506833333333333</v>
       </c>
       <c r="F315" t="n">
-        <v>0.0309378125</v>
+        <v>0.0297521875</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="n">
-        <v>44955</v>
+        <v>44949</v>
       </c>
       <c r="B316" t="n">
-        <v>85.48666666666666</v>
+        <v>86.53666666666666</v>
       </c>
       <c r="C316" t="n">
-        <v>58.5371875</v>
+        <v>52.77185714285714</v>
       </c>
       <c r="D316" t="n">
-        <v>395.72</v>
+        <v>401.09</v>
       </c>
       <c r="E316" t="n">
-        <v>0.03590233333333333</v>
+        <v>0.03593333333333333</v>
       </c>
       <c r="F316" t="n">
-        <v>0.029159375</v>
+        <v>0.03056714285714286</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="n">
-        <v>44976</v>
+        <v>44970</v>
       </c>
       <c r="B317" t="n">
-        <v>83.71333333333332</v>
+        <v>86.06333333333333</v>
       </c>
       <c r="C317" t="n">
-        <v>50.10010714285714</v>
+        <v>46.855</v>
       </c>
       <c r="D317" t="n">
-        <v>391.54</v>
+        <v>387.4366666666667</v>
       </c>
       <c r="E317" t="n">
-        <v>0.03662266666666666</v>
+        <v>0.038713</v>
       </c>
       <c r="F317" t="n">
-        <v>0.03148714285714285</v>
+        <v>0.03223612903225806</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="n">
-        <v>44997</v>
+        <v>44991</v>
       </c>
       <c r="B318" t="n">
-        <v>81.44</v>
+        <v>77.07666666666667</v>
       </c>
       <c r="C318" t="n">
-        <v>47.121</v>
+        <v>47.65300000000001</v>
       </c>
       <c r="D318" t="n">
-        <v>387.4766666666667</v>
+        <v>386.5333333333334</v>
       </c>
       <c r="E318" t="n">
-        <v>0.033985</v>
+        <v>0.032597</v>
       </c>
       <c r="F318" t="n">
-        <v>0.03162870967741935</v>
+        <v>0.03041387096774194</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="n">
-        <v>45018</v>
+        <v>45012</v>
       </c>
       <c r="B319" t="n">
-        <v>83.21000000000001</v>
+        <v>85.27666666666667</v>
       </c>
       <c r="C319" t="n">
-        <v>47.17835714285714</v>
+        <v>42.52585714285714</v>
       </c>
       <c r="D319" t="n">
-        <v>394.35</v>
+        <v>380.6733333333333</v>
       </c>
       <c r="E319" t="n">
-        <v>0.033277</v>
+        <v>0.03480866666666667</v>
       </c>
       <c r="F319" t="n">
-        <v>0.02999785714285715</v>
+        <v>0.03012285714285715</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="n">
-        <v>45039</v>
+        <v>45033</v>
       </c>
       <c r="B320" t="n">
-        <v>82.37333333333333</v>
+        <v>76.44</v>
       </c>
       <c r="C320" t="n">
-        <v>40.19960714285714</v>
+        <v>35.35090909090909</v>
       </c>
       <c r="D320" t="n">
-        <v>387.5533333333333</v>
+        <v>367.7166666666666</v>
       </c>
       <c r="E320" t="n">
-        <v>0.03513766666666666</v>
+        <v>0.033303</v>
       </c>
       <c r="F320" t="n">
-        <v>0.03018535714285714</v>
+        <v>0.03013454545454546</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="n">
-        <v>45060</v>
+        <v>45054</v>
       </c>
       <c r="B321" t="n">
-        <v>74.87666666666667</v>
+        <v>77.03</v>
       </c>
       <c r="C321" t="n">
-        <v>32.87206060606061</v>
+        <v>27.91436363636364</v>
       </c>
       <c r="D321" t="n">
-        <v>366.7566666666667</v>
+        <v>377.0133333333333</v>
       </c>
       <c r="E321" t="n">
-        <v>0.033307</v>
+        <v>0.03572566666666666</v>
       </c>
       <c r="F321" t="n">
-        <v>0.03006030303030303</v>
+        <v>0.02991181818181818</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="n">
-        <v>45081</v>
+        <v>45075</v>
       </c>
       <c r="B322" t="n">
-        <v>76.51666666666667</v>
+        <v>76.26333333333334</v>
       </c>
       <c r="C322" t="n">
-        <v>28.2188</v>
+        <v>33.0026</v>
       </c>
       <c r="D322" t="n">
-        <v>364.8233333333333</v>
+        <v>375.9133333333333</v>
       </c>
       <c r="E322" t="n">
-        <v>0.03462733333333333</v>
+        <v>0.03635766666666667</v>
       </c>
       <c r="F322" t="n">
-        <v>0.02996533333333333</v>
+        <v>0.030264</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="n">
-        <v>45102</v>
+        <v>45096</v>
       </c>
       <c r="B323" t="n">
-        <v>74.07000000000001</v>
+        <v>77.95</v>
       </c>
       <c r="C323" t="n">
-        <v>35.3945</v>
+        <v>34.56645161290323</v>
       </c>
       <c r="D323" t="n">
-        <v>363.7533333333333</v>
+        <v>350.3333333333333</v>
       </c>
       <c r="E323" t="n">
-        <v>0.034879</v>
+        <v>0.03768</v>
       </c>
       <c r="F323" t="n">
-        <v>0.03041333333333333</v>
+        <v>0.03063903225806452</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="n">
-        <v>45123</v>
+        <v>45117</v>
       </c>
       <c r="B324" t="n">
-        <v>78.95666666666666</v>
+        <v>85.37</v>
       </c>
       <c r="C324" t="n">
-        <v>32.59358064516129</v>
+        <v>28.64783870967742</v>
       </c>
       <c r="D324" t="n">
-        <v>353.2866666666667</v>
+        <v>357.1866666666667</v>
       </c>
       <c r="E324" t="n">
-        <v>0.03590933333333333</v>
+        <v>0.03535733333333333</v>
       </c>
       <c r="F324" t="n">
-        <v>0.03073161290322581</v>
+        <v>0.03091677419354839</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="n">
-        <v>45144</v>
+        <v>45138</v>
       </c>
       <c r="B325" t="n">
-        <v>85.64</v>
+        <v>84.57333333333332</v>
       </c>
       <c r="C325" t="n">
-        <v>29.65561290322581</v>
+        <v>32.66470967741936</v>
       </c>
       <c r="D325" t="n">
-        <v>362.3533333333334</v>
+        <v>375.9033333333333</v>
       </c>
       <c r="E325" t="n">
-        <v>0.03585633333333333</v>
+        <v>0.03695966666666667</v>
       </c>
       <c r="F325" t="n">
-        <v>0.03090483870967742</v>
+        <v>0.03084612903225806</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="n">
-        <v>45165</v>
+        <v>45159</v>
       </c>
       <c r="B326" t="n">
-        <v>84.44</v>
+        <v>90.64333333333333</v>
       </c>
       <c r="C326" t="n">
-        <v>34.16925806451613</v>
+        <v>37.38417241379311</v>
       </c>
       <c r="D326" t="n">
-        <v>380.84</v>
+        <v>391.5433333333334</v>
       </c>
       <c r="E326" t="n">
-        <v>0.03636633333333333</v>
+        <v>0.03703633333333334</v>
       </c>
       <c r="F326" t="n">
-        <v>0.03081677419354839</v>
+        <v>0.03211724137931034</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="n">
-        <v>45186</v>
+        <v>45180</v>
       </c>
       <c r="B327" t="n">
-        <v>94.26333333333334</v>
+        <v>92.24333333333333</v>
       </c>
       <c r="C327" t="n">
-        <v>39.03279310344828</v>
+        <v>42.2431875</v>
       </c>
       <c r="D327" t="n">
-        <v>392.65</v>
+        <v>396.74</v>
       </c>
       <c r="E327" t="n">
-        <v>0.037686</v>
+        <v>0.03865</v>
       </c>
       <c r="F327" t="n">
-        <v>0.03303931034482759</v>
+        <v>0.03462</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="n">
-        <v>45207</v>
+        <v>45201</v>
       </c>
       <c r="B328" t="n">
-        <v>86.96000000000001</v>
+        <v>90.60666666666667</v>
       </c>
       <c r="C328" t="n">
-        <v>43.58784375</v>
+        <v>46.27715625</v>
       </c>
       <c r="D328" t="n">
-        <v>393.37</v>
+        <v>374.6133333333333</v>
       </c>
       <c r="E328" t="n">
-        <v>0.03802733333333334</v>
+        <v>0.03910466666666667</v>
       </c>
       <c r="F328" t="n">
         <v>0.03462</v>
@@ -6451,199 +6455,199 @@
     </row>
     <row r="329">
       <c r="A329" s="2" t="n">
-        <v>45228</v>
+        <v>45222</v>
       </c>
       <c r="B329" t="n">
-        <v>88.46000000000001</v>
+        <v>82.15666666666667</v>
       </c>
       <c r="C329" t="n">
-        <v>47.6218125</v>
+        <v>45.64</v>
       </c>
       <c r="D329" t="n">
-        <v>372.4033333333334</v>
+        <v>358.85</v>
       </c>
       <c r="E329" t="n">
-        <v>0.03834766666666667</v>
+        <v>0.03725466666666667</v>
       </c>
       <c r="F329" t="n">
-        <v>0.03462</v>
+        <v>0.033168</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="n">
-        <v>45249</v>
+        <v>45243</v>
       </c>
       <c r="B330" t="n">
-        <v>81.75</v>
+        <v>78.31333333333333</v>
       </c>
       <c r="C330" t="n">
-        <v>44.25983333333333</v>
+        <v>41.08331034482759</v>
       </c>
       <c r="D330" t="n">
-        <v>358.5166666666667</v>
+        <v>367.5666666666667</v>
       </c>
       <c r="E330" t="n">
-        <v>0.03609266666666667</v>
+        <v>0.03328866666666667</v>
       </c>
       <c r="F330" t="n">
-        <v>0.032321</v>
+        <v>0.0305296551724138</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="n">
-        <v>45270</v>
+        <v>45264</v>
       </c>
       <c r="B331" t="n">
-        <v>75.96666666666667</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="C331" t="n">
-        <v>38.73203448275862</v>
+        <v>34.02948275862069</v>
       </c>
       <c r="D331" t="n">
-        <v>364.47</v>
+        <v>369.89</v>
       </c>
       <c r="E331" t="n">
-        <v>0.03297333333333333</v>
+        <v>0.0292848</v>
       </c>
       <c r="F331" t="n">
-        <v>0.02945551724137931</v>
+        <v>0.02730724137931034</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="n">
-        <v>45291</v>
+        <v>45285</v>
       </c>
       <c r="B332" t="n">
-        <v>76.465</v>
+        <v>78.19666666666667</v>
       </c>
       <c r="C332" t="n">
-        <v>32.22181818181819</v>
+        <v>31.32454545454545</v>
       </c>
       <c r="D332" t="n">
-        <v>362.83</v>
+        <v>371.63</v>
       </c>
       <c r="E332" t="n">
-        <v>0.030093</v>
+        <v>0.03205233333333334</v>
       </c>
       <c r="F332" t="n">
-        <v>0.02658969696969697</v>
+        <v>0.02693757575757576</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="n">
-        <v>45312</v>
+        <v>45306</v>
       </c>
       <c r="B333" t="n">
-        <v>79.56</v>
+        <v>77.77</v>
       </c>
       <c r="C333" t="n">
-        <v>30.87590909090909</v>
+        <v>29.49431034482759</v>
       </c>
       <c r="D333" t="n">
-        <v>374.0533333333333</v>
+        <v>393.81</v>
       </c>
       <c r="E333" t="n">
-        <v>0.03293766666666667</v>
+        <v>0.03284933333333333</v>
       </c>
       <c r="F333" t="n">
-        <v>0.02711151515151515</v>
+        <v>0.0276151724137931</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="n">
-        <v>45333</v>
+        <v>45327</v>
       </c>
       <c r="B334" t="n">
-        <v>82.06333333333333</v>
+        <v>82.22666666666667</v>
       </c>
       <c r="C334" t="n">
-        <v>28.19810344827586</v>
+        <v>25.60568965517241</v>
       </c>
       <c r="D334" t="n">
-        <v>396.1933333333333</v>
+        <v>387.46</v>
       </c>
       <c r="E334" t="n">
-        <v>0.033678</v>
+        <v>0.033935</v>
       </c>
       <c r="F334" t="n">
-        <v>0.02806172413793103</v>
+        <v>0.0289548275862069</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="n">
-        <v>45354</v>
+        <v>45348</v>
       </c>
       <c r="B335" t="n">
-        <v>83.05</v>
+        <v>86.37333333333333</v>
       </c>
       <c r="C335" t="n">
-        <v>25.12103448275862</v>
+        <v>26.31586206896552</v>
       </c>
       <c r="D335" t="n">
-        <v>376.8666666666667</v>
+        <v>379.1433333333333</v>
       </c>
       <c r="E335" t="n">
-        <v>0.033953</v>
+        <v>0.033847</v>
       </c>
       <c r="F335" t="n">
-        <v>0.02907551724137931</v>
+        <v>0.02844793103448276</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="n">
-        <v>45375</v>
+        <v>45369</v>
       </c>
       <c r="B336" t="n">
-        <v>86.31</v>
+        <v>90.64333333333333</v>
       </c>
       <c r="C336" t="n">
-        <v>26.91327586206896</v>
+        <v>27.8400625</v>
       </c>
       <c r="D336" t="n">
-        <v>372.4533333333333</v>
+        <v>377.6466666666666</v>
       </c>
       <c r="E336" t="n">
-        <v>0.03296933333333333</v>
+        <v>0.03335666666666667</v>
       </c>
       <c r="F336" t="n">
-        <v>0.02813413793103448</v>
+        <v>0.02868625</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="n">
-        <v>45396</v>
+        <v>45390</v>
       </c>
       <c r="B337" t="n">
-        <v>90.21666666666667</v>
+        <v>88.76666666666667</v>
       </c>
       <c r="C337" t="n">
-        <v>28.229</v>
+        <v>29.006875</v>
       </c>
       <c r="D337" t="n">
-        <v>380.7333333333333</v>
+        <v>374.48</v>
       </c>
       <c r="E337" t="n">
-        <v>0.033427</v>
+        <v>0.03459333333333333</v>
       </c>
       <c r="F337" t="n">
-        <v>0.02929</v>
+        <v>0.0304975</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="n">
-        <v>45417</v>
+        <v>45411</v>
       </c>
       <c r="B338" t="n">
-        <v>83.20666666666666</v>
+        <v>83.8</v>
       </c>
       <c r="C338" t="n">
-        <v>29.94138709677419</v>
+        <v>32.24687096774193</v>
       </c>
       <c r="D338" t="n">
-        <v>385.14</v>
+        <v>393.63</v>
       </c>
       <c r="E338" t="n">
-        <v>0.034173</v>
+        <v>0.034715</v>
       </c>
       <c r="F338" t="n">
         <v>0.03067</v>
@@ -6651,646 +6655,642 @@
     </row>
     <row r="339">
       <c r="A339" s="2" t="n">
-        <v>45438</v>
+        <v>45432</v>
       </c>
       <c r="B339" t="n">
-        <v>82.77333333333333</v>
+        <v>80.95999999999999</v>
       </c>
       <c r="C339" t="n">
-        <v>33.39961290322581</v>
+        <v>34.30560714285714</v>
       </c>
       <c r="D339" t="n">
-        <v>398.9533333333333</v>
+        <v>414.69</v>
       </c>
       <c r="E339" t="n">
-        <v>0.035068</v>
+        <v>0.03579566666666666</v>
       </c>
       <c r="F339" t="n">
-        <v>0.03067</v>
+        <v>0.03068285714285714</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="n">
-        <v>45459</v>
+        <v>45453</v>
       </c>
       <c r="B340" t="n">
-        <v>83.70666666666666</v>
+        <v>86.53666666666666</v>
       </c>
       <c r="C340" t="n">
-        <v>34.36985714285714</v>
+        <v>34.56412121212121</v>
       </c>
       <c r="D340" t="n">
-        <v>412.1766666666667</v>
+        <v>400.43</v>
       </c>
       <c r="E340" t="n">
-        <v>0.033852</v>
+        <v>0.03557233333333333</v>
       </c>
       <c r="F340" t="n">
-        <v>0.03069285714285714</v>
+        <v>0.03056212121212121</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="n">
-        <v>45480</v>
+        <v>45474</v>
       </c>
       <c r="B341" t="n">
-        <v>86.01333333333334</v>
+        <v>82.47666666666667</v>
       </c>
       <c r="C341" t="n">
-        <v>34.85854545454545</v>
+        <v>35.44739393939394</v>
       </c>
       <c r="D341" t="n">
-        <v>411.5433333333334</v>
+        <v>405.29</v>
       </c>
       <c r="E341" t="n">
-        <v>0.034912</v>
+        <v>0.034317</v>
       </c>
       <c r="F341" t="n">
-        <v>0.03004454545454546</v>
+        <v>0.02900939393939394</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="n">
-        <v>45501</v>
+        <v>45495</v>
       </c>
       <c r="B342" t="n">
-        <v>80.23</v>
+        <v>81.42</v>
       </c>
       <c r="C342" t="n">
-        <v>35.74181818181818</v>
+        <v>37.31816666666667</v>
       </c>
       <c r="D342" t="n">
-        <v>397.49</v>
+        <v>389.9233333333333</v>
       </c>
       <c r="E342" t="n">
-        <v>0.03324266666666666</v>
+        <v>0.032527</v>
       </c>
       <c r="F342" t="n">
-        <v>0.02849181818181818</v>
+        <v>0.02809766666666667</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="n">
-        <v>45522</v>
+        <v>45516</v>
       </c>
       <c r="B343" t="n">
-        <v>78.33333333333333</v>
+        <v>77.94666666666666</v>
       </c>
       <c r="C343" t="n">
-        <v>38.241</v>
+        <v>39.77274193548387</v>
       </c>
       <c r="D343" t="n">
-        <v>392.6666666666667</v>
+        <v>390.6166666666667</v>
       </c>
       <c r="E343" t="n">
-        <v>0.03270866666666666</v>
+        <v>0.03324466666666667</v>
       </c>
       <c r="F343" t="n">
-        <v>0.027988</v>
+        <v>0.02772451612903225</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="n">
-        <v>45543</v>
+        <v>45537</v>
       </c>
       <c r="B344" t="n">
-        <v>71.58</v>
+        <v>74.09666666666666</v>
       </c>
       <c r="C344" t="n">
-        <v>39.59683870967742</v>
+        <v>39.24503225806451</v>
       </c>
       <c r="D344" t="n">
-        <v>381.99</v>
+        <v>389.3733333333333</v>
       </c>
       <c r="E344" t="n">
-        <v>0.03186966666666666</v>
+        <v>0.03204433333333333</v>
       </c>
       <c r="F344" t="n">
-        <v>0.02746032258064516</v>
+        <v>0.02693193548387096</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="n">
-        <v>45564</v>
+        <v>45558</v>
       </c>
       <c r="B345" t="n">
-        <v>71.84</v>
+        <v>77.98666666666666</v>
       </c>
       <c r="C345" t="n">
-        <v>39.06912903225806</v>
+        <v>39.69148387096774</v>
       </c>
       <c r="D345" t="n">
-        <v>376.5033333333333</v>
+        <v>375.1633333333333</v>
       </c>
       <c r="E345" t="n">
-        <v>0.03140433333333333</v>
+        <v>0.03286266666666667</v>
       </c>
       <c r="F345" t="n">
-        <v>0.02666774193548387</v>
+        <v>0.02735967741935484</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="n">
-        <v>45585</v>
+        <v>45579</v>
       </c>
       <c r="B346" t="n">
-        <v>73.88000000000001</v>
+        <v>74.42</v>
       </c>
       <c r="C346" t="n">
-        <v>40.04012903225806</v>
+        <v>41.33520689655172</v>
       </c>
       <c r="D346" t="n">
-        <v>387.3566666666667</v>
+        <v>382.64</v>
       </c>
       <c r="E346" t="n">
-        <v>0.03224466666666666</v>
+        <v>0.033662</v>
       </c>
       <c r="F346" t="n">
-        <v>0.02775258064516129</v>
+        <v>0.02812586206896552</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="n">
-        <v>45606</v>
+        <v>45600</v>
       </c>
       <c r="B347" t="n">
-        <v>72.51000000000001</v>
+        <v>73.73</v>
       </c>
       <c r="C347" t="n">
-        <v>43.07868965517241</v>
+        <v>46.56565517241379</v>
       </c>
       <c r="D347" t="n">
-        <v>384.5666666666667</v>
+        <v>388.0566666666667</v>
       </c>
       <c r="E347" t="n">
-        <v>0.03281633333333333</v>
+        <v>0.03197533333333333</v>
       </c>
       <c r="F347" t="n">
-        <v>0.02755620689655172</v>
+        <v>0.02641689655172414</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="n">
-        <v>45627</v>
+        <v>45621</v>
       </c>
       <c r="B348" t="n">
-        <v>72.2</v>
+        <v>74.10333333333332</v>
       </c>
       <c r="C348" t="n">
-        <v>47.878375</v>
+        <v>48.35</v>
       </c>
       <c r="D348" t="n">
-        <v>398.3633333333333</v>
+        <v>418.11</v>
       </c>
       <c r="E348" t="n">
-        <v>0.030431</v>
+        <v>0.031519</v>
       </c>
       <c r="F348" t="n">
-        <v>0.026138125</v>
+        <v>0.027035</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="n">
-        <v>45648</v>
+        <v>45642</v>
       </c>
       <c r="B349" t="n">
-        <v>72.73333333333333</v>
+        <v>76.37</v>
       </c>
       <c r="C349" t="n">
-        <v>48.5858125</v>
+        <v>49.59029032258065</v>
       </c>
       <c r="D349" t="n">
-        <v>423.97</v>
+        <v>431.8233333333333</v>
       </c>
       <c r="E349" t="n">
-        <v>0.032278</v>
+        <v>0.03368133333333333</v>
       </c>
       <c r="F349" t="n">
-        <v>0.0274834375</v>
+        <v>0.02813258064516129</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="n">
-        <v>45669</v>
+        <v>45663</v>
       </c>
       <c r="B350" t="n">
-        <v>80.59333333333333</v>
+        <v>77.55333333333333</v>
       </c>
       <c r="C350" t="n">
-        <v>50.57209677419355</v>
+        <v>52.53570967741936</v>
       </c>
       <c r="D350" t="n">
-        <v>433.44</v>
+        <v>423.39</v>
       </c>
       <c r="E350" t="n">
-        <v>0.034956</v>
+        <v>0.034249</v>
       </c>
       <c r="F350" t="n">
-        <v>0.0282341935483871</v>
+        <v>0.02843741935483871</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="n">
-        <v>45690</v>
+        <v>45684</v>
       </c>
       <c r="B351" t="n">
-        <v>76.22666666666666</v>
+        <v>75.06</v>
       </c>
       <c r="C351" t="n">
-        <v>52.60007142857143</v>
+        <v>48.14157142857143</v>
       </c>
       <c r="D351" t="n">
-        <v>443.7833333333334</v>
+        <v>442.5333333333333</v>
       </c>
       <c r="E351" t="n">
-        <v>0.032465</v>
+        <v>0.032655</v>
       </c>
       <c r="F351" t="n">
-        <v>0.02846785714285714</v>
+        <v>0.02817285714285714</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="n">
-        <v>45711</v>
+        <v>45705</v>
       </c>
       <c r="B352" t="n">
-        <v>74.66333333333334</v>
+        <v>69.64</v>
       </c>
       <c r="C352" t="n">
-        <v>45.91232142857143</v>
+        <v>43.25945161290323</v>
       </c>
       <c r="D352" t="n">
-        <v>442.5166666666667</v>
+        <v>453.04</v>
       </c>
       <c r="E352" t="n">
-        <v>0.03215166666666667</v>
+        <v>0.03466033333333333</v>
       </c>
       <c r="F352" t="n">
-        <v>0.02802535714285714</v>
+        <v>0.02891</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="n">
-        <v>45732</v>
+        <v>45726</v>
       </c>
       <c r="B353" t="n">
-        <v>70.90666666666667</v>
+        <v>74.36999999999999</v>
       </c>
       <c r="C353" t="n">
-        <v>42.43458064516129</v>
+        <v>40.78483870967742</v>
       </c>
       <c r="D353" t="n">
-        <v>451.6533333333334</v>
+        <v>441.5366666666666</v>
       </c>
       <c r="E353" t="n">
-        <v>0.03484833333333334</v>
+        <v>0.03409966666666667</v>
       </c>
       <c r="F353" t="n">
-        <v>0.02968</v>
+        <v>0.03122</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="n">
-        <v>45753</v>
+        <v>45747</v>
       </c>
       <c r="B354" t="n">
-        <v>64.66666666666666</v>
+        <v>66.685</v>
       </c>
       <c r="C354" t="n">
-        <v>38.997</v>
+        <v>35.10033333333333</v>
       </c>
       <c r="D354" t="n">
-        <v>450.5633333333333</v>
+        <v>442.7066666666666</v>
       </c>
       <c r="E354" t="n">
-        <v>0.03399133333333333</v>
+        <v>0.0325604</v>
       </c>
       <c r="F354" t="n">
-        <v>0.030922</v>
+        <v>0.02997</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="n">
-        <v>45774</v>
+        <v>45768</v>
       </c>
       <c r="B355" t="n">
-        <v>66.19666666666667</v>
+        <v>64.61</v>
       </c>
       <c r="C355" t="n">
-        <v>33.152</v>
+        <v>33.0177</v>
       </c>
       <c r="D355" t="n">
-        <v>434.94</v>
+        <v>438.9233333333333</v>
       </c>
       <c r="E355" t="n">
-        <v>0.03284166666666666</v>
+        <v>0.034343</v>
       </c>
       <c r="F355" t="n">
-        <v>0.029494</v>
+        <v>0.02939266666666666</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="n">
-        <v>45795</v>
+        <v>45789</v>
       </c>
       <c r="B356" t="n">
-        <v>65.49666666666667</v>
+        <v>64.38666666666666</v>
       </c>
       <c r="C356" t="n">
-        <v>33.4636</v>
+        <v>34.1421935483871</v>
       </c>
       <c r="D356" t="n">
-        <v>423.7966666666667</v>
+        <v>432.2266666666666</v>
       </c>
       <c r="E356" t="n">
-        <v>0.03404166666666667</v>
+        <v>0.03364966666666667</v>
       </c>
       <c r="F356" t="n">
-        <v>0.029458</v>
+        <v>0.02961387096774194</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="n">
-        <v>45816</v>
+        <v>45810</v>
       </c>
       <c r="B357" t="n">
-        <v>66.85000000000001</v>
+        <v>73.32333333333334</v>
       </c>
       <c r="C357" t="n">
-        <v>33.84187096774194</v>
+        <v>33.24122580645162</v>
       </c>
       <c r="D357" t="n">
-        <v>432.4133333333334</v>
+        <v>450.0766666666667</v>
       </c>
       <c r="E357" t="n">
-        <v>0.03423566666666667</v>
+        <v>0.034136</v>
       </c>
       <c r="F357" t="n">
-        <v>0.02976741935483871</v>
+        <v>0.03007451612903226</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="n">
-        <v>45837</v>
+        <v>45831</v>
       </c>
       <c r="B358" t="n">
-        <v>67.66333333333333</v>
+        <v>69.59333333333333</v>
       </c>
       <c r="C358" t="n">
-        <v>32.94090322580645</v>
+        <v>33.89648387096774</v>
       </c>
       <c r="D358" t="n">
-        <v>459.8133333333333</v>
+        <v>473.3466666666666</v>
       </c>
       <c r="E358" t="n">
-        <v>0.03464033333333334</v>
+        <v>0.034963</v>
       </c>
       <c r="F358" t="n">
-        <v>0.03022806451612903</v>
+        <v>0.03036322580645161</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="n">
-        <v>45858</v>
+        <v>45852</v>
       </c>
       <c r="B359" t="n">
-        <v>69.23333333333333</v>
+        <v>69.06333333333333</v>
       </c>
       <c r="C359" t="n">
-        <v>34.43412903225807</v>
+        <v>34.90068965517241</v>
       </c>
       <c r="D359" t="n">
-        <v>478.49</v>
+        <v>486.4233333333333</v>
       </c>
       <c r="E359" t="n">
-        <v>0.03407133333333334</v>
+        <v>0.03400533333333333</v>
       </c>
       <c r="F359" t="n">
-        <v>0.0304241935483871</v>
+        <v>0.03055206896551724</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="n">
-        <v>45879</v>
+        <v>45873</v>
       </c>
       <c r="B360" t="n">
-        <v>66.61666666666666</v>
+        <v>68.44333333333333</v>
       </c>
       <c r="C360" t="n">
-        <v>34.01796551724138</v>
+        <v>32.25251724137931</v>
       </c>
       <c r="D360" t="n">
-        <v>478.6566666666667</v>
+        <v>479.9166666666667</v>
       </c>
       <c r="E360" t="n">
-        <v>0.034306</v>
+        <v>0.03474333333333333</v>
       </c>
       <c r="F360" t="n">
-        <v>0.03062689655172414</v>
+        <v>0.03077655172413793</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="n">
-        <v>45900</v>
+        <v>45894</v>
       </c>
       <c r="B361" t="n">
-        <v>68.14</v>
+        <v>67.28999999999999</v>
       </c>
       <c r="C361" t="n">
-        <v>31.6088125</v>
+        <v>31.5165</v>
       </c>
       <c r="D361" t="n">
-        <v>479.21</v>
+        <v>495.3366666666666</v>
       </c>
       <c r="E361" t="n">
-        <v>0.03472933333333333</v>
+        <v>0.034548</v>
       </c>
       <c r="F361" t="n">
-        <v>0.0308325</v>
+        <v>0.03085</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="n">
-        <v>45921</v>
+        <v>45915</v>
       </c>
       <c r="B362" t="n">
-        <v>66.60666666666667</v>
+        <v>65.15666666666667</v>
       </c>
       <c r="C362" t="n">
-        <v>31.47034375</v>
+        <v>31.36438709677419</v>
       </c>
       <c r="D362" t="n">
-        <v>510.48</v>
+        <v>507.8033333333333</v>
       </c>
       <c r="E362" t="n">
-        <v>0.03481066666666667</v>
+        <v>0.034519</v>
       </c>
       <c r="F362" t="n">
-        <v>0.03085875</v>
+        <v>0.03077161290322581</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="n">
-        <v>45942</v>
+        <v>45936</v>
       </c>
       <c r="B363" t="n">
-        <v>63.12333333333333</v>
+        <v>65.72666666666667</v>
       </c>
       <c r="C363" t="n">
-        <v>31.29912903225807</v>
+        <v>31.16861290322581</v>
       </c>
       <c r="D363" t="n">
-        <v>524.8533333333334</v>
+        <v>547.9166666666666</v>
       </c>
       <c r="E363" t="n">
-        <v>0.03399733333333334</v>
+        <v>0.03382866666666667</v>
       </c>
       <c r="F363" t="n">
-        <v>0.03063387096774194</v>
+        <v>0.03035838709677419</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="n">
-        <v>45963</v>
+        <v>45957</v>
       </c>
       <c r="B364" t="n">
-        <v>64.95</v>
+        <v>64.26333333333334</v>
       </c>
       <c r="C364" t="n">
-        <v>30.95735714285714</v>
+        <v>29.80485714285714</v>
       </c>
       <c r="D364" t="n">
-        <v>542.98</v>
+        <v>548.14</v>
       </c>
       <c r="E364" t="n">
-        <v>0.03406166666666666</v>
+        <v>0.03498233333333333</v>
       </c>
       <c r="F364" t="n">
-        <v>0.03029857142857143</v>
+        <v>0.03056857142857143</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="n">
-        <v>45984</v>
+        <v>45978</v>
       </c>
       <c r="B365" t="n">
-        <v>63.1</v>
+        <v>62.91</v>
       </c>
       <c r="C365" t="n">
-        <v>29.22860714285714</v>
-      </c>
-      <c r="D365" t="n">
-        <v>548.14</v>
-      </c>
+        <v>28.63809090909091</v>
+      </c>
+      <c r="D365" t="inlineStr"/>
       <c r="E365" t="n">
-        <v>0.035075</v>
+        <v>0.03630533333333333</v>
       </c>
       <c r="F365" t="n">
-        <v>0.03070357142857143</v>
+        <v>0.03114090909090909</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="n">
-        <v>46005</v>
+        <v>45999</v>
       </c>
       <c r="B366" t="n">
-        <v>60.74666666666667</v>
+        <v>61.50666666666667</v>
       </c>
       <c r="C366" t="n">
-        <v>28.49893939393939</v>
+        <v>28.22063636363637</v>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="n">
-        <v>0.03641733333333334</v>
+        <v>0.0363226</v>
       </c>
       <c r="F366" t="n">
-        <v>0.03140606060606061</v>
+        <v>0.03193636363636364</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="n">
-        <v>46026</v>
+        <v>46020</v>
       </c>
       <c r="B367" t="n">
-        <v>61.42333333333333</v>
+        <v>64.00333333333333</v>
       </c>
       <c r="C367" t="n">
-        <v>29.6442</v>
+        <v>34.8354</v>
       </c>
       <c r="D367" t="inlineStr"/>
       <c r="E367" t="n">
-        <v>0.03672766666666667</v>
+        <v>0.03596633333333333</v>
       </c>
       <c r="F367" t="n">
-        <v>0.03196466666666667</v>
+        <v>0.031666</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="n">
-        <v>46047</v>
+        <v>46041</v>
       </c>
       <c r="B368" t="n">
-        <v>65.68666666666667</v>
+        <v>68.71000000000001</v>
       </c>
       <c r="C368" t="n">
-        <v>37.431</v>
+        <v>36.93021428571429</v>
       </c>
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="n">
-        <v>0.036223</v>
+        <v>0.03561666666666667</v>
       </c>
       <c r="F368" t="n">
-        <v>0.03151666666666667</v>
+        <v>0.03079285714285714</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="n">
-        <v>46068</v>
+        <v>46062</v>
       </c>
       <c r="B369" t="n">
-        <v>68.35000000000001</v>
+        <v>75.98666666666666</v>
       </c>
       <c r="C369" t="n">
-        <v>35.09871428571429</v>
+        <v>33.77028</v>
       </c>
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="n">
-        <v>0.03492333333333333</v>
+        <v>0.03484</v>
       </c>
       <c r="F369" t="n">
-        <v>0.03031285714285714</v>
+        <v>0.02986083333333333</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="n">
-        <v>46089</v>
+        <v>46083</v>
       </c>
       <c r="B370" t="n">
         <v>81.40000000000001</v>
       </c>
       <c r="C370" t="n">
-        <v>40.10976</v>
+        <v>52.78872</v>
       </c>
       <c r="D370" t="inlineStr"/>
       <c r="E370" t="n">
-        <v>0.036761</v>
+        <v>0.036821</v>
       </c>
       <c r="F370" t="n">
-        <v>0.03115875</v>
+        <v>0.03375458333333333</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="n">
-        <v>46110</v>
+        <v>46104</v>
       </c>
       <c r="B371" t="inlineStr"/>
       <c r="C371" t="n">
         <v>54.6</v>
       </c>
       <c r="D371" t="inlineStr"/>
-      <c r="E371" t="n">
-        <v>0.036821</v>
-      </c>
+      <c r="E371" t="inlineStr"/>
       <c r="F371" t="n">
         <v>0.03394</v>
       </c>

--- a/data/merged_input_data.xlsx
+++ b/data/merged_input_data.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F371"/>
+  <dimension ref="A1:F278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6832 +466,5118 @@
         <v>38355</v>
       </c>
       <c r="B2" t="n">
-        <v>45.91666666666666</v>
+        <v>45.59666666666667</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>277.8</v>
+        <v>281.5</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>38376</v>
+        <v>38383</v>
       </c>
       <c r="B3" t="n">
-        <v>45.28666666666667</v>
+        <v>49.91</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>295.0066666666667</v>
+        <v>281.9566666666666</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>38397</v>
+        <v>38411</v>
       </c>
       <c r="B4" t="n">
-        <v>51.99333333333333</v>
+        <v>53.39</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>283.1966666666667</v>
+        <v>282.84</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>38418</v>
+        <v>38439</v>
       </c>
       <c r="B5" t="n">
-        <v>53.39</v>
+        <v>54.59</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>282.84</v>
+        <v>285.18</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>38439</v>
+        <v>38467</v>
       </c>
       <c r="B6" t="n">
-        <v>51.05666666666666</v>
+        <v>48.25666666666667</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>282.69</v>
+        <v>294.9</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>38460</v>
+        <v>38495</v>
       </c>
       <c r="B7" t="n">
-        <v>51.11666666666667</v>
+        <v>58.13333333333333</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>289.1166666666667</v>
+        <v>304.1266666666667</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>38481</v>
+        <v>38523</v>
       </c>
       <c r="B8" t="n">
-        <v>50.715</v>
+        <v>57.19666666666667</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>301.48</v>
+        <v>303.3333333333334</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>38502</v>
+        <v>38551</v>
       </c>
       <c r="B9" t="n">
-        <v>58.13333333333333</v>
+        <v>65.87</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>304.1266666666667</v>
+        <v>313.0133333333333</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>38523</v>
+        <v>38579</v>
       </c>
       <c r="B10" t="n">
-        <v>57.69333333333334</v>
+        <v>62.14666666666667</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>306.28</v>
+        <v>327.0966666666667</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>38544</v>
+        <v>38607</v>
       </c>
       <c r="B11" t="n">
-        <v>60.08333333333333</v>
+        <v>58.92333333333333</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>309.6266666666667</v>
+        <v>319.9966666666667</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>38565</v>
+        <v>38635</v>
       </c>
       <c r="B12" t="n">
-        <v>64.45333333333333</v>
+        <v>58.44333333333334</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>315.0066666666667</v>
+        <v>318.7266666666666</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>38586</v>
+        <v>38663</v>
       </c>
       <c r="B13" t="n">
-        <v>62.14666666666667</v>
+        <v>57.50333333333333</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>327.0966666666667</v>
+        <v>331.4966666666667</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>38607</v>
+        <v>38691</v>
       </c>
       <c r="B14" t="n">
-        <v>63.02666666666666</v>
+        <v>60.165</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>329.6366666666667</v>
+        <v>346.5833333333333</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>38628</v>
+        <v>38719</v>
       </c>
       <c r="B15" t="n">
-        <v>58.32</v>
+        <v>66.47333333333333</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>310.5933333333333</v>
+        <v>370.4766666666667</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>38649</v>
+        <v>38747</v>
       </c>
       <c r="B16" t="n">
-        <v>54.81666666666666</v>
+        <v>61.52666666666667</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>325.4</v>
+        <v>382.6633333333334</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>38670</v>
+        <v>38775</v>
       </c>
       <c r="B17" t="n">
-        <v>57.50333333333333</v>
+        <v>63.57666666666667</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>331.4966666666667</v>
+        <v>380.6066666666667</v>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>38691</v>
+        <v>38803</v>
       </c>
       <c r="B18" t="n">
-        <v>56.48999999999999</v>
+        <v>73.96333333333334</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>344.97</v>
+        <v>381.1233333333333</v>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>38712</v>
+        <v>38831</v>
       </c>
       <c r="B19" t="n">
-        <v>62.70666666666666</v>
+        <v>69.12666666666667</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>357.39</v>
+        <v>374.82</v>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>38733</v>
+        <v>38859</v>
       </c>
       <c r="B20" t="n">
-        <v>63.35</v>
+        <v>68.34</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>369.9666666666666</v>
+        <v>364.4633333333333</v>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>38754</v>
+        <v>38887</v>
       </c>
       <c r="B21" t="n">
-        <v>61.52666666666667</v>
+        <v>76.37</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>382.6633333333334</v>
+        <v>377.24</v>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>38775</v>
+        <v>38915</v>
       </c>
       <c r="B22" t="n">
-        <v>61.98</v>
+        <v>74.74333333333333</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
-        <v>386.04</v>
+        <v>399.6166666666667</v>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>38796</v>
+        <v>38943</v>
       </c>
       <c r="B23" t="n">
-        <v>68.26333333333334</v>
+        <v>64.81</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="n">
-        <v>376.15</v>
+        <v>413.97</v>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>38817</v>
+        <v>38971</v>
       </c>
       <c r="B24" t="n">
-        <v>73.10000000000001</v>
+        <v>60.30333333333333</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="n">
-        <v>388.1133333333333</v>
+        <v>429.28</v>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>38838</v>
+        <v>38999</v>
       </c>
       <c r="B25" t="n">
-        <v>69.12666666666667</v>
+        <v>59.55</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="n">
-        <v>374.82</v>
+        <v>444.4066666666666</v>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>38859</v>
+        <v>39027</v>
       </c>
       <c r="B26" t="n">
-        <v>69.44666666666667</v>
+        <v>63.84</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
-        <v>359.4666666666667</v>
+        <v>459.56</v>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>38880</v>
+        <v>39055</v>
       </c>
       <c r="B27" t="n">
-        <v>73.43000000000001</v>
+        <v>60.65</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">
-        <v>374.7166666666666</v>
+        <v>455.5666666666667</v>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>38901</v>
+        <v>39083</v>
       </c>
       <c r="B28" t="n">
-        <v>74.32333333333334</v>
+        <v>54.21666666666667</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="n">
-        <v>391.1733333333333</v>
+        <v>480.7566666666667</v>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>38922</v>
+        <v>39111</v>
       </c>
       <c r="B29" t="n">
-        <v>74.74333333333333</v>
+        <v>61.18</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
-        <v>399.6166666666667</v>
+        <v>458.99</v>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>38943</v>
+        <v>39139</v>
       </c>
       <c r="B30" t="n">
-        <v>68.19</v>
+        <v>64</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="n">
-        <v>402.5466666666667</v>
+        <v>490.5133333333333</v>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>38964</v>
+        <v>39167</v>
       </c>
       <c r="B31" t="n">
-        <v>60.66999999999999</v>
+        <v>67.59666666666666</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="n">
-        <v>423.4766666666667</v>
+        <v>498.1233333333333</v>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>38985</v>
+        <v>39195</v>
       </c>
       <c r="B32" t="n">
-        <v>59.81333333333333</v>
+        <v>70.13333333333333</v>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="n">
-        <v>432.3</v>
+        <v>521.6233333333333</v>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>39006</v>
+        <v>39223</v>
       </c>
       <c r="B33" t="n">
-        <v>59.55</v>
+        <v>71.94333333333334</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="n">
-        <v>444.4066666666666</v>
+        <v>507.0266666666667</v>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>39027</v>
+        <v>39251</v>
       </c>
       <c r="B34" t="n">
-        <v>60.30333333333333</v>
+        <v>77.41</v>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="n">
-        <v>448.0966666666667</v>
+        <v>480.12</v>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>39048</v>
+        <v>39279</v>
       </c>
       <c r="B35" t="n">
-        <v>62.58333333333334</v>
+        <v>70.28333333333333</v>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="n">
-        <v>461.7766666666666</v>
+        <v>484.3466666666666</v>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>39069</v>
+        <v>39307</v>
       </c>
       <c r="B36" t="n">
-        <v>55.61333333333334</v>
+        <v>75.34333333333333</v>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="n">
-        <v>458.7266666666667</v>
+        <v>505.1333333333333</v>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>39090</v>
+        <v>39335</v>
       </c>
       <c r="B37" t="n">
-        <v>54.21666666666667</v>
+        <v>77.35333333333334</v>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="n">
-        <v>480.7566666666667</v>
+        <v>529.4599999999999</v>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>39111</v>
+        <v>39363</v>
       </c>
       <c r="B38" t="n">
-        <v>58.41</v>
+        <v>91.02</v>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="n">
-        <v>452.6366666666667</v>
+        <v>537.11</v>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>39132</v>
+        <v>39391</v>
       </c>
       <c r="B39" t="n">
-        <v>60.87</v>
+        <v>89.28666666666666</v>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="n">
-        <v>469.6633333333334</v>
+        <v>551.5500000000001</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>39153</v>
+        <v>39419</v>
       </c>
       <c r="B40" t="n">
-        <v>68.52666666666666</v>
+        <v>93.86</v>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="n">
-        <v>491.8166666666667</v>
+        <v>525.02</v>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>39174</v>
+        <v>39447</v>
       </c>
       <c r="B41" t="n">
-        <v>67.59666666666666</v>
+        <v>91.22</v>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="n">
-        <v>498.1233333333333</v>
+        <v>508.0433333333334</v>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>39195</v>
+        <v>39475</v>
       </c>
       <c r="B42" t="n">
-        <v>66.83</v>
+        <v>97.46333333333334</v>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="n">
-        <v>510.0266666666666</v>
+        <v>472.3766666666667</v>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>39216</v>
+        <v>39503</v>
       </c>
       <c r="B43" t="n">
-        <v>69.95666666666666</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="n">
-        <v>511.87</v>
+        <v>462.9366666666667</v>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>39237</v>
+        <v>39531</v>
       </c>
       <c r="B44" t="n">
-        <v>71.3</v>
+        <v>114.26</v>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="n">
-        <v>504.7533333333333</v>
+        <v>476.0133333333333</v>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>39258</v>
+        <v>39559</v>
       </c>
       <c r="B45" t="n">
-        <v>77.41</v>
+        <v>125.0366666666667</v>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="n">
-        <v>480.12</v>
+        <v>490.2366666666667</v>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>39279</v>
+        <v>39587</v>
       </c>
       <c r="B46" t="n">
-        <v>72.36333333333333</v>
+        <v>134.5566666666667</v>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="n">
-        <v>477.2433333333333</v>
+        <v>457.1966666666667</v>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>39300</v>
+        <v>39615</v>
       </c>
       <c r="B47" t="n">
-        <v>70.84</v>
+        <v>144.11</v>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="n">
-        <v>480.4933333333333</v>
+        <v>439.7833333333334</v>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>39321</v>
+        <v>39643</v>
       </c>
       <c r="B48" t="n">
-        <v>76.72666666666667</v>
+        <v>112.89</v>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="n">
-        <v>517.4300000000001</v>
+        <v>446.4766666666667</v>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>39342</v>
+        <v>39671</v>
       </c>
       <c r="B49" t="n">
-        <v>77.35333333333334</v>
+        <v>103.6566666666667</v>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="n">
-        <v>529.4599999999999</v>
+        <v>405.2533333333333</v>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>39363</v>
+        <v>39699</v>
       </c>
       <c r="B50" t="n">
-        <v>89.77666666666666</v>
+        <v>85.87</v>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="n">
-        <v>542.4666666666666</v>
+        <v>322.3966666666666</v>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>39384</v>
+        <v>39727</v>
       </c>
       <c r="B51" t="n">
-        <v>92.06</v>
+        <v>62.09333333333333</v>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="n">
-        <v>547.6</v>
+        <v>332.8933333333333</v>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>39405</v>
+        <v>39755</v>
       </c>
       <c r="B52" t="n">
-        <v>88.24000000000001</v>
+        <v>49.81</v>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="n">
-        <v>546.7233333333334</v>
+        <v>325.3833333333333</v>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>39426</v>
+        <v>39783</v>
       </c>
       <c r="B53" t="n">
-        <v>93.86</v>
+        <v>39.82333333333333</v>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="n">
-        <v>525.02</v>
+        <v>310.93</v>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>39447</v>
+        <v>39811</v>
       </c>
       <c r="B54" t="n">
-        <v>88.08333333333334</v>
+        <v>47.43</v>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="n">
-        <v>489.16</v>
+        <v>300.4833333333333</v>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>39468</v>
+        <v>39839</v>
       </c>
       <c r="B55" t="n">
-        <v>93</v>
+        <v>41.29</v>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="n">
-        <v>485.5833333333333</v>
+        <v>268.5166666666667</v>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>39489</v>
+        <v>39867</v>
       </c>
       <c r="B56" t="n">
-        <v>100.3533333333333</v>
+        <v>52.72</v>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="n">
-        <v>454.9633333333333</v>
+        <v>285.37</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>39510</v>
+        <v>39895</v>
       </c>
       <c r="B57" t="n">
-        <v>99.98999999999999</v>
+        <v>51.02333333333333</v>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="n">
-        <v>462.9366666666667</v>
+        <v>302.3633333333333</v>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>39531</v>
+        <v>39923</v>
       </c>
       <c r="B58" t="n">
-        <v>109.4766666666667</v>
+        <v>57.64</v>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="n">
-        <v>478.07</v>
+        <v>303.5566666666667</v>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>39552</v>
+        <v>39951</v>
       </c>
       <c r="B59" t="n">
-        <v>116.8466666666667</v>
+        <v>69.93333333333334</v>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="n">
-        <v>484.0466666666666</v>
+        <v>284.5266666666666</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>39573</v>
+        <v>39979</v>
       </c>
       <c r="B60" t="n">
-        <v>132.1033333333333</v>
+        <v>60.63333333333333</v>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="n">
-        <v>471.4166666666667</v>
-      </c>
-      <c r="E60" t="inlineStr"/>
+        <v>309.3133333333333</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.045655</v>
+      </c>
       <c r="F60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>39594</v>
+        <v>40007</v>
       </c>
       <c r="B61" t="n">
-        <v>134.5566666666667</v>
+        <v>73.53</v>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="n">
-        <v>457.1966666666667</v>
-      </c>
-      <c r="E61" t="inlineStr"/>
+        <v>329.8466666666667</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.045909</v>
+      </c>
       <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>39615</v>
+        <v>40035</v>
       </c>
       <c r="B62" t="n">
-        <v>142.72</v>
+        <v>66.62666666666667</v>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="n">
-        <v>439.8866666666667</v>
-      </c>
-      <c r="E62" t="inlineStr"/>
+        <v>325.96</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.04277266666666667</v>
+      </c>
       <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>39636</v>
+        <v>40063</v>
       </c>
       <c r="B63" t="n">
-        <v>125.4</v>
+        <v>68.05</v>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="n">
-        <v>438.09</v>
-      </c>
-      <c r="E63" t="inlineStr"/>
+        <v>314.24</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.04210366666666666</v>
+      </c>
       <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>39657</v>
+        <v>40091</v>
       </c>
       <c r="B64" t="n">
-        <v>112.1433333333333</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="n">
-        <v>420.3633333333333</v>
-      </c>
-      <c r="E64" t="inlineStr"/>
+        <v>319.3666666666667</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.04244033333333333</v>
+      </c>
       <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>39678</v>
+        <v>40119</v>
       </c>
       <c r="B65" t="n">
-        <v>103.6566666666667</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="n">
-        <v>405.2533333333333</v>
-      </c>
-      <c r="E65" t="inlineStr"/>
+        <v>342.5733333333333</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.040405</v>
+      </c>
       <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>39699</v>
+        <v>40147</v>
       </c>
       <c r="B66" t="n">
-        <v>97.16666666666667</v>
+        <v>77.0675</v>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="n">
-        <v>361.0233333333333</v>
-      </c>
-      <c r="E66" t="inlineStr"/>
+        <v>331.0366666666667</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.04189533333333333</v>
+      </c>
       <c r="F66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>39720</v>
+        <v>40175</v>
       </c>
       <c r="B67" t="n">
-        <v>71.22</v>
+        <v>73.40333333333334</v>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="n">
-        <v>372.3533333333333</v>
-      </c>
-      <c r="E67" t="inlineStr"/>
+        <v>322.5466666666667</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.040587</v>
+      </c>
       <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>39741</v>
+        <v>40203</v>
       </c>
       <c r="B68" t="n">
-        <v>58.50333333333333</v>
-      </c>
-      <c r="C68" t="inlineStr"/>
+        <v>78.47</v>
+      </c>
+      <c r="C68" t="n">
+        <v>12.68582142857143</v>
+      </c>
       <c r="D68" t="n">
-        <v>322.68</v>
-      </c>
-      <c r="E68" t="inlineStr"/>
+        <v>327.9966666666667</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.04129033333333333</v>
+      </c>
       <c r="F68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>39762</v>
+        <v>40231</v>
       </c>
       <c r="B69" t="n">
-        <v>49.81</v>
-      </c>
-      <c r="C69" t="inlineStr"/>
+        <v>80.32000000000001</v>
+      </c>
+      <c r="C69" t="n">
+        <v>11.96021212121212</v>
+      </c>
       <c r="D69" t="n">
-        <v>325.3833333333333</v>
-      </c>
-      <c r="E69" t="inlineStr"/>
+        <v>335.3933333333333</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.039046</v>
+      </c>
       <c r="F69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>39783</v>
+        <v>40259</v>
       </c>
       <c r="B70" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="C70" t="inlineStr"/>
+        <v>84.81666666666666</v>
+      </c>
+      <c r="C70" t="n">
+        <v>13.3196</v>
+      </c>
       <c r="D70" t="n">
-        <v>321.8233333333333</v>
-      </c>
-      <c r="E70" t="inlineStr"/>
+        <v>297.1733333333333</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.03897533333333333</v>
+      </c>
       <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>39804</v>
+        <v>40287</v>
       </c>
       <c r="B71" t="n">
-        <v>43.41333333333333</v>
-      </c>
-      <c r="C71" t="inlineStr"/>
+        <v>75.79333333333334</v>
+      </c>
+      <c r="C71" t="n">
+        <v>15.35393548387097</v>
+      </c>
       <c r="D71" t="n">
-        <v>328.8166666666667</v>
-      </c>
-      <c r="E71" t="inlineStr"/>
+        <v>310.48</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.038129</v>
+      </c>
       <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>39825</v>
+        <v>40315</v>
       </c>
       <c r="B72" t="n">
-        <v>44.50666666666667</v>
-      </c>
-      <c r="C72" t="inlineStr"/>
+        <v>74.91666666666667</v>
+      </c>
+      <c r="C72" t="n">
+        <v>18.02766666666666</v>
+      </c>
       <c r="D72" t="n">
-        <v>285.7933333333334</v>
-      </c>
-      <c r="E72" t="inlineStr"/>
+        <v>295.44</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.03829633333333333</v>
+      </c>
       <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>39846</v>
+        <v>40343</v>
       </c>
       <c r="B73" t="n">
-        <v>41.29</v>
-      </c>
-      <c r="C73" t="inlineStr"/>
+        <v>74.72</v>
+      </c>
+      <c r="C73" t="n">
+        <v>19.59583333333333</v>
+      </c>
       <c r="D73" t="n">
-        <v>268.5166666666667</v>
-      </c>
-      <c r="E73" t="inlineStr"/>
+        <v>309.0366666666667</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.03844366666666667</v>
+      </c>
       <c r="F73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>39867</v>
+        <v>40371</v>
       </c>
       <c r="B74" t="n">
-        <v>44.29666666666667</v>
-      </c>
-      <c r="C74" t="inlineStr"/>
+        <v>80.71333333333332</v>
+      </c>
+      <c r="C74" t="n">
+        <v>18.4716875</v>
+      </c>
       <c r="D74" t="n">
-        <v>283.48</v>
-      </c>
-      <c r="E74" t="inlineStr"/>
+        <v>317.1333333333333</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.03578666666666667</v>
+      </c>
       <c r="F74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>39888</v>
+        <v>40399</v>
       </c>
       <c r="B75" t="n">
-        <v>52.65</v>
-      </c>
-      <c r="C75" t="inlineStr"/>
+        <v>76.80333333333334</v>
+      </c>
+      <c r="C75" t="n">
+        <v>18.53916666666667</v>
+      </c>
       <c r="D75" t="n">
-        <v>303.8233333333333</v>
-      </c>
-      <c r="E75" t="inlineStr"/>
+        <v>303.65</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.03410433333333333</v>
+      </c>
       <c r="F75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>39909</v>
+        <v>40427</v>
       </c>
       <c r="B76" t="n">
-        <v>50.77</v>
-      </c>
-      <c r="C76" t="inlineStr"/>
+        <v>83.43666666666667</v>
+      </c>
+      <c r="C76" t="n">
+        <v>19.15934482758621</v>
+      </c>
       <c r="D76" t="n">
-        <v>308.8633333333333</v>
-      </c>
-      <c r="E76" t="inlineStr"/>
+        <v>317.96</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.03477466666666666</v>
+      </c>
       <c r="F76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>39930</v>
+        <v>40455</v>
       </c>
       <c r="B77" t="n">
-        <v>57.64</v>
-      </c>
-      <c r="C77" t="inlineStr"/>
+        <v>84.13000000000001</v>
+      </c>
+      <c r="C77" t="n">
+        <v>18.9915</v>
+      </c>
       <c r="D77" t="n">
-        <v>303.5566666666667</v>
-      </c>
-      <c r="E77" t="inlineStr"/>
+        <v>304.65</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.03686966666666667</v>
+      </c>
       <c r="F77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>39951</v>
+        <v>40483</v>
       </c>
       <c r="B78" t="n">
-        <v>68.03333333333333</v>
-      </c>
-      <c r="C78" t="inlineStr"/>
+        <v>86.75333333333333</v>
+      </c>
+      <c r="C78" t="n">
+        <v>21.5745</v>
+      </c>
       <c r="D78" t="n">
-        <v>291.8866666666667</v>
-      </c>
-      <c r="E78" t="inlineStr"/>
+        <v>313.19</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.03995433333333333</v>
+      </c>
       <c r="F78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>39972</v>
+        <v>40511</v>
       </c>
       <c r="B79" t="n">
-        <v>70.3</v>
-      </c>
-      <c r="C79" t="inlineStr"/>
+        <v>93.82333333333332</v>
+      </c>
+      <c r="C79" t="n">
+        <v>23.77525806451613</v>
+      </c>
       <c r="D79" t="n">
-        <v>304.03</v>
+        <v>324.58</v>
       </c>
       <c r="E79" t="n">
-        <v>0.046994</v>
+        <v>0.04230933333333333</v>
       </c>
       <c r="F79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>39993</v>
+        <v>40539</v>
       </c>
       <c r="B80" t="n">
-        <v>66.08666666666666</v>
-      </c>
-      <c r="C80" t="inlineStr"/>
+        <v>96.94</v>
+      </c>
+      <c r="C80" t="n">
+        <v>21.69606451612903</v>
+      </c>
       <c r="D80" t="n">
-        <v>309.3133333333333</v>
+        <v>326.8633333333333</v>
       </c>
       <c r="E80" t="n">
-        <v>0.04657233333333333</v>
+        <v>0.04406833333333333</v>
       </c>
       <c r="F80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>40014</v>
+        <v>40567</v>
       </c>
       <c r="B81" t="n">
-        <v>73.53</v>
-      </c>
-      <c r="C81" t="inlineStr"/>
+        <v>104.6666666666667</v>
+      </c>
+      <c r="C81" t="n">
+        <v>21.79871428571429</v>
+      </c>
       <c r="D81" t="n">
-        <v>329.8466666666667</v>
+        <v>314.6566666666666</v>
       </c>
       <c r="E81" t="n">
-        <v>0.045909</v>
+        <v>0.04364466666666666</v>
       </c>
       <c r="F81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>40035</v>
+        <v>40595</v>
       </c>
       <c r="B82" t="n">
-        <v>70.69666666666667</v>
-      </c>
-      <c r="C82" t="inlineStr"/>
+        <v>114.6166666666667</v>
+      </c>
+      <c r="C82" t="n">
+        <v>23.85461290322581</v>
+      </c>
       <c r="D82" t="n">
-        <v>334.6666666666667</v>
+        <v>322.0633333333333</v>
       </c>
       <c r="E82" t="n">
-        <v>0.04338066666666666</v>
+        <v>0.04427200000000001</v>
       </c>
       <c r="F82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>40056</v>
+        <v>40623</v>
       </c>
       <c r="B83" t="n">
-        <v>69.56666666666666</v>
-      </c>
-      <c r="C83" t="inlineStr"/>
+        <v>122.2233333333333</v>
+      </c>
+      <c r="C83" t="n">
+        <v>23.788</v>
+      </c>
       <c r="D83" t="n">
-        <v>319.7166666666667</v>
+        <v>310.94</v>
       </c>
       <c r="E83" t="n">
-        <v>0.04394533333333333</v>
+        <v>0.04414266666666666</v>
       </c>
       <c r="F83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>40077</v>
+        <v>40651</v>
       </c>
       <c r="B84" t="n">
-        <v>70.90666666666667</v>
-      </c>
-      <c r="C84" t="inlineStr"/>
+        <v>113.0966666666667</v>
+      </c>
+      <c r="C84" t="n">
+        <v>23.405</v>
+      </c>
       <c r="D84" t="n">
-        <v>318.97</v>
+        <v>299.8533333333333</v>
       </c>
       <c r="E84" t="n">
-        <v>0.04274466666666666</v>
-      </c>
-      <c r="F84" t="inlineStr"/>
+        <v>0.04220433333333334</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.035775</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>40098</v>
+        <v>40679</v>
       </c>
       <c r="B85" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="C85" t="inlineStr"/>
+        <v>118.9933333333333</v>
+      </c>
+      <c r="C85" t="n">
+        <v>23.164</v>
+      </c>
       <c r="D85" t="n">
-        <v>319.3666666666667</v>
+        <v>288.4133333333334</v>
       </c>
       <c r="E85" t="n">
-        <v>0.04244033333333333</v>
-      </c>
-      <c r="F85" t="inlineStr"/>
+        <v>0.04135933333333333</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.035036</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>40119</v>
+        <v>40707</v>
       </c>
       <c r="B86" t="n">
-        <v>77.37333333333333</v>
-      </c>
-      <c r="C86" t="inlineStr"/>
+        <v>117.6033333333333</v>
+      </c>
+      <c r="C86" t="n">
+        <v>22.29713793103448</v>
+      </c>
       <c r="D86" t="n">
-        <v>333.7166666666666</v>
+        <v>259.02</v>
       </c>
       <c r="E86" t="n">
-        <v>0.041447</v>
-      </c>
-      <c r="F86" t="inlineStr"/>
+        <v>0.04113333333333333</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.03460103448275862</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>40140</v>
+        <v>40735</v>
       </c>
       <c r="B87" t="n">
-        <v>71.88666666666667</v>
-      </c>
-      <c r="C87" t="inlineStr"/>
+        <v>105.6166666666667</v>
+      </c>
+      <c r="C87" t="n">
+        <v>23.48245454545454</v>
+      </c>
       <c r="D87" t="n">
-        <v>342.0766666666667</v>
+        <v>242.1833333333333</v>
       </c>
       <c r="E87" t="n">
-        <v>0.04086466666666667</v>
-      </c>
-      <c r="F87" t="inlineStr"/>
+        <v>0.03937866666666667</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.03188727272727272</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>40161</v>
+        <v>40763</v>
       </c>
       <c r="B88" t="n">
-        <v>79.57250000000001</v>
-      </c>
-      <c r="C88" t="inlineStr"/>
+        <v>110.83</v>
+      </c>
+      <c r="C88" t="n">
+        <v>26.8054</v>
+      </c>
       <c r="D88" t="n">
-        <v>328.4966666666667</v>
+        <v>276.5766666666667</v>
       </c>
       <c r="E88" t="n">
-        <v>0.04243633333333334</v>
-      </c>
-      <c r="F88" t="inlineStr"/>
+        <v>0.038202</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.029304</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>40182</v>
+        <v>40791</v>
       </c>
       <c r="B89" t="n">
-        <v>73.40333333333334</v>
-      </c>
-      <c r="C89" t="inlineStr"/>
+        <v>102.06</v>
+      </c>
+      <c r="C89" t="n">
+        <v>26.6098064516129</v>
+      </c>
       <c r="D89" t="n">
-        <v>322.5466666666667</v>
+        <v>264.7033333333333</v>
       </c>
       <c r="E89" t="n">
-        <v>0.040587</v>
-      </c>
-      <c r="F89" t="inlineStr"/>
+        <v>0.04002033333333334</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.02774129032258064</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>40203</v>
+        <v>40819</v>
       </c>
       <c r="B90" t="n">
-        <v>72.64</v>
+        <v>109.6766666666667</v>
       </c>
       <c r="C90" t="n">
-        <v>13.34357142857143</v>
+        <v>25.65509677419355</v>
       </c>
       <c r="D90" t="n">
-        <v>331.0133333333333</v>
+        <v>263.0766666666667</v>
       </c>
       <c r="E90" t="n">
-        <v>0.04084566666666667</v>
-      </c>
-      <c r="F90" t="inlineStr"/>
+        <v>0.04050933333333333</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.02915935483870968</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>40224</v>
+        <v>40847</v>
       </c>
       <c r="B91" t="n">
-        <v>80.27666666666667</v>
+        <v>108.1333333333333</v>
       </c>
       <c r="C91" t="n">
-        <v>12.11590909090909</v>
+        <v>24.118</v>
       </c>
       <c r="D91" t="n">
-        <v>340.7033333333333</v>
+        <v>266.2</v>
       </c>
       <c r="E91" t="n">
-        <v>0.03988966666666666</v>
-      </c>
-      <c r="F91" t="inlineStr"/>
+        <v>0.03973533333333333</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.033737</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>40245</v>
+        <v>40875</v>
       </c>
       <c r="B92" t="n">
-        <v>80.54333333333334</v>
+        <v>108.615</v>
       </c>
       <c r="C92" t="n">
-        <v>11.88236363636364</v>
+        <v>22.62766666666667</v>
       </c>
       <c r="D92" t="n">
-        <v>325.7066666666667</v>
+        <v>262.7866666666667</v>
       </c>
       <c r="E92" t="n">
-        <v>0.03966066666666666</v>
-      </c>
-      <c r="F92" t="inlineStr"/>
+        <v>0.036396</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.02983166666666667</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>40266</v>
+        <v>40903</v>
       </c>
       <c r="B93" t="n">
-        <v>84.81666666666666</v>
+        <v>110.34</v>
       </c>
       <c r="C93" t="n">
-        <v>13.3196</v>
+        <v>22.8301875</v>
       </c>
       <c r="D93" t="n">
-        <v>297.1733333333333</v>
+        <v>264.69</v>
       </c>
       <c r="E93" t="n">
-        <v>0.03897533333333333</v>
-      </c>
-      <c r="F93" t="inlineStr"/>
+        <v>0.035447</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.0283678125</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>40287</v>
+        <v>40931</v>
       </c>
       <c r="B94" t="n">
-        <v>79.50333333333333</v>
+        <v>119.8933333333333</v>
       </c>
       <c r="C94" t="n">
-        <v>14.89283870967742</v>
+        <v>23.90206896551724</v>
       </c>
       <c r="D94" t="n">
-        <v>301.7966666666667</v>
+        <v>267.9533333333333</v>
       </c>
       <c r="E94" t="n">
-        <v>0.038558</v>
-      </c>
-      <c r="F94" t="inlineStr"/>
+        <v>0.03598633333333334</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.02787137931034483</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>40308</v>
+        <v>40959</v>
       </c>
       <c r="B95" t="n">
-        <v>74.44</v>
+        <v>125.7433333333333</v>
       </c>
       <c r="C95" t="n">
-        <v>16.27612903225806</v>
+        <v>24.8908</v>
       </c>
       <c r="D95" t="n">
-        <v>285.96</v>
+        <v>257.3233333333333</v>
       </c>
       <c r="E95" t="n">
-        <v>0.03794</v>
-      </c>
-      <c r="F95" t="inlineStr"/>
+        <v>0.03419266666666667</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.02734</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>40329</v>
+        <v>40987</v>
       </c>
       <c r="B96" t="n">
-        <v>78.61999999999999</v>
+        <v>119.73</v>
       </c>
       <c r="C96" t="n">
-        <v>18.93533333333333</v>
+        <v>25.21838709677419</v>
       </c>
       <c r="D96" t="n">
-        <v>300.77</v>
+        <v>248.4266666666666</v>
       </c>
       <c r="E96" t="n">
-        <v>0.03933433333333333</v>
-      </c>
-      <c r="F96" t="inlineStr"/>
+        <v>0.031259</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.02698193548387097</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>40350</v>
+        <v>41015</v>
       </c>
       <c r="B97" t="n">
-        <v>74.72</v>
+        <v>111.8</v>
       </c>
       <c r="C97" t="n">
-        <v>19.59583333333333</v>
+        <v>24.55754838709677</v>
       </c>
       <c r="D97" t="n">
-        <v>309.0366666666667</v>
+        <v>251.4133333333333</v>
       </c>
       <c r="E97" t="n">
-        <v>0.03844366666666667</v>
-      </c>
-      <c r="F97" t="inlineStr"/>
+        <v>0.029234</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.02478903225806452</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>40371</v>
+        <v>41043</v>
       </c>
       <c r="B98" t="n">
-        <v>79.94</v>
+        <v>98.48999999999999</v>
       </c>
       <c r="C98" t="n">
-        <v>18.491375</v>
+        <v>23.76524137931034</v>
       </c>
       <c r="D98" t="n">
-        <v>309.1666666666667</v>
+        <v>255.4266666666667</v>
       </c>
       <c r="E98" t="n">
-        <v>0.03757166666666667</v>
-      </c>
-      <c r="F98" t="inlineStr"/>
+        <v>0.02770233333333333</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.02283862068965517</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>40392</v>
+        <v>41071</v>
       </c>
       <c r="B99" t="n">
-        <v>73.83333333333334</v>
+        <v>99.61</v>
       </c>
       <c r="C99" t="n">
-        <v>18.4323125</v>
+        <v>23.9921875</v>
       </c>
       <c r="D99" t="n">
-        <v>304.2433333333333</v>
+        <v>268.4366666666667</v>
       </c>
       <c r="E99" t="n">
-        <v>0.03344466666666667</v>
-      </c>
-      <c r="F99" t="inlineStr"/>
+        <v>0.026128</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.02358</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>40413</v>
+        <v>41099</v>
       </c>
       <c r="B100" t="n">
-        <v>78.73999999999999</v>
+        <v>109.3466666666667</v>
       </c>
       <c r="C100" t="n">
-        <v>18.7242</v>
+        <v>24.32370967741936</v>
       </c>
       <c r="D100" t="n">
-        <v>307.7766666666666</v>
+        <v>277.4566666666667</v>
       </c>
       <c r="E100" t="n">
-        <v>0.03498266666666667</v>
-      </c>
-      <c r="F100" t="inlineStr"/>
+        <v>0.02479666666666666</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.02057483870967742</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>40434</v>
+        <v>41127</v>
       </c>
       <c r="B101" t="n">
-        <v>83.43666666666667</v>
+        <v>115.3766666666667</v>
       </c>
       <c r="C101" t="n">
-        <v>19.15934482758621</v>
+        <v>25.55757142857143</v>
       </c>
       <c r="D101" t="n">
-        <v>317.96</v>
+        <v>267.96</v>
       </c>
       <c r="E101" t="n">
-        <v>0.03477466666666666</v>
-      </c>
-      <c r="F101" t="inlineStr"/>
+        <v>0.023189</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.01933214285714285</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>40455</v>
+        <v>41155</v>
       </c>
       <c r="B102" t="n">
-        <v>83.34666666666666</v>
+        <v>112.2566666666667</v>
       </c>
       <c r="C102" t="n">
-        <v>18.87475862068965</v>
+        <v>26.52348484848485</v>
       </c>
       <c r="D102" t="n">
-        <v>308.21</v>
+        <v>259.3733333333333</v>
       </c>
       <c r="E102" t="n">
-        <v>0.03659766666666667</v>
-      </c>
-      <c r="F102" t="inlineStr"/>
+        <v>0.02623466666666667</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.01974212121212121</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>40476</v>
+        <v>41183</v>
       </c>
       <c r="B103" t="n">
-        <v>86.58</v>
+        <v>109.4766666666667</v>
       </c>
       <c r="C103" t="n">
-        <v>20.283</v>
+        <v>27.20227272727272</v>
       </c>
       <c r="D103" t="n">
-        <v>311.2266666666667</v>
+        <v>253.95</v>
       </c>
       <c r="E103" t="n">
-        <v>0.03760133333333333</v>
-      </c>
-      <c r="F103" t="inlineStr"/>
+        <v>0.025968</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.01963181818181818</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>40497</v>
+        <v>41211</v>
       </c>
       <c r="B104" t="n">
-        <v>91.44</v>
+        <v>111.0733333333333</v>
       </c>
       <c r="C104" t="n">
-        <v>22.14674193548387</v>
+        <v>27.5875</v>
       </c>
       <c r="D104" t="n">
-        <v>315.9366666666667</v>
+        <v>261.0833333333333</v>
       </c>
       <c r="E104" t="n">
-        <v>0.04082233333333333</v>
-      </c>
-      <c r="F104" t="inlineStr"/>
+        <v>0.02477366666666667</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.01866166666666667</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>40518</v>
+        <v>41239</v>
       </c>
       <c r="B105" t="n">
-        <v>93.82333333333332</v>
+        <v>108.8566666666667</v>
       </c>
       <c r="C105" t="n">
-        <v>23.77525806451613</v>
+        <v>26.70106451612903</v>
       </c>
       <c r="D105" t="n">
-        <v>324.58</v>
+        <v>246.9233333333333</v>
       </c>
       <c r="E105" t="n">
-        <v>0.04230933333333333</v>
-      </c>
-      <c r="F105" t="inlineStr"/>
+        <v>0.02434633333333333</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.01748322580645161</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>40539</v>
+        <v>41267</v>
       </c>
       <c r="B106" t="n">
-        <v>97.84666666666668</v>
+        <v>111.77</v>
       </c>
       <c r="C106" t="n">
-        <v>22.44687096774194</v>
+        <v>25.85487096774193</v>
       </c>
       <c r="D106" t="n">
-        <v>336.27</v>
+        <v>252.4533333333333</v>
       </c>
       <c r="E106" t="n">
-        <v>0.04325433333333333</v>
-      </c>
-      <c r="F106" t="inlineStr"/>
+        <v>0.02563433333333333</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.01949483870967742</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>40560</v>
+        <v>41295</v>
       </c>
       <c r="B107" t="n">
-        <v>99.44333333333333</v>
+        <v>117.4733333333333</v>
       </c>
       <c r="C107" t="n">
-        <v>21.12621428571429</v>
+        <v>25.96078571428572</v>
       </c>
       <c r="D107" t="n">
-        <v>317.7133333333334</v>
+        <v>257.9766666666667</v>
       </c>
       <c r="E107" t="n">
-        <v>0.04458400000000001</v>
-      </c>
-      <c r="F107" t="inlineStr"/>
+        <v>0.02647366666666667</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.01983071428571429</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>40581</v>
+        <v>41323</v>
       </c>
       <c r="B108" t="n">
-        <v>111.9133333333333</v>
+        <v>109.6133333333333</v>
       </c>
       <c r="C108" t="n">
-        <v>22.13496428571429</v>
+        <v>26.85020689655173</v>
       </c>
       <c r="D108" t="n">
-        <v>320.3633333333333</v>
+        <v>272.4433333333333</v>
       </c>
       <c r="E108" t="n">
-        <v>0.04349766666666667</v>
-      </c>
-      <c r="F108" t="inlineStr"/>
+        <v>0.02355233333333333</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.01882310344827586</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>40602</v>
+        <v>41351</v>
       </c>
       <c r="B109" t="n">
-        <v>114.6166666666667</v>
+        <v>101.2966666666667</v>
       </c>
       <c r="C109" t="n">
-        <v>23.85461290322581</v>
+        <v>26.8565</v>
       </c>
       <c r="D109" t="n">
-        <v>322.0633333333333</v>
+        <v>264.71</v>
       </c>
       <c r="E109" t="n">
-        <v>0.04427200000000001</v>
-      </c>
-      <c r="F109" t="inlineStr"/>
+        <v>0.02235366666666667</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.017265</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>40623</v>
+        <v>41379</v>
       </c>
       <c r="B110" t="n">
-        <v>124.87</v>
+        <v>103.1833333333333</v>
       </c>
       <c r="C110" t="n">
-        <v>24.194</v>
+        <v>26.377</v>
       </c>
       <c r="D110" t="n">
-        <v>315.15</v>
+        <v>249.95</v>
       </c>
       <c r="E110" t="n">
-        <v>0.04605433333333334</v>
-      </c>
-      <c r="F110" t="inlineStr"/>
+        <v>0.02258266666666667</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.01696709677419355</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>40644</v>
+        <v>41407</v>
       </c>
       <c r="B111" t="n">
-        <v>125.3766666666667</v>
+        <v>104.1533333333333</v>
       </c>
       <c r="C111" t="n">
-        <v>23.131125</v>
+        <v>26.2975</v>
       </c>
       <c r="D111" t="n">
-        <v>303.81</v>
+        <v>257.2833333333334</v>
       </c>
       <c r="E111" t="n">
-        <v>0.04355833333333334</v>
+        <v>0.02415</v>
       </c>
       <c r="F111" t="n">
-        <v>0.036733125</v>
+        <v>0.01938821428571429</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>40665</v>
+        <v>41435</v>
       </c>
       <c r="B112" t="n">
-        <v>110.8633333333333</v>
+        <v>107.5266666666667</v>
       </c>
       <c r="C112" t="n">
-        <v>23.5419375</v>
+        <v>26.20636363636364</v>
       </c>
       <c r="D112" t="n">
-        <v>296.8333333333334</v>
+        <v>259.2566666666667</v>
       </c>
       <c r="E112" t="n">
-        <v>0.04160766666666667</v>
+        <v>0.02598</v>
       </c>
       <c r="F112" t="n">
-        <v>0.0352959375</v>
+        <v>0.02117545454545455</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>40686</v>
+        <v>41463</v>
       </c>
       <c r="B113" t="n">
-        <v>118.9933333333333</v>
+        <v>108.7833333333333</v>
       </c>
       <c r="C113" t="n">
-        <v>23.164</v>
+        <v>26.09253333333333</v>
       </c>
       <c r="D113" t="n">
-        <v>288.4133333333334</v>
+        <v>274.3566666666667</v>
       </c>
       <c r="E113" t="n">
-        <v>0.04135933333333333</v>
+        <v>0.02551433333333333</v>
       </c>
       <c r="F113" t="n">
-        <v>0.035036</v>
+        <v>0.02128066666666667</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>40707</v>
+        <v>41491</v>
       </c>
       <c r="B114" t="n">
-        <v>111.5166666666667</v>
+        <v>114.2233333333333</v>
       </c>
       <c r="C114" t="n">
-        <v>22.32224137931034</v>
+        <v>26.16932258064516</v>
       </c>
       <c r="D114" t="n">
-        <v>257.0866666666666</v>
+        <v>279.9933333333333</v>
       </c>
       <c r="E114" t="n">
-        <v>0.04306833333333333</v>
+        <v>0.02733666666666667</v>
       </c>
       <c r="F114" t="n">
-        <v>0.03527931034482758</v>
+        <v>0.02233967741935484</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>40728</v>
+        <v>41519</v>
       </c>
       <c r="B115" t="n">
-        <v>118.1833333333333</v>
+        <v>108.4566666666667</v>
       </c>
       <c r="C115" t="n">
-        <v>22.24693103448276</v>
+        <v>27.01383870967742</v>
       </c>
       <c r="D115" t="n">
-        <v>255.5433333333333</v>
+        <v>279.32</v>
       </c>
       <c r="E115" t="n">
-        <v>0.04229266666666667</v>
+        <v>0.026029</v>
       </c>
       <c r="F115" t="n">
-        <v>0.03324448275862069</v>
+        <v>0.02163516129032258</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>40749</v>
+        <v>41547</v>
       </c>
       <c r="B116" t="n">
-        <v>109.2833333333333</v>
+        <v>108.7166666666667</v>
       </c>
       <c r="C116" t="n">
-        <v>24.45736363636363</v>
+        <v>27.071</v>
       </c>
       <c r="D116" t="n">
-        <v>259.2866666666667</v>
+        <v>266.7466666666667</v>
       </c>
       <c r="E116" t="n">
-        <v>0.04092166666666667</v>
+        <v>0.02592033333333333</v>
       </c>
       <c r="F116" t="n">
-        <v>0.03120848484848485</v>
+        <v>0.02051258064516129</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>40770</v>
+        <v>41575</v>
       </c>
       <c r="B117" t="n">
-        <v>110.83</v>
+        <v>111.0166666666667</v>
       </c>
       <c r="C117" t="n">
-        <v>26.8054</v>
+        <v>28.07141379310345</v>
       </c>
       <c r="D117" t="n">
-        <v>276.5766666666667</v>
+        <v>279.2966666666667</v>
       </c>
       <c r="E117" t="n">
-        <v>0.038202</v>
+        <v>0.025871</v>
       </c>
       <c r="F117" t="n">
-        <v>0.029304</v>
+        <v>0.02035</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>40791</v>
+        <v>41603</v>
       </c>
       <c r="B118" t="n">
-        <v>103.95</v>
+        <v>111.63</v>
       </c>
       <c r="C118" t="n">
-        <v>26.7025</v>
+        <v>27.75503125</v>
       </c>
       <c r="D118" t="n">
-        <v>262.7033333333333</v>
+        <v>285.04</v>
       </c>
       <c r="E118" t="n">
-        <v>0.038032</v>
+        <v>0.027379</v>
       </c>
       <c r="F118" t="n">
-        <v>0.02796</v>
+        <v>0.0217659375</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>40812</v>
+        <v>41631</v>
       </c>
       <c r="B119" t="n">
-        <v>111.6666666666667</v>
+        <v>106.3933333333333</v>
       </c>
       <c r="C119" t="n">
-        <v>26.13245161290322</v>
+        <v>26.01958064516129</v>
       </c>
       <c r="D119" t="n">
-        <v>250.15</v>
+        <v>298.69</v>
       </c>
       <c r="E119" t="n">
-        <v>0.04124666666666667</v>
+        <v>0.02593333333333333</v>
       </c>
       <c r="F119" t="n">
-        <v>0.02845032258064516</v>
+        <v>0.02078774193548387</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>40833</v>
+        <v>41659</v>
       </c>
       <c r="B120" t="n">
-        <v>113.6966666666667</v>
+        <v>109.1466666666667</v>
       </c>
       <c r="C120" t="n">
-        <v>25.287</v>
+        <v>23.93357142857143</v>
       </c>
       <c r="D120" t="n">
-        <v>255.3066666666667</v>
+        <v>304.8066666666667</v>
       </c>
       <c r="E120" t="n">
-        <v>0.038524</v>
+        <v>0.02482466666666667</v>
       </c>
       <c r="F120" t="n">
-        <v>0.030216</v>
+        <v>0.01965428571428571</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>40854</v>
+        <v>41687</v>
       </c>
       <c r="B121" t="n">
-        <v>108.1333333333333</v>
+        <v>107.0166666666667</v>
       </c>
       <c r="C121" t="n">
-        <v>24.118</v>
+        <v>22.09993548387097</v>
       </c>
       <c r="D121" t="n">
-        <v>266.2</v>
+        <v>307.7633333333333</v>
       </c>
       <c r="E121" t="n">
-        <v>0.03973533333333333</v>
+        <v>0.023681</v>
       </c>
       <c r="F121" t="n">
-        <v>0.033737</v>
+        <v>0.01919967741935484</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>40875</v>
+        <v>41715</v>
       </c>
       <c r="B122" t="n">
-        <v>103.5433333333333</v>
+        <v>108.49</v>
       </c>
       <c r="C122" t="n">
-        <v>22.9982</v>
+        <v>20.5336</v>
       </c>
       <c r="D122" t="n">
-        <v>254.15</v>
+        <v>318.8933333333333</v>
       </c>
       <c r="E122" t="n">
-        <v>0.03603133333333333</v>
+        <v>0.023337</v>
       </c>
       <c r="F122" t="n">
-        <v>0.031066</v>
+        <v>0.018513</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>40896</v>
+        <v>41743</v>
       </c>
       <c r="B123" t="n">
-        <v>112.6533333333333</v>
+        <v>108.2366666666667</v>
       </c>
       <c r="C123" t="n">
-        <v>22.5458125</v>
+        <v>19.45393333333333</v>
       </c>
       <c r="D123" t="n">
-        <v>263.3366666666666</v>
+        <v>323.2833333333333</v>
       </c>
       <c r="E123" t="n">
-        <v>0.034397</v>
+        <v>0.02220433333333333</v>
       </c>
       <c r="F123" t="n">
-        <v>0.0287221875</v>
+        <v>0.01739666666666667</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>40917</v>
+        <v>41771</v>
       </c>
       <c r="B124" t="n">
-        <v>110.9866666666667</v>
+        <v>109.53</v>
       </c>
       <c r="C124" t="n">
-        <v>22.972375</v>
+        <v>18.51945161290323</v>
       </c>
       <c r="D124" t="n">
-        <v>265.9</v>
+        <v>312.4833333333333</v>
       </c>
       <c r="E124" t="n">
-        <v>0.034386</v>
+        <v>0.02089833333333333</v>
       </c>
       <c r="F124" t="n">
-        <v>0.028190625</v>
+        <v>0.01591354838709677</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>40938</v>
+        <v>41799</v>
       </c>
       <c r="B125" t="n">
-        <v>119.8933333333333</v>
+        <v>110.3733333333333</v>
       </c>
       <c r="C125" t="n">
-        <v>23.90206896551724</v>
+        <v>17.53041935483871</v>
       </c>
       <c r="D125" t="n">
-        <v>267.9533333333333</v>
+        <v>318.23</v>
       </c>
       <c r="E125" t="n">
-        <v>0.03598633333333334</v>
+        <v>0.01987433333333333</v>
       </c>
       <c r="F125" t="n">
-        <v>0.02787137931034483</v>
+        <v>0.01471870967741935</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>40959</v>
+        <v>41827</v>
       </c>
       <c r="B126" t="n">
-        <v>125.5533333333333</v>
+        <v>105.22</v>
       </c>
       <c r="C126" t="n">
-        <v>24.68826666666667</v>
+        <v>18.89027586206896</v>
       </c>
       <c r="D126" t="n">
-        <v>257.7566666666667</v>
+        <v>321.1366666666667</v>
       </c>
       <c r="E126" t="n">
-        <v>0.03216266666666667</v>
+        <v>0.01870933333333333</v>
       </c>
       <c r="F126" t="n">
-        <v>0.02749166666666667</v>
+        <v>0.01355724137931034</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>40980</v>
+        <v>41855</v>
       </c>
       <c r="B127" t="n">
-        <v>124.58</v>
+        <v>102.9233333333333</v>
       </c>
       <c r="C127" t="n">
-        <v>25.23554838709677</v>
+        <v>22.1573125</v>
       </c>
       <c r="D127" t="n">
-        <v>254.6433333333333</v>
+        <v>308.1733333333333</v>
       </c>
       <c r="E127" t="n">
-        <v>0.03243366666666667</v>
+        <v>0.01638233333333334</v>
       </c>
       <c r="F127" t="n">
-        <v>0.02706774193548387</v>
+        <v>0.010793125</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>41001</v>
+        <v>41883</v>
       </c>
       <c r="B128" t="n">
-        <v>118.7266666666667</v>
+        <v>97.13333333333334</v>
       </c>
       <c r="C128" t="n">
-        <v>25.2098064516129</v>
+        <v>23.9396875</v>
       </c>
       <c r="D128" t="n">
-        <v>238.53</v>
+        <v>314.26</v>
       </c>
       <c r="E128" t="n">
-        <v>0.03115366666666667</v>
+        <v>0.01626333333333333</v>
       </c>
       <c r="F128" t="n">
-        <v>0.02693903225806452</v>
+        <v>0.011256875</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>41022</v>
+        <v>41911</v>
       </c>
       <c r="B129" t="n">
-        <v>111.8</v>
+        <v>85.92999999999999</v>
       </c>
       <c r="C129" t="n">
-        <v>24.55754838709677</v>
+        <v>23.04796774193548</v>
       </c>
       <c r="D129" t="n">
-        <v>251.4133333333333</v>
+        <v>314.5533333333333</v>
       </c>
       <c r="E129" t="n">
-        <v>0.029234</v>
+        <v>0.01571466666666667</v>
       </c>
       <c r="F129" t="n">
-        <v>0.02478903225806452</v>
+        <v>0.01058548387096774</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>41043</v>
+        <v>41939</v>
       </c>
       <c r="B130" t="n">
-        <v>98.70999999999999</v>
+        <v>79.90666666666667</v>
       </c>
       <c r="C130" t="n">
-        <v>23.6971724137931</v>
+        <v>23.96503571428572</v>
       </c>
       <c r="D130" t="n">
-        <v>260.8566666666667</v>
+        <v>315.22</v>
       </c>
       <c r="E130" t="n">
-        <v>0.02682233333333333</v>
+        <v>0.01466633333333334</v>
       </c>
       <c r="F130" t="n">
-        <v>0.02216758620689655</v>
+        <v>0.009217857142857142</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>41064</v>
+        <v>41967</v>
       </c>
       <c r="B131" t="n">
-        <v>91</v>
+        <v>60.53333333333333</v>
       </c>
       <c r="C131" t="n">
-        <v>23.90137931034483</v>
+        <v>22.17812121212121</v>
       </c>
       <c r="D131" t="n">
-        <v>254.3566666666667</v>
+        <v>319.9066666666667</v>
       </c>
       <c r="E131" t="n">
-        <v>0.029016</v>
+        <v>0.013253</v>
       </c>
       <c r="F131" t="n">
-        <v>0.02418068965517241</v>
+        <v>0.008043939393939395</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>41085</v>
+        <v>41995</v>
       </c>
       <c r="B132" t="n">
-        <v>103.1666666666667</v>
+        <v>49.28333333333334</v>
       </c>
       <c r="C132" t="n">
-        <v>24.025</v>
+        <v>20.6774</v>
       </c>
       <c r="D132" t="n">
-        <v>263.2566666666667</v>
+        <v>325.4566666666666</v>
       </c>
       <c r="E132" t="n">
-        <v>0.025059</v>
+        <v>0.011494</v>
       </c>
       <c r="F132" t="n">
-        <v>0.02274</v>
+        <v>0.006402000000000001</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>41106</v>
+        <v>42023</v>
       </c>
       <c r="B133" t="n">
-        <v>109.3466666666667</v>
+        <v>61.44</v>
       </c>
       <c r="C133" t="n">
-        <v>24.32370967741936</v>
+        <v>21.85985714285714</v>
       </c>
       <c r="D133" t="n">
-        <v>277.4566666666667</v>
+        <v>335.5933333333333</v>
       </c>
       <c r="E133" t="n">
-        <v>0.02479666666666666</v>
+        <v>0.01033666666666667</v>
       </c>
       <c r="F133" t="n">
-        <v>0.02057483870967742</v>
+        <v>0.005055714285714286</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>41127</v>
+        <v>42051</v>
       </c>
       <c r="B134" t="n">
-        <v>112.7033333333333</v>
+        <v>53.85</v>
       </c>
       <c r="C134" t="n">
-        <v>25.26329032258064</v>
+        <v>22.3115</v>
       </c>
       <c r="D134" t="n">
-        <v>271.5133333333334</v>
+        <v>332.8366666666667</v>
       </c>
       <c r="E134" t="n">
-        <v>0.02321366666666667</v>
+        <v>0.01010366666666667</v>
       </c>
       <c r="F134" t="n">
-        <v>0.01954516129032258</v>
+        <v>0.003485</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>41148</v>
+        <v>42079</v>
       </c>
       <c r="B135" t="n">
-        <v>114.7466666666667</v>
+        <v>57.91</v>
       </c>
       <c r="C135" t="n">
-        <v>26.05157142857143</v>
+        <v>21.1314</v>
       </c>
       <c r="D135" t="n">
-        <v>268.7633333333333</v>
+        <v>319.97</v>
       </c>
       <c r="E135" t="n">
-        <v>0.02690266666666667</v>
+        <v>0.009583666666666667</v>
       </c>
       <c r="F135" t="n">
-        <v>0.01955714285714286</v>
+        <v>0.003036</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>41169</v>
+        <v>42107</v>
       </c>
       <c r="B136" t="n">
-        <v>111.8866666666667</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="C136" t="n">
-        <v>26.69318181818182</v>
+        <v>20.39731034482759</v>
       </c>
       <c r="D136" t="n">
-        <v>249</v>
+        <v>317.1433333333333</v>
       </c>
       <c r="E136" t="n">
-        <v>0.02629666666666667</v>
+        <v>0.013294</v>
       </c>
       <c r="F136" t="n">
-        <v>0.01971454545454545</v>
+        <v>0.004946896551724138</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>41190</v>
+        <v>42135</v>
       </c>
       <c r="B137" t="n">
-        <v>109.4766666666667</v>
+        <v>62.89666666666667</v>
       </c>
       <c r="C137" t="n">
-        <v>27.20227272727272</v>
+        <v>20.3030625</v>
       </c>
       <c r="D137" t="n">
-        <v>253.95</v>
+        <v>325.7966666666667</v>
       </c>
       <c r="E137" t="n">
-        <v>0.025968</v>
+        <v>0.016596</v>
       </c>
       <c r="F137" t="n">
-        <v>0.01963181818181818</v>
+        <v>0.0074728125</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>41211</v>
+        <v>42163</v>
       </c>
       <c r="B138" t="n">
-        <v>110.7833333333333</v>
+        <v>57.8</v>
       </c>
       <c r="C138" t="n">
-        <v>27.5</v>
+        <v>20.46303225806452</v>
       </c>
       <c r="D138" t="n">
-        <v>261.9866666666667</v>
+        <v>291.21</v>
       </c>
       <c r="E138" t="n">
-        <v>0.024136</v>
+        <v>0.01678366666666667</v>
       </c>
       <c r="F138" t="n">
-        <v>0.01893</v>
+        <v>0.009692258064516127</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>41232</v>
+        <v>42191</v>
       </c>
       <c r="B139" t="n">
-        <v>107.2266666666667</v>
+        <v>50.41666666666667</v>
       </c>
       <c r="C139" t="n">
-        <v>27.27867741935484</v>
+        <v>20.42870967741936</v>
       </c>
       <c r="D139" t="n">
-        <v>254.9266666666667</v>
+        <v>290.4966666666667</v>
       </c>
       <c r="E139" t="n">
-        <v>0.02369933333333333</v>
+        <v>0.014725</v>
       </c>
       <c r="F139" t="n">
-        <v>0.01808387096774194</v>
+        <v>0.008085806451612904</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>41253</v>
+        <v>42219</v>
       </c>
       <c r="B140" t="n">
-        <v>110.9466666666667</v>
+        <v>52.78333333333333</v>
       </c>
       <c r="C140" t="n">
-        <v>26.41225806451613</v>
+        <v>19.29064516129032</v>
       </c>
       <c r="D140" t="n">
-        <v>250.36</v>
+        <v>311.97</v>
       </c>
       <c r="E140" t="n">
-        <v>0.02375366666666667</v>
+        <v>0.016024</v>
       </c>
       <c r="F140" t="n">
-        <v>0.01718290322580645</v>
+        <v>0.00872709677419355</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>41274</v>
+        <v>42247</v>
       </c>
       <c r="B141" t="n">
-        <v>111.77</v>
+        <v>47.76000000000001</v>
       </c>
       <c r="C141" t="n">
-        <v>25.85487096774193</v>
+        <v>18.7253</v>
       </c>
       <c r="D141" t="n">
-        <v>252.4533333333333</v>
+        <v>313.7233333333334</v>
       </c>
       <c r="E141" t="n">
-        <v>0.02563433333333333</v>
+        <v>0.016208</v>
       </c>
       <c r="F141" t="n">
-        <v>0.01949483870967742</v>
+        <v>0.008425999999999999</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>41295</v>
+        <v>42275</v>
       </c>
       <c r="B142" t="n">
-        <v>118.3866666666667</v>
+        <v>47.69</v>
       </c>
       <c r="C142" t="n">
-        <v>25.80028571428571</v>
+        <v>18.102</v>
       </c>
       <c r="D142" t="n">
-        <v>254.0866666666667</v>
+        <v>302.52</v>
       </c>
       <c r="E142" t="n">
-        <v>0.02640266666666667</v>
+        <v>0.01517033333333333</v>
       </c>
       <c r="F142" t="n">
-        <v>0.02022571428571429</v>
+        <v>0.007873333333333333</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>41316</v>
+        <v>42303</v>
       </c>
       <c r="B143" t="n">
-        <v>110.1933333333333</v>
+        <v>44.77333333333333</v>
       </c>
       <c r="C143" t="n">
-        <v>26.32544827586207</v>
+        <v>18.01570967741936</v>
       </c>
       <c r="D143" t="n">
-        <v>257.45</v>
+        <v>291.7766666666666</v>
       </c>
       <c r="E143" t="n">
-        <v>0.02442166666666666</v>
+        <v>0.01445966666666667</v>
       </c>
       <c r="F143" t="n">
-        <v>0.01914172413793104</v>
+        <v>0.007228387096774193</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>41337</v>
+        <v>42331</v>
       </c>
       <c r="B144" t="n">
-        <v>108</v>
+        <v>36.52666666666667</v>
       </c>
       <c r="C144" t="n">
-        <v>27.11258620689655</v>
+        <v>15.93532258064516</v>
       </c>
       <c r="D144" t="n">
-        <v>270.8933333333334</v>
+        <v>282.1733333333333</v>
       </c>
       <c r="E144" t="n">
-        <v>0.02318933333333333</v>
+        <v>0.01515733333333333</v>
       </c>
       <c r="F144" t="n">
-        <v>0.01866379310344828</v>
+        <v>0.007891612903225806</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>41358</v>
+        <v>42359</v>
       </c>
       <c r="B145" t="n">
-        <v>101.2966666666667</v>
+        <v>28.68</v>
       </c>
       <c r="C145" t="n">
-        <v>26.8565</v>
+        <v>13.95944827586207</v>
       </c>
       <c r="D145" t="n">
-        <v>264.71</v>
+        <v>287.2266666666666</v>
       </c>
       <c r="E145" t="n">
-        <v>0.02235366666666667</v>
+        <v>0.01579566666666667</v>
       </c>
       <c r="F145" t="n">
-        <v>0.017265</v>
+        <v>0.006794827586206896</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>41379</v>
+        <v>42387</v>
       </c>
       <c r="B146" t="n">
-        <v>105.0366666666667</v>
+        <v>33.38</v>
       </c>
       <c r="C146" t="n">
-        <v>26.398</v>
+        <v>12.76541935483871</v>
       </c>
       <c r="D146" t="n">
-        <v>248.87</v>
+        <v>293.91</v>
       </c>
       <c r="E146" t="n">
-        <v>0.02182566666666667</v>
+        <v>0.013869</v>
       </c>
       <c r="F146" t="n">
-        <v>0.01639129032258065</v>
+        <v>0.004755806451612903</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>41400</v>
+        <v>42415</v>
       </c>
       <c r="B147" t="n">
-        <v>102.6266666666667</v>
+        <v>39.81666666666667</v>
       </c>
       <c r="C147" t="n">
-        <v>26.335</v>
+        <v>12.08564516129032</v>
       </c>
       <c r="D147" t="n">
-        <v>249.8</v>
+        <v>287.0633333333333</v>
       </c>
       <c r="E147" t="n">
-        <v>0.02267266666666667</v>
+        <v>0.013245</v>
       </c>
       <c r="F147" t="n">
-        <v>0.01811870967741936</v>
+        <v>0.004072903225806452</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>41421</v>
+        <v>42443</v>
       </c>
       <c r="B148" t="n">
-        <v>105.6233333333333</v>
+        <v>42.53333333333333</v>
       </c>
       <c r="C148" t="n">
-        <v>26.28</v>
+        <v>12.22734482758621</v>
       </c>
       <c r="D148" t="n">
-        <v>262.1766666666667</v>
+        <v>280.24</v>
       </c>
       <c r="E148" t="n">
-        <v>0.023851</v>
+        <v>0.010107</v>
       </c>
       <c r="F148" t="n">
-        <v>0.02005571428571429</v>
+        <v>0.004746896551724138</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>41442</v>
+        <v>42471</v>
       </c>
       <c r="B149" t="n">
-        <v>107.5266666666667</v>
+        <v>44.21</v>
       </c>
       <c r="C149" t="n">
-        <v>26.20636363636364</v>
+        <v>13.18934375</v>
       </c>
       <c r="D149" t="n">
-        <v>259.2566666666667</v>
+        <v>297.8733333333333</v>
       </c>
       <c r="E149" t="n">
-        <v>0.02598</v>
+        <v>0.01034933333333334</v>
       </c>
       <c r="F149" t="n">
-        <v>0.02117545454545455</v>
+        <v>0.0051459375</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>41463</v>
+        <v>42499</v>
       </c>
       <c r="B150" t="n">
-        <v>107.3566666666667</v>
+        <v>50.24666666666666</v>
       </c>
       <c r="C150" t="n">
-        <v>26.10454545454546</v>
+        <v>14.26083333333333</v>
       </c>
       <c r="D150" t="n">
-        <v>271.9266666666667</v>
+        <v>294.2666666666667</v>
       </c>
       <c r="E150" t="n">
-        <v>0.025672</v>
+        <v>0.01035733333333333</v>
       </c>
       <c r="F150" t="n">
-        <v>0.02111818181818182</v>
+        <v>0.003888333333333333</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>41484</v>
+        <v>42527</v>
       </c>
       <c r="B151" t="n">
-        <v>110.0666666666667</v>
+        <v>50.18333333333334</v>
       </c>
       <c r="C151" t="n">
-        <v>26.1014</v>
+        <v>14.38358620689655</v>
       </c>
       <c r="D151" t="n">
-        <v>271.82</v>
+        <v>295.0466666666667</v>
       </c>
       <c r="E151" t="n">
-        <v>0.02715733333333333</v>
+        <v>0.007558</v>
       </c>
       <c r="F151" t="n">
-        <v>0.021878</v>
+        <v>0.002217586206896552</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>41505</v>
+        <v>42555</v>
       </c>
       <c r="B152" t="n">
-        <v>114.52</v>
+        <v>42.24666666666667</v>
       </c>
       <c r="C152" t="n">
-        <v>26.38045161290323</v>
+        <v>14.34981818181818</v>
       </c>
       <c r="D152" t="n">
-        <v>277.69</v>
+        <v>277.52</v>
       </c>
       <c r="E152" t="n">
-        <v>0.02801233333333333</v>
+        <v>0.005294666666666666</v>
       </c>
       <c r="F152" t="n">
-        <v>0.02216354838709677</v>
+        <v>0.000783939393939394</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>41526</v>
+        <v>42583</v>
       </c>
       <c r="B153" t="n">
-        <v>108.4566666666667</v>
+        <v>49.48</v>
       </c>
       <c r="C153" t="n">
-        <v>27.01383870967742</v>
+        <v>12.83527272727273</v>
       </c>
       <c r="D153" t="n">
-        <v>279.32</v>
+        <v>272.4333333333333</v>
       </c>
       <c r="E153" t="n">
-        <v>0.026029</v>
+        <v>0.005631666666666667</v>
       </c>
       <c r="F153" t="n">
-        <v>0.02163516129032258</v>
+        <v>0.0004190909090909091</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>41547</v>
+        <v>42611</v>
       </c>
       <c r="B154" t="n">
-        <v>109.74</v>
+        <v>46.86333333333334</v>
       </c>
       <c r="C154" t="n">
-        <v>27.064</v>
+        <v>14.90383333333333</v>
       </c>
       <c r="D154" t="n">
-        <v>268.9233333333333</v>
+        <v>258.5833333333333</v>
       </c>
       <c r="E154" t="n">
-        <v>0.02663033333333333</v>
+        <v>0.005890333333333333</v>
       </c>
       <c r="F154" t="n">
-        <v>0.02079709677419355</v>
+        <v>8.833333333333333e-05</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>41568</v>
+        <v>42639</v>
       </c>
       <c r="B155" t="n">
-        <v>105.9733333333333</v>
+        <v>51.56666666666667</v>
       </c>
       <c r="C155" t="n">
-        <v>27.4901724137931</v>
+        <v>17.16106451612903</v>
       </c>
       <c r="D155" t="n">
-        <v>278.0366666666666</v>
+        <v>276.5333333333333</v>
       </c>
       <c r="E155" t="n">
-        <v>0.02578033333333333</v>
+        <v>0.007114000000000001</v>
       </c>
       <c r="F155" t="n">
-        <v>0.02035</v>
+        <v>0.001669677419354839</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>41589</v>
+        <v>42667</v>
       </c>
       <c r="B156" t="n">
-        <v>110.8633333333333</v>
+        <v>48.22</v>
       </c>
       <c r="C156" t="n">
-        <v>28.2334375</v>
+        <v>18.07233333333333</v>
       </c>
       <c r="D156" t="n">
-        <v>283.0033333333333</v>
+        <v>268.2866666666666</v>
       </c>
       <c r="E156" t="n">
-        <v>0.02580733333333333</v>
+        <v>0.01143766666666667</v>
       </c>
       <c r="F156" t="n">
-        <v>0.020473125</v>
+        <v>0.00352</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>41610</v>
+        <v>42695</v>
       </c>
       <c r="B157" t="n">
-        <v>111.63</v>
+        <v>55.01666666666667</v>
       </c>
       <c r="C157" t="n">
-        <v>27.75503125</v>
+        <v>19.0098</v>
       </c>
       <c r="D157" t="n">
-        <v>285.04</v>
+        <v>276.68</v>
       </c>
       <c r="E157" t="n">
-        <v>0.027379</v>
+        <v>0.011563</v>
       </c>
       <c r="F157" t="n">
-        <v>0.0217659375</v>
+        <v>0.004142</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>41631</v>
+        <v>42723</v>
       </c>
       <c r="B158" t="n">
-        <v>106.9166666666667</v>
+        <v>55.72333333333334</v>
       </c>
       <c r="C158" t="n">
-        <v>26.58341935483871</v>
+        <v>20.145</v>
       </c>
       <c r="D158" t="n">
-        <v>298.91</v>
+        <v>285.6733333333333</v>
       </c>
       <c r="E158" t="n">
-        <v>0.02667866666666667</v>
+        <v>0.011763</v>
       </c>
       <c r="F158" t="n">
-        <v>0.02135225806451613</v>
+        <v>0.00493</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>41652</v>
+        <v>42751</v>
       </c>
       <c r="B159" t="n">
-        <v>106.16</v>
+        <v>55.96</v>
       </c>
       <c r="C159" t="n">
-        <v>24.91307142857143</v>
+        <v>19.09771428571429</v>
       </c>
       <c r="D159" t="n">
-        <v>302.83</v>
+        <v>289.78</v>
       </c>
       <c r="E159" t="n">
-        <v>0.024483</v>
+        <v>0.01229433333333333</v>
       </c>
       <c r="F159" t="n">
-        <v>0.01979928571428571</v>
+        <v>0.005202857142857143</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>41673</v>
+        <v>42779</v>
       </c>
       <c r="B160" t="n">
-        <v>110.3766666666667</v>
+        <v>51.35666666666667</v>
       </c>
       <c r="C160" t="n">
-        <v>23.44382142857143</v>
+        <v>16.47212903225806</v>
       </c>
       <c r="D160" t="n">
-        <v>303.21</v>
+        <v>305.82</v>
       </c>
       <c r="E160" t="n">
-        <v>0.024772</v>
+        <v>0.01393333333333333</v>
       </c>
       <c r="F160" t="n">
-        <v>0.01958178571428571</v>
+        <v>0.004887096774193549</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>41694</v>
+        <v>42807</v>
       </c>
       <c r="B161" t="n">
-        <v>107.0166666666667</v>
+        <v>55.73333333333333</v>
       </c>
       <c r="C161" t="n">
-        <v>22.09993548387097</v>
+        <v>15.92346428571429</v>
       </c>
       <c r="D161" t="n">
-        <v>307.7633333333333</v>
+        <v>307.7066666666667</v>
       </c>
       <c r="E161" t="n">
-        <v>0.023681</v>
+        <v>0.01164433333333333</v>
       </c>
       <c r="F161" t="n">
-        <v>0.01919967741935484</v>
+        <v>0.0055225</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>41715</v>
+        <v>42835</v>
       </c>
       <c r="B162" t="n">
-        <v>106.12</v>
+        <v>49.26000000000001</v>
       </c>
       <c r="C162" t="n">
-        <v>20.8752</v>
+        <v>15.94009090909091</v>
       </c>
       <c r="D162" t="n">
-        <v>316.52</v>
+        <v>294.3133333333333</v>
       </c>
       <c r="E162" t="n">
-        <v>0.02358966666666667</v>
+        <v>0.012715</v>
       </c>
       <c r="F162" t="n">
-        <v>0.018716</v>
+        <v>0.005523636363636364</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>41736</v>
+        <v>42863</v>
       </c>
       <c r="B163" t="n">
-        <v>108.6066666666667</v>
+        <v>49.63</v>
       </c>
       <c r="C163" t="n">
-        <v>19.8504</v>
+        <v>15.23433333333333</v>
       </c>
       <c r="D163" t="n">
-        <v>325.4833333333333</v>
+        <v>299.9666666666667</v>
       </c>
       <c r="E163" t="n">
-        <v>0.02305533333333333</v>
+        <v>0.01146066666666667</v>
       </c>
       <c r="F163" t="n">
-        <v>0.018107</v>
+        <v>0.005554666666666667</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>41757</v>
+        <v>42891</v>
       </c>
       <c r="B164" t="n">
-        <v>109.4966666666667</v>
+        <v>49.09333333333333</v>
       </c>
       <c r="C164" t="n">
-        <v>19.2948</v>
+        <v>14.84812903225806</v>
       </c>
       <c r="D164" t="n">
-        <v>314.62</v>
+        <v>306.49</v>
       </c>
       <c r="E164" t="n">
-        <v>0.02112966666666667</v>
+        <v>0.01341066666666667</v>
       </c>
       <c r="F164" t="n">
-        <v>0.017</v>
+        <v>0.006589677419354839</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>41778</v>
+        <v>42919</v>
       </c>
       <c r="B165" t="n">
-        <v>109.53</v>
+        <v>52.60666666666667</v>
       </c>
       <c r="C165" t="n">
-        <v>18.51945161290323</v>
+        <v>14.96193548387097</v>
       </c>
       <c r="D165" t="n">
-        <v>312.4833333333333</v>
+        <v>300.37</v>
       </c>
       <c r="E165" t="n">
-        <v>0.02089833333333333</v>
+        <v>0.01254166666666667</v>
       </c>
       <c r="F165" t="n">
-        <v>0.01591354838709677</v>
+        <v>0.00700516129032258</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>41799</v>
+        <v>42947</v>
       </c>
       <c r="B166" t="n">
-        <v>112.6733333333333</v>
+        <v>52.06333333333333</v>
       </c>
       <c r="C166" t="n">
-        <v>17.34683870967742</v>
+        <v>16.25938709677419</v>
       </c>
       <c r="D166" t="n">
-        <v>313.8866666666667</v>
+        <v>310.41</v>
       </c>
       <c r="E166" t="n">
-        <v>0.01998866666666667</v>
+        <v>0.010994</v>
       </c>
       <c r="F166" t="n">
-        <v>0.01496516129032258</v>
+        <v>0.005556774193548387</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>41820</v>
+        <v>42975</v>
       </c>
       <c r="B167" t="n">
-        <v>107.5333333333333</v>
+        <v>58.3</v>
       </c>
       <c r="C167" t="n">
-        <v>18.08906451612903</v>
+        <v>17.22148275862069</v>
       </c>
       <c r="D167" t="n">
-        <v>322.0433333333334</v>
+        <v>303.6333333333333</v>
       </c>
       <c r="E167" t="n">
-        <v>0.01905</v>
+        <v>0.011963</v>
       </c>
       <c r="F167" t="n">
-        <v>0.01424903225806451</v>
+        <v>0.006151034482758621</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>41841</v>
+        <v>43003</v>
       </c>
       <c r="B168" t="n">
-        <v>104.7933333333333</v>
+        <v>57.49666666666666</v>
       </c>
       <c r="C168" t="n">
-        <v>19.73558620689655</v>
+        <v>17.97784375</v>
       </c>
       <c r="D168" t="n">
-        <v>315.7133333333334</v>
+        <v>297.3566666666667</v>
       </c>
       <c r="E168" t="n">
-        <v>0.01818633333333333</v>
+        <v>0.01190066666666667</v>
       </c>
       <c r="F168" t="n">
-        <v>0.01280413793103448</v>
+        <v>0.005507812500000001</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>41862</v>
+        <v>43031</v>
       </c>
       <c r="B169" t="n">
-        <v>102.9233333333333</v>
+        <v>62.38666666666666</v>
       </c>
       <c r="C169" t="n">
-        <v>22.1573125</v>
+        <v>19.53656666666667</v>
       </c>
       <c r="D169" t="n">
-        <v>308.1733333333333</v>
+        <v>279.6166666666667</v>
       </c>
       <c r="E169" t="n">
-        <v>0.01638233333333334</v>
+        <v>0.010942</v>
       </c>
       <c r="F169" t="n">
-        <v>0.010793125</v>
+        <v>0.005139333333333333</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>41883</v>
+        <v>43059</v>
       </c>
       <c r="B170" t="n">
-        <v>97.44333333333333</v>
+        <v>63.34999999999999</v>
       </c>
       <c r="C170" t="n">
-        <v>23.49409375</v>
+        <v>19.90596551724138</v>
       </c>
       <c r="D170" t="n">
-        <v>309</v>
+        <v>265.64</v>
       </c>
       <c r="E170" t="n">
-        <v>0.01666433333333333</v>
+        <v>0.01065666666666667</v>
       </c>
       <c r="F170" t="n">
-        <v>0.0111409375</v>
+        <v>0.005403103448275862</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>41904</v>
+        <v>43087</v>
       </c>
       <c r="B171" t="n">
-        <v>89.33</v>
+        <v>70.13000000000001</v>
       </c>
       <c r="C171" t="n">
-        <v>23.59667741935484</v>
+        <v>18.81287878787879</v>
       </c>
       <c r="D171" t="n">
-        <v>327.3933333333333</v>
+        <v>282.4733333333334</v>
       </c>
       <c r="E171" t="n">
-        <v>0.015762</v>
+        <v>0.01285666666666667</v>
       </c>
       <c r="F171" t="n">
-        <v>0.01096483870967742</v>
+        <v>0.006986969696969696</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>41925</v>
+        <v>43115</v>
       </c>
       <c r="B172" t="n">
-        <v>85.14</v>
+        <v>62.65666666666667</v>
       </c>
       <c r="C172" t="n">
-        <v>22.94878571428572</v>
+        <v>17.71428571428572</v>
       </c>
       <c r="D172" t="n">
-        <v>315.6133333333333</v>
+        <v>298.0233333333334</v>
       </c>
       <c r="E172" t="n">
-        <v>0.01543166666666667</v>
+        <v>0.01414566666666667</v>
       </c>
       <c r="F172" t="n">
-        <v>0.01034285714285714</v>
+        <v>0.008528571428571429</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>41946</v>
+        <v>43143</v>
       </c>
       <c r="B173" t="n">
-        <v>79.90666666666667</v>
+        <v>65.13</v>
       </c>
       <c r="C173" t="n">
-        <v>23.96503571428572</v>
+        <v>17.66386666666667</v>
       </c>
       <c r="D173" t="n">
-        <v>315.22</v>
+        <v>290.3766666666667</v>
       </c>
       <c r="E173" t="n">
-        <v>0.01466633333333334</v>
+        <v>0.01346</v>
       </c>
       <c r="F173" t="n">
-        <v>0.009217857142857142</v>
+        <v>0.008191666666666667</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>41967</v>
+        <v>43171</v>
       </c>
       <c r="B174" t="n">
-        <v>61.32333333333334</v>
+        <v>68.13666666666667</v>
       </c>
       <c r="C174" t="n">
-        <v>22.79560606060606</v>
+        <v>18.9021935483871</v>
       </c>
       <c r="D174" t="n">
-        <v>321.2366666666667</v>
+        <v>289.02</v>
       </c>
       <c r="E174" t="n">
-        <v>0.01367066666666667</v>
+        <v>0.01309666666666667</v>
       </c>
       <c r="F174" t="n">
-        <v>0.00831969696969697</v>
+        <v>0.007481290322580645</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>41988</v>
+        <v>43199</v>
       </c>
       <c r="B175" t="n">
-        <v>54.21333333333333</v>
+        <v>75.73666666666666</v>
       </c>
       <c r="C175" t="n">
-        <v>21.15853333333333</v>
+        <v>20.99032258064516</v>
       </c>
       <c r="D175" t="n">
-        <v>325.7833333333333</v>
+        <v>293.3033333333333</v>
       </c>
       <c r="E175" t="n">
-        <v>0.012489</v>
+        <v>0.01316933333333333</v>
       </c>
       <c r="F175" t="n">
-        <v>0.007372666666666667</v>
+        <v>0.007561935483870968</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>42009</v>
+        <v>43227</v>
       </c>
       <c r="B176" t="n">
-        <v>48.37</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="C176" t="n">
-        <v>20.43683333333333</v>
+        <v>22.52448275862069</v>
       </c>
       <c r="D176" t="n">
-        <v>330.39</v>
+        <v>289.4733333333334</v>
       </c>
       <c r="E176" t="n">
-        <v>0.01107533333333333</v>
+        <v>0.01376166666666667</v>
       </c>
       <c r="F176" t="n">
-        <v>0.005916666666666667</v>
+        <v>0.007059655172413793</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>42030</v>
+        <v>43255</v>
       </c>
       <c r="B177" t="n">
-        <v>61.44</v>
+        <v>78.01333333333334</v>
       </c>
       <c r="C177" t="n">
-        <v>21.85985714285714</v>
+        <v>21.8851875</v>
       </c>
       <c r="D177" t="n">
-        <v>335.5933333333333</v>
+        <v>284.6533333333334</v>
       </c>
       <c r="E177" t="n">
-        <v>0.01033666666666667</v>
+        <v>0.01307</v>
       </c>
       <c r="F177" t="n">
-        <v>0.005055714285714286</v>
+        <v>0.0070125</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>42051</v>
+        <v>43283</v>
       </c>
       <c r="B178" t="n">
-        <v>58.93</v>
+        <v>74.74333333333334</v>
       </c>
       <c r="C178" t="n">
-        <v>22.63721875</v>
+        <v>22.0978125</v>
       </c>
       <c r="D178" t="n">
-        <v>329.62</v>
+        <v>275.5166666666667</v>
       </c>
       <c r="E178" t="n">
-        <v>0.010146</v>
+        <v>0.013165</v>
       </c>
       <c r="F178" t="n">
-        <v>0.0040034375</v>
+        <v>0.007607500000000001</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>42072</v>
+        <v>43311</v>
       </c>
       <c r="B179" t="n">
-        <v>56.33</v>
+        <v>76.08</v>
       </c>
       <c r="C179" t="n">
-        <v>21.6600625</v>
+        <v>25.23635483870968</v>
       </c>
       <c r="D179" t="n">
-        <v>337.1766666666667</v>
+        <v>289.96</v>
       </c>
       <c r="E179" t="n">
-        <v>0.01015466666666667</v>
+        <v>0.01259766666666667</v>
       </c>
       <c r="F179" t="n">
-        <v>0.002448125</v>
+        <v>0.007062903225806451</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>42093</v>
+        <v>43339</v>
       </c>
       <c r="B180" t="n">
-        <v>63.45</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="C180" t="n">
-        <v>20.8773</v>
+        <v>27.06257142857143</v>
       </c>
       <c r="D180" t="n">
-        <v>319.0866666666666</v>
+        <v>283.0733333333333</v>
       </c>
       <c r="E180" t="n">
-        <v>0.009574666666666667</v>
+        <v>0.01441066666666667</v>
       </c>
       <c r="F180" t="n">
-        <v>0.003465333333333333</v>
+        <v>0.007919285714285714</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>42114</v>
+        <v>43367</v>
       </c>
       <c r="B181" t="n">
-        <v>65.06999999999999</v>
+        <v>79.81333333333333</v>
       </c>
       <c r="C181" t="n">
-        <v>20.39731034482759</v>
+        <v>25.24087878787878</v>
       </c>
       <c r="D181" t="n">
-        <v>317.1433333333333</v>
+        <v>294.1866666666667</v>
       </c>
       <c r="E181" t="n">
-        <v>0.013294</v>
+        <v>0.014102</v>
       </c>
       <c r="F181" t="n">
-        <v>0.004946896551724138</v>
+        <v>0.007941818181818182</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>42135</v>
+        <v>43395</v>
       </c>
       <c r="B182" t="n">
-        <v>65.10666666666667</v>
+        <v>66.78</v>
       </c>
       <c r="C182" t="n">
-        <v>20.257125</v>
+        <v>24.5478</v>
       </c>
       <c r="D182" t="n">
-        <v>321.8966666666666</v>
+        <v>307.4533333333333</v>
       </c>
       <c r="E182" t="n">
-        <v>0.01313233333333333</v>
+        <v>0.01440933333333333</v>
       </c>
       <c r="F182" t="n">
-        <v>0.006700625</v>
+        <v>0.007638000000000001</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>42156</v>
+        <v>43423</v>
       </c>
       <c r="B183" t="n">
-        <v>63.23333333333333</v>
+        <v>59.83333333333334</v>
       </c>
       <c r="C183" t="n">
-        <v>20.3949375</v>
+        <v>23.2928064516129</v>
       </c>
       <c r="D183" t="n">
-        <v>305.57</v>
+        <v>311.7633333333333</v>
       </c>
       <c r="E183" t="n">
-        <v>0.017324</v>
+        <v>0.014219</v>
       </c>
       <c r="F183" t="n">
-        <v>0.009017187499999999</v>
+        <v>0.007319677419354838</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>42177</v>
+        <v>43451</v>
       </c>
       <c r="B184" t="n">
-        <v>58.14333333333333</v>
+        <v>59.48666666666666</v>
       </c>
       <c r="C184" t="n">
-        <v>20.47567741935484</v>
+        <v>21.08877419354839</v>
       </c>
       <c r="D184" t="n">
-        <v>290.0733333333333</v>
+        <v>316.0266666666667</v>
       </c>
       <c r="E184" t="n">
-        <v>0.01774633333333333</v>
+        <v>0.013941</v>
       </c>
       <c r="F184" t="n">
-        <v>0.009247419354838709</v>
+        <v>0.006694516129032258</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>42198</v>
+        <v>43479</v>
       </c>
       <c r="B185" t="n">
-        <v>50.41666666666667</v>
+        <v>61.70666666666666</v>
       </c>
       <c r="C185" t="n">
-        <v>20.42870967741936</v>
+        <v>19.12414285714286</v>
       </c>
       <c r="D185" t="n">
-        <v>290.4966666666667</v>
+        <v>312.56</v>
       </c>
       <c r="E185" t="n">
-        <v>0.014725</v>
+        <v>0.01146533333333333</v>
       </c>
       <c r="F185" t="n">
-        <v>0.008085806451612904</v>
+        <v>0.006121428571428571</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>42219</v>
+        <v>43507</v>
       </c>
       <c r="B186" t="n">
-        <v>43.61333333333333</v>
+        <v>66.3</v>
       </c>
       <c r="C186" t="n">
-        <v>19.57516129032258</v>
+        <v>16.57227586206897</v>
       </c>
       <c r="D186" t="n">
-        <v>314.6733333333333</v>
+        <v>311.58</v>
       </c>
       <c r="E186" t="n">
-        <v>0.01453533333333333</v>
+        <v>0.01093366666666667</v>
       </c>
       <c r="F186" t="n">
-        <v>0.008566774193548388</v>
+        <v>0.005432758620689655</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>42240</v>
+        <v>43535</v>
       </c>
       <c r="B187" t="n">
-        <v>46.96</v>
+        <v>70.84666666666666</v>
       </c>
       <c r="C187" t="n">
-        <v>18.99736666666667</v>
+        <v>14.2625</v>
       </c>
       <c r="D187" t="n">
-        <v>304.3433333333333</v>
+        <v>321.6533333333333</v>
       </c>
       <c r="E187" t="n">
-        <v>0.015567</v>
+        <v>0.009608333333333333</v>
       </c>
       <c r="F187" t="n">
-        <v>0.008594000000000001</v>
+        <v>0.0039671875</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>42261</v>
+        <v>43563</v>
       </c>
       <c r="B188" t="n">
-        <v>48.87666666666667</v>
+        <v>71.11</v>
       </c>
       <c r="C188" t="n">
-        <v>18.5766</v>
+        <v>13.87545161290323</v>
       </c>
       <c r="D188" t="n">
-        <v>304.63</v>
+        <v>324.13</v>
       </c>
       <c r="E188" t="n">
-        <v>0.01584566666666667</v>
+        <v>0.008728000000000001</v>
       </c>
       <c r="F188" t="n">
-        <v>0.008307333333333333</v>
+        <v>0.003899677419354839</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>42282</v>
+        <v>43591</v>
       </c>
       <c r="B189" t="n">
-        <v>47.69</v>
+        <v>62.35</v>
       </c>
       <c r="C189" t="n">
-        <v>18.102</v>
+        <v>11.12728571428571</v>
       </c>
       <c r="D189" t="n">
-        <v>302.52</v>
+        <v>323.4166666666667</v>
       </c>
       <c r="E189" t="n">
-        <v>0.01517033333333333</v>
+        <v>0.008133666666666666</v>
       </c>
       <c r="F189" t="n">
-        <v>0.007873333333333333</v>
+        <v>0.002266428571428571</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>42303</v>
+        <v>43619</v>
       </c>
       <c r="B190" t="n">
-        <v>44.24333333333333</v>
+        <v>65.55666666666667</v>
       </c>
       <c r="C190" t="n">
-        <v>18.00758064516129</v>
+        <v>10.17039393939394</v>
       </c>
       <c r="D190" t="n">
-        <v>284.9433333333333</v>
+        <v>331.7733333333333</v>
       </c>
       <c r="E190" t="n">
-        <v>0.01486466666666667</v>
+        <v>0.005529</v>
       </c>
       <c r="F190" t="n">
-        <v>0.007393225806451613</v>
+        <v>0.0005612121212121212</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>42324</v>
+        <v>43647</v>
       </c>
       <c r="B191" t="n">
-        <v>41.48666666666666</v>
+        <v>63.62666666666667</v>
       </c>
       <c r="C191" t="n">
-        <v>17.39809677419355</v>
+        <v>10.91790909090909</v>
       </c>
       <c r="D191" t="n">
-        <v>277.09</v>
+        <v>342.4166666666666</v>
       </c>
       <c r="E191" t="n">
-        <v>0.015702</v>
+        <v>0.003579333333333333</v>
       </c>
       <c r="F191" t="n">
-        <v>0.007295483870967742</v>
+        <v>-0.0008218181818181818</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>42345</v>
+        <v>43675</v>
       </c>
       <c r="B192" t="n">
-        <v>36.9375</v>
+        <v>58.91333333333333</v>
       </c>
       <c r="C192" t="n">
-        <v>15.20393548387097</v>
+        <v>12.49716666666667</v>
       </c>
       <c r="D192" t="n">
-        <v>282.4433333333333</v>
+        <v>340.52</v>
       </c>
       <c r="E192" t="n">
-        <v>0.01563725</v>
+        <v>0.001993666666666667</v>
       </c>
       <c r="F192" t="n">
-        <v>0.008189677419354838</v>
+        <v>-0.003295</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>42366</v>
+        <v>43703</v>
       </c>
       <c r="B193" t="n">
-        <v>28.68</v>
+        <v>64.60666666666667</v>
       </c>
       <c r="C193" t="n">
-        <v>13.95944827586207</v>
+        <v>15.46425806451613</v>
       </c>
       <c r="D193" t="n">
-        <v>287.2266666666666</v>
+        <v>340.88</v>
       </c>
       <c r="E193" t="n">
-        <v>0.01579566666666667</v>
+        <v>0.003577333333333333</v>
       </c>
       <c r="F193" t="n">
-        <v>0.006794827586206896</v>
+        <v>-0.002862258064516129</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>42387</v>
+        <v>43731</v>
       </c>
       <c r="B194" t="n">
-        <v>33.27333333333333</v>
+        <v>59.11333333333334</v>
       </c>
       <c r="C194" t="n">
-        <v>13.03254838709677</v>
+        <v>16.22490322580645</v>
       </c>
       <c r="D194" t="n">
-        <v>290.9666666666667</v>
+        <v>356.2666666666667</v>
       </c>
       <c r="E194" t="n">
-        <v>0.01365066666666667</v>
+        <v>0.005004666666666667</v>
       </c>
       <c r="F194" t="n">
-        <v>0.005164516129032258</v>
+        <v>-0.00135</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>42408</v>
+        <v>43759</v>
       </c>
       <c r="B195" t="n">
-        <v>35.68</v>
+        <v>62.72666666666667</v>
       </c>
       <c r="C195" t="n">
-        <v>12.23116129032258</v>
+        <v>16.24848275862069</v>
       </c>
       <c r="D195" t="n">
-        <v>289.0333333333334</v>
+        <v>392.65</v>
       </c>
       <c r="E195" t="n">
-        <v>0.01289833333333333</v>
+        <v>0.004680333333333334</v>
       </c>
       <c r="F195" t="n">
-        <v>0.003938387096774193</v>
+        <v>-0.0004027586206896552</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>42429</v>
+        <v>43787</v>
       </c>
       <c r="B196" t="n">
-        <v>41.42666666666667</v>
+        <v>65.3</v>
       </c>
       <c r="C196" t="n">
-        <v>12.02783870967742</v>
+        <v>14.1905</v>
       </c>
       <c r="D196" t="n">
-        <v>296.6833333333333</v>
+        <v>384.8633333333333</v>
       </c>
       <c r="E196" t="n">
-        <v>0.01214133333333333</v>
+        <v>0.005252000000000001</v>
       </c>
       <c r="F196" t="n">
-        <v>0.004176774193548387</v>
+        <v>0.00055</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>42450</v>
+        <v>43815</v>
       </c>
       <c r="B197" t="n">
-        <v>42.53333333333333</v>
+        <v>64.46000000000001</v>
       </c>
       <c r="C197" t="n">
-        <v>12.22734482758621</v>
+        <v>11.16222580645161</v>
       </c>
       <c r="D197" t="n">
-        <v>280.24</v>
+        <v>297.01</v>
       </c>
       <c r="E197" t="n">
-        <v>0.010107</v>
+        <v>0.005753333333333333</v>
       </c>
       <c r="F197" t="n">
-        <v>0.004746896551724138</v>
+        <v>0.0002432258064516129</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>42471</v>
+        <v>43843</v>
       </c>
       <c r="B198" t="n">
-        <v>46.59666666666666</v>
+        <v>53.67</v>
       </c>
       <c r="C198" t="n">
-        <v>12.8701875</v>
+        <v>9.471821428571429</v>
       </c>
       <c r="D198" t="n">
-        <v>288.3</v>
+        <v>312.41</v>
       </c>
       <c r="E198" t="n">
-        <v>0.01142066666666667</v>
+        <v>0.003567</v>
       </c>
       <c r="F198" t="n">
-        <v>0.005436875000000001</v>
+        <v>-0.001799642857142857</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>42492</v>
+        <v>43871</v>
       </c>
       <c r="B199" t="n">
-        <v>48.47333333333334</v>
+        <v>37.99666666666667</v>
       </c>
       <c r="C199" t="n">
-        <v>13.82765625</v>
+        <v>8.319375000000001</v>
       </c>
       <c r="D199" t="n">
-        <v>300.33</v>
+        <v>339.8033333333333</v>
       </c>
       <c r="E199" t="n">
-        <v>0.01151866666666667</v>
+        <v>0.003203</v>
       </c>
       <c r="F199" t="n">
-        <v>0.0045640625</v>
+        <v>-0.00169125</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>42513</v>
+        <v>43899</v>
       </c>
       <c r="B200" t="n">
-        <v>50.41333333333333</v>
+        <v>33.40333333333333</v>
       </c>
       <c r="C200" t="n">
-        <v>14.2928</v>
+        <v>6.7885</v>
       </c>
       <c r="D200" t="n">
-        <v>287.5733333333333</v>
+        <v>347.9366666666667</v>
       </c>
       <c r="E200" t="n">
-        <v>0.009699666666666667</v>
+        <v>0.01323366666666667</v>
       </c>
       <c r="F200" t="n">
-        <v>0.003466</v>
+        <v>0.0003366666666666666</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>42534</v>
+        <v>43927</v>
       </c>
       <c r="B201" t="n">
-        <v>50.18333333333334</v>
+        <v>26.94666666666667</v>
       </c>
       <c r="C201" t="n">
-        <v>14.38358620689655</v>
+        <v>6.031068965517242</v>
       </c>
       <c r="D201" t="n">
-        <v>295.0466666666667</v>
+        <v>359.0033333333333</v>
       </c>
       <c r="E201" t="n">
-        <v>0.007558</v>
+        <v>0.0072525</v>
       </c>
       <c r="F201" t="n">
-        <v>0.002217586206896552</v>
+        <v>-0.0008655172413793103</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>42555</v>
+        <v>43955</v>
       </c>
       <c r="B202" t="n">
-        <v>45.04333333333333</v>
+        <v>37.32333333333333</v>
       </c>
       <c r="C202" t="n">
-        <v>14.44368965517241</v>
+        <v>4.496125</v>
       </c>
       <c r="D202" t="n">
-        <v>288.6</v>
+        <v>355.4766666666667</v>
       </c>
       <c r="E202" t="n">
-        <v>0.005619333333333333</v>
+        <v>0.007699333333333333</v>
       </c>
       <c r="F202" t="n">
-        <v>0.001080689655172414</v>
+        <v>-0.0007943749999999999</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>42576</v>
+        <v>43983</v>
       </c>
       <c r="B203" t="n">
-        <v>47.89</v>
+        <v>41.48</v>
       </c>
       <c r="C203" t="n">
-        <v>13.59254545454545</v>
+        <v>6.051875000000001</v>
       </c>
       <c r="D203" t="n">
-        <v>282.94</v>
+        <v>339.23</v>
       </c>
       <c r="E203" t="n">
-        <v>0.005426333333333334</v>
+        <v>0.005323666666666668</v>
       </c>
       <c r="F203" t="n">
-        <v>0.0006015151515151515</v>
+        <v>-0.001555625</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>42597</v>
+        <v>44011</v>
       </c>
       <c r="B204" t="n">
-        <v>47.36333333333334</v>
+        <v>43.38666666666666</v>
       </c>
       <c r="C204" t="n">
-        <v>13.02993333333333</v>
+        <v>6.04558064516129</v>
       </c>
       <c r="D204" t="n">
-        <v>262.3166666666667</v>
+        <v>360.6933333333333</v>
       </c>
       <c r="E204" t="n">
-        <v>0.005917333333333333</v>
+        <v>0.004222999999999999</v>
       </c>
       <c r="F204" t="n">
-        <v>0.0003333333333333333</v>
+        <v>-0.002029354838709677</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>42618</v>
+        <v>44039</v>
       </c>
       <c r="B205" t="n">
-        <v>46.86333333333334</v>
+        <v>44.87</v>
       </c>
       <c r="C205" t="n">
-        <v>14.90383333333333</v>
+        <v>9.892935483870968</v>
       </c>
       <c r="D205" t="n">
-        <v>258.5833333333333</v>
+        <v>374.46</v>
       </c>
       <c r="E205" t="n">
-        <v>0.005890333333333333</v>
+        <v>0.003201666666666666</v>
       </c>
       <c r="F205" t="n">
-        <v>8.833333333333333e-05</v>
+        <v>-0.001293870967741936</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>42639</v>
+        <v>44067</v>
       </c>
       <c r="B206" t="n">
-        <v>51.66333333333333</v>
+        <v>42.01</v>
       </c>
       <c r="C206" t="n">
-        <v>16.60987096774194</v>
+        <v>12.60366666666667</v>
       </c>
       <c r="D206" t="n">
-        <v>273.3833333333333</v>
+        <v>369.52</v>
       </c>
       <c r="E206" t="n">
-        <v>0.007365666666666666</v>
+        <v>0.003001333333333333</v>
       </c>
       <c r="F206" t="n">
-        <v>0.001170645161290323</v>
+        <v>-0.001663333333333333</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>42660</v>
+        <v>44095</v>
       </c>
       <c r="B207" t="n">
-        <v>45.96</v>
+        <v>42.72333333333333</v>
       </c>
       <c r="C207" t="n">
-        <v>17.8754</v>
+        <v>13.751</v>
       </c>
       <c r="D207" t="n">
-        <v>271.9933333333333</v>
+        <v>399.36</v>
       </c>
       <c r="E207" t="n">
-        <v>0.008413333333333333</v>
+        <v>0.001688666666666667</v>
       </c>
       <c r="F207" t="n">
-        <v>0.002624</v>
+        <v>-0.002854</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>42681</v>
+        <v>44123</v>
       </c>
       <c r="B208" t="n">
-        <v>47.90666666666667</v>
+        <v>43.47333333333334</v>
       </c>
       <c r="C208" t="n">
-        <v>18.1708</v>
+        <v>14.61687096774194</v>
       </c>
       <c r="D208" t="n">
-        <v>265.4233333333333</v>
+        <v>375.3733333333333</v>
       </c>
       <c r="E208" t="n">
-        <v>0.010613</v>
+        <v>0.001583333333333334</v>
       </c>
       <c r="F208" t="n">
-        <v>0.003967999999999999</v>
+        <v>-0.00366741935483871</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>42702</v>
+        <v>44151</v>
       </c>
       <c r="B209" t="n">
-        <v>55.01666666666667</v>
+        <v>50.18333333333333</v>
       </c>
       <c r="C209" t="n">
-        <v>19.0098</v>
+        <v>16.80912903225806</v>
       </c>
       <c r="D209" t="n">
-        <v>276.68</v>
+        <v>366.3366666666666</v>
       </c>
       <c r="E209" t="n">
-        <v>0.011563</v>
+        <v>0.0008863333333333333</v>
       </c>
       <c r="F209" t="n">
-        <v>0.004142</v>
+        <v>-0.003957096774193549</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>42723</v>
+        <v>44179</v>
       </c>
       <c r="B210" t="n">
-        <v>55.66</v>
+        <v>55.77</v>
       </c>
       <c r="C210" t="n">
-        <v>19.88075</v>
+        <v>19.363</v>
       </c>
       <c r="D210" t="n">
-        <v>280.51</v>
+        <v>390.42</v>
       </c>
       <c r="E210" t="n">
-        <v>0.011834</v>
+        <v>0.001525333333333333</v>
       </c>
       <c r="F210" t="n">
-        <v>0.00458</v>
+        <v>-0.00385</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>42744</v>
+        <v>44207</v>
       </c>
       <c r="B211" t="n">
-        <v>55.32666666666667</v>
+        <v>60.15333333333334</v>
       </c>
       <c r="C211" t="n">
-        <v>20.6735</v>
+        <v>18.49310714285714</v>
       </c>
       <c r="D211" t="n">
-        <v>293.9066666666666</v>
+        <v>383.29</v>
       </c>
       <c r="E211" t="n">
-        <v>0.013358</v>
+        <v>0.002125333333333334</v>
       </c>
       <c r="F211" t="n">
-        <v>0.00563</v>
+        <v>-0.002624642857142857</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>42765</v>
+        <v>44235</v>
       </c>
       <c r="B212" t="n">
-        <v>56.05666666666666</v>
+        <v>68.61333333333333</v>
       </c>
       <c r="C212" t="n">
-        <v>18.13446428571429</v>
+        <v>16.594</v>
       </c>
       <c r="D212" t="n">
-        <v>289.4966666666667</v>
+        <v>378.58</v>
       </c>
       <c r="E212" t="n">
-        <v>0.01192466666666667</v>
+        <v>0.003527333333333334</v>
       </c>
       <c r="F212" t="n">
-        <v>0.004895357142857143</v>
+        <v>-0.0008018181818181819</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>42786</v>
+        <v>44263</v>
       </c>
       <c r="B213" t="n">
-        <v>51.35666666666667</v>
+        <v>62.8275</v>
       </c>
       <c r="C213" t="n">
-        <v>16.47212903225806</v>
+        <v>19.56613333333333</v>
       </c>
       <c r="D213" t="n">
-        <v>305.82</v>
+        <v>375.26</v>
       </c>
       <c r="E213" t="n">
-        <v>0.01393333333333333</v>
+        <v>0.0034022</v>
       </c>
       <c r="F213" t="n">
-        <v>0.004887096774193549</v>
+        <v>-0.0005880000000000001</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>42807</v>
+        <v>44291</v>
       </c>
       <c r="B214" t="n">
-        <v>53.02333333333333</v>
+        <v>67.45666666666666</v>
       </c>
       <c r="C214" t="n">
-        <v>15.82821428571429</v>
+        <v>23.40358064516129</v>
       </c>
       <c r="D214" t="n">
-        <v>304.7233333333333</v>
+        <v>382.9966666666667</v>
       </c>
       <c r="E214" t="n">
-        <v>0.012493</v>
+        <v>0.004332666666666667</v>
       </c>
       <c r="F214" t="n">
-        <v>0.005505</v>
+        <v>0.0001748387096774194</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>42828</v>
+        <v>44319</v>
       </c>
       <c r="B215" t="n">
-        <v>51.72</v>
+        <v>69.42333333333333</v>
       </c>
       <c r="C215" t="n">
-        <v>16.11396428571429</v>
+        <v>25.06370967741936</v>
       </c>
       <c r="D215" t="n">
-        <v>291.7433333333333</v>
+        <v>396.4933333333333</v>
       </c>
       <c r="E215" t="n">
-        <v>0.01252633333333333</v>
+        <v>0.004740333333333333</v>
       </c>
       <c r="F215" t="n">
-        <v>0.0055575</v>
+        <v>0.0006625806451612903</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>42849</v>
+        <v>44347</v>
       </c>
       <c r="B216" t="n">
-        <v>51.49333333333333</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="C216" t="n">
-        <v>15.75193939393939</v>
+        <v>33.6721</v>
       </c>
       <c r="D216" t="n">
-        <v>290.4866666666666</v>
+        <v>374.69</v>
       </c>
       <c r="E216" t="n">
-        <v>0.01247366666666667</v>
+        <v>0.004678</v>
       </c>
       <c r="F216" t="n">
-        <v>0.005487575757575758</v>
+        <v>0.000545</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>42870</v>
+        <v>44375</v>
       </c>
       <c r="B217" t="n">
-        <v>49.63</v>
+        <v>74.36666666666666</v>
       </c>
       <c r="C217" t="n">
-        <v>15.23433333333333</v>
+        <v>39.73366666666666</v>
       </c>
       <c r="D217" t="n">
-        <v>299.9666666666667</v>
+        <v>382.31</v>
       </c>
       <c r="E217" t="n">
-        <v>0.01146066666666667</v>
+        <v>0.002676</v>
       </c>
       <c r="F217" t="n">
-        <v>0.005554666666666667</v>
+        <v>-0.001245</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>42891</v>
+        <v>44403</v>
       </c>
       <c r="B218" t="n">
-        <v>45.73333333333333</v>
+        <v>67.56</v>
       </c>
       <c r="C218" t="n">
-        <v>14.91583333333333</v>
+        <v>47.6430625</v>
       </c>
       <c r="D218" t="n">
-        <v>301.8333333333333</v>
+        <v>392.56</v>
       </c>
       <c r="E218" t="n">
-        <v>0.01131666666666667</v>
+        <v>0.002179333333333333</v>
       </c>
       <c r="F218" t="n">
-        <v>0.006366666666666666</v>
+        <v>-0.00134125</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>42912</v>
+        <v>44431</v>
       </c>
       <c r="B219" t="n">
-        <v>48.58333333333334</v>
+        <v>74.39333333333333</v>
       </c>
       <c r="C219" t="n">
-        <v>14.90503225806452</v>
+        <v>80.38079999999999</v>
       </c>
       <c r="D219" t="n">
-        <v>301.48</v>
+        <v>390.02</v>
       </c>
       <c r="E219" t="n">
-        <v>0.01315633333333333</v>
+        <v>0.003948666666666667</v>
       </c>
       <c r="F219" t="n">
-        <v>0.006797419354838709</v>
+        <v>-5.566666666666654e-05</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>42933</v>
+        <v>44459</v>
       </c>
       <c r="B220" t="n">
-        <v>52.38666666666666</v>
+        <v>84.50666666666666</v>
       </c>
       <c r="C220" t="n">
-        <v>15.25341935483871</v>
+        <v>78.48193103448276</v>
       </c>
       <c r="D220" t="n">
-        <v>302.7733333333333</v>
+        <v>394.4233333333333</v>
       </c>
       <c r="E220" t="n">
-        <v>0.01173633333333333</v>
+        <v>0.005678666666666666</v>
       </c>
       <c r="F220" t="n">
-        <v>0.006694838709677419</v>
+        <v>0.001268965517241379</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>42954</v>
+        <v>44487</v>
       </c>
       <c r="B221" t="n">
-        <v>52.06333333333333</v>
+        <v>82.09</v>
       </c>
       <c r="C221" t="n">
-        <v>16.25938709677419</v>
+        <v>78.6885</v>
       </c>
       <c r="D221" t="n">
-        <v>310.41</v>
+        <v>383.7033333333334</v>
       </c>
       <c r="E221" t="n">
-        <v>0.010994</v>
+        <v>0.004999333333333333</v>
       </c>
       <c r="F221" t="n">
-        <v>0.005556774193548387</v>
+        <v>0.0008899999999999999</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>42975</v>
+        <v>44515</v>
       </c>
       <c r="B222" t="n">
-        <v>55.52666666666666</v>
+        <v>74.64333333333333</v>
       </c>
       <c r="C222" t="n">
-        <v>16.99675862068966</v>
+        <v>83.93106451612904</v>
       </c>
       <c r="D222" t="n">
-        <v>299.1133333333333</v>
+        <v>364.0033333333333</v>
       </c>
       <c r="E222" t="n">
-        <v>0.01224066666666667</v>
+        <v>0.004709666666666667</v>
       </c>
       <c r="F222" t="n">
-        <v>0.005914482758620689</v>
+        <v>0.0006096774193548387</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>42996</v>
+        <v>44543</v>
       </c>
       <c r="B223" t="n">
-        <v>55.73333333333333</v>
+        <v>81.16333333333334</v>
       </c>
       <c r="C223" t="n">
-        <v>17.61515625</v>
+        <v>74.50303225806452</v>
       </c>
       <c r="D223" t="n">
-        <v>297.0566666666667</v>
+        <v>397.44</v>
       </c>
       <c r="E223" t="n">
-        <v>0.012218</v>
+        <v>0.007433333333333333</v>
       </c>
       <c r="F223" t="n">
-        <v>0.006002187500000001</v>
+        <v>0.002028709677419355</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>43017</v>
+        <v>44571</v>
       </c>
       <c r="B224" t="n">
-        <v>60.74666666666666</v>
+        <v>92.88333333333333</v>
       </c>
       <c r="C224" t="n">
-        <v>18.1591875</v>
+        <v>87.6555</v>
       </c>
       <c r="D224" t="n">
-        <v>291.41</v>
+        <v>391.09</v>
       </c>
       <c r="E224" t="n">
-        <v>0.01091566666666667</v>
+        <v>0.01219966666666667</v>
       </c>
       <c r="F224" t="n">
-        <v>0.005260625</v>
+        <v>0.00409</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>43038</v>
+        <v>44599</v>
       </c>
       <c r="B225" t="n">
-        <v>62.38666666666666</v>
+        <v>121.51</v>
       </c>
       <c r="C225" t="n">
-        <v>19.53656666666667</v>
+        <v>103.881</v>
       </c>
       <c r="D225" t="n">
-        <v>279.6166666666667</v>
+        <v>385.4266666666667</v>
       </c>
       <c r="E225" t="n">
-        <v>0.010942</v>
+        <v>0.010793</v>
       </c>
       <c r="F225" t="n">
-        <v>0.005139333333333333</v>
+        <v>0.007494516129032259</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>43059</v>
+        <v>44627</v>
       </c>
       <c r="B226" t="n">
-        <v>64.25999999999999</v>
+        <v>106.4833333333333</v>
       </c>
       <c r="C226" t="n">
-        <v>20.06986206896552</v>
+        <v>123.1691724137931</v>
       </c>
       <c r="D226" t="n">
-        <v>273.05</v>
+        <v>354.22</v>
       </c>
       <c r="E226" t="n">
-        <v>0.01040133333333333</v>
+        <v>0.016363</v>
       </c>
       <c r="F226" t="n">
-        <v>0.005282413793103448</v>
+        <v>0.01116413793103448</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>43080</v>
+        <v>44655</v>
       </c>
       <c r="B227" t="n">
-        <v>66.72</v>
+        <v>108.1666666666667</v>
       </c>
       <c r="C227" t="n">
-        <v>19.52348484848485</v>
+        <v>99.10962500000001</v>
       </c>
       <c r="D227" t="n">
-        <v>279.4566666666666</v>
+        <v>371.18</v>
       </c>
       <c r="E227" t="n">
-        <v>0.012081</v>
+        <v>0.02081266666666667</v>
       </c>
       <c r="F227" t="n">
-        <v>0.005782121212121212</v>
+        <v>0.015460625</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>43101</v>
+        <v>44683</v>
       </c>
       <c r="B228" t="n">
-        <v>68.89</v>
+        <v>120.9233333333333</v>
       </c>
       <c r="C228" t="n">
-        <v>18.45757575757576</v>
+        <v>94.344375</v>
       </c>
       <c r="D228" t="n">
-        <v>286.5766666666667</v>
+        <v>382.56</v>
       </c>
       <c r="E228" t="n">
-        <v>0.01244533333333333</v>
+        <v>0.02320166666666667</v>
       </c>
       <c r="F228" t="n">
-        <v>0.007589393939393939</v>
+        <v>0.016869375</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>43122</v>
+        <v>44711</v>
       </c>
       <c r="B229" t="n">
-        <v>62.65666666666667</v>
+        <v>114.4333333333333</v>
       </c>
       <c r="C229" t="n">
-        <v>17.71428571428572</v>
+        <v>137.7793333333333</v>
       </c>
       <c r="D229" t="n">
-        <v>298.0233333333334</v>
+        <v>355.82</v>
       </c>
       <c r="E229" t="n">
-        <v>0.01414566666666667</v>
+        <v>0.030201</v>
       </c>
       <c r="F229" t="n">
-        <v>0.008528571428571429</v>
+        <v>0.02025466666666667</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>43143</v>
+        <v>44739</v>
       </c>
       <c r="B230" t="n">
-        <v>65.15000000000001</v>
+        <v>104.5</v>
       </c>
       <c r="C230" t="n">
-        <v>17.46413333333333</v>
+        <v>182.9148275862069</v>
       </c>
       <c r="D230" t="n">
-        <v>301.0933333333334</v>
+        <v>321.9466666666667</v>
       </c>
       <c r="E230" t="n">
-        <v>0.01332433333333333</v>
+        <v>0.023649</v>
       </c>
       <c r="F230" t="n">
-        <v>0.008483333333333332</v>
+        <v>0.01633241379310345</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>43164</v>
+        <v>44767</v>
       </c>
       <c r="B231" t="n">
-        <v>70.23</v>
+        <v>96.56</v>
       </c>
       <c r="C231" t="n">
-        <v>18.06333333333333</v>
+        <v>225.0609393939394</v>
       </c>
       <c r="D231" t="n">
-        <v>290.2466666666667</v>
+        <v>359.49</v>
       </c>
       <c r="E231" t="n">
-        <v>0.01326233333333333</v>
+        <v>0.02754733333333333</v>
       </c>
       <c r="F231" t="n">
-        <v>0.007608333333333333</v>
+        <v>0.02063030303030303</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>43185</v>
+        <v>44795</v>
       </c>
       <c r="B232" t="n">
-        <v>71.80666666666667</v>
+        <v>91.78333333333333</v>
       </c>
       <c r="C232" t="n">
-        <v>19.44367741935484</v>
+        <v>209.2428</v>
       </c>
       <c r="D232" t="n">
-        <v>294.38</v>
+        <v>368.8533333333334</v>
       </c>
       <c r="E232" t="n">
-        <v>0.01316333333333333</v>
+        <v>0.03388366666666667</v>
       </c>
       <c r="F232" t="n">
-        <v>0.007544516129032258</v>
+        <v>0.02674</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>43206</v>
+        <v>44823</v>
       </c>
       <c r="B233" t="n">
-        <v>75.73666666666666</v>
+        <v>91.62333333333333</v>
       </c>
       <c r="C233" t="n">
-        <v>20.99032258064516</v>
+        <v>155.0203870967742</v>
       </c>
       <c r="D233" t="n">
-        <v>293.3033333333333</v>
+        <v>373.4</v>
       </c>
       <c r="E233" t="n">
-        <v>0.01316933333333333</v>
+        <v>0.04002233333333333</v>
       </c>
       <c r="F233" t="n">
-        <v>0.007561935483870968</v>
+        <v>0.02933096774193548</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>43227</v>
+        <v>44851</v>
       </c>
       <c r="B234" t="n">
-        <v>75.67999999999999</v>
+        <v>94.09</v>
       </c>
       <c r="C234" t="n">
-        <v>22.34245161290323</v>
+        <v>133.3381666666667</v>
       </c>
       <c r="D234" t="n">
-        <v>289.41</v>
+        <v>366.4333333333333</v>
       </c>
       <c r="E234" t="n">
-        <v>0.01292533333333333</v>
+        <v>0.03726966666666667</v>
       </c>
       <c r="F234" t="n">
-        <v>0.007148709677419355</v>
+        <v>0.027943</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
-        <v>43248</v>
+        <v>44879</v>
       </c>
       <c r="B235" t="n">
-        <v>74.70666666666666</v>
+        <v>77.36</v>
       </c>
       <c r="C235" t="n">
-        <v>22.17206896551724</v>
+        <v>120.7002666666667</v>
       </c>
       <c r="D235" t="n">
-        <v>284.4633333333333</v>
+        <v>366.4133333333334</v>
       </c>
       <c r="E235" t="n">
-        <v>0.01357033333333333</v>
+        <v>0.03354466666666667</v>
       </c>
       <c r="F235" t="n">
-        <v>0.007011379310344827</v>
+        <v>0.028147</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
-        <v>43269</v>
+        <v>44907</v>
       </c>
       <c r="B236" t="n">
-        <v>77.75</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="C236" t="n">
-        <v>21.93834375</v>
+        <v>70.98165625</v>
       </c>
       <c r="D236" t="n">
-        <v>282.4933333333333</v>
+        <v>395.5833333333334</v>
       </c>
       <c r="E236" t="n">
-        <v>0.01291233333333333</v>
+        <v>0.03598633333333334</v>
       </c>
       <c r="F236" t="n">
-        <v>0.00716125</v>
+        <v>0.0309378125</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>43290</v>
+        <v>44935</v>
       </c>
       <c r="B237" t="n">
-        <v>74.74333333333334</v>
+        <v>80.64</v>
       </c>
       <c r="C237" t="n">
-        <v>22.0978125</v>
+        <v>55.44360714285714</v>
       </c>
       <c r="D237" t="n">
-        <v>275.5166666666667</v>
+        <v>398.99</v>
       </c>
       <c r="E237" t="n">
-        <v>0.013165</v>
+        <v>0.03448066666666667</v>
       </c>
       <c r="F237" t="n">
-        <v>0.007607500000000001</v>
+        <v>0.02964714285714286</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
-        <v>43311</v>
+        <v>44963</v>
       </c>
       <c r="B238" t="n">
-        <v>72.08333333333333</v>
+        <v>86.06333333333333</v>
       </c>
       <c r="C238" t="n">
-        <v>24.39545161290323</v>
+        <v>46.855</v>
       </c>
       <c r="D238" t="n">
-        <v>282.8433333333334</v>
+        <v>387.4366666666667</v>
       </c>
       <c r="E238" t="n">
-        <v>0.011835</v>
+        <v>0.038713</v>
       </c>
       <c r="F238" t="n">
-        <v>0.007220967741935484</v>
+        <v>0.03223612903225806</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
-        <v>43332</v>
+        <v>44991</v>
       </c>
       <c r="B239" t="n">
-        <v>77.19</v>
+        <v>83.21000000000001</v>
       </c>
       <c r="C239" t="n">
-        <v>26.31657142857143</v>
+        <v>47.17835714285714</v>
       </c>
       <c r="D239" t="n">
-        <v>289.96</v>
+        <v>394.35</v>
       </c>
       <c r="E239" t="n">
-        <v>0.013933</v>
+        <v>0.033277</v>
       </c>
       <c r="F239" t="n">
-        <v>0.007329285714285714</v>
+        <v>0.02999785714285715</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
-        <v>43353</v>
+        <v>45019</v>
       </c>
       <c r="B240" t="n">
-        <v>84.22666666666667</v>
+        <v>79.38666666666667</v>
       </c>
       <c r="C240" t="n">
-        <v>27.14742424242424</v>
+        <v>37.82975757575758</v>
       </c>
       <c r="D240" t="n">
-        <v>289.0033333333333</v>
+        <v>381.36</v>
       </c>
       <c r="E240" t="n">
-        <v>0.01437766666666667</v>
+        <v>0.033222</v>
       </c>
       <c r="F240" t="n">
-        <v>0.008113636363636365</v>
+        <v>0.03020878787878788</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
-        <v>43374</v>
+        <v>45047</v>
       </c>
       <c r="B241" t="n">
-        <v>79.81333333333333</v>
+        <v>77.03</v>
       </c>
       <c r="C241" t="n">
-        <v>25.24087878787878</v>
+        <v>27.91436363636364</v>
       </c>
       <c r="D241" t="n">
-        <v>294.1866666666667</v>
+        <v>377.0133333333333</v>
       </c>
       <c r="E241" t="n">
-        <v>0.014102</v>
+        <v>0.03572566666666666</v>
       </c>
       <c r="F241" t="n">
-        <v>0.007941818181818182</v>
+        <v>0.02991181818181818</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
-        <v>43395</v>
+        <v>45075</v>
       </c>
       <c r="B242" t="n">
-        <v>70.14</v>
+        <v>74.07000000000001</v>
       </c>
       <c r="C242" t="n">
-        <v>24.46426666666667</v>
+        <v>35.3945</v>
       </c>
       <c r="D242" t="n">
-        <v>306.86</v>
+        <v>363.7533333333333</v>
       </c>
       <c r="E242" t="n">
-        <v>0.014055</v>
+        <v>0.034879</v>
       </c>
       <c r="F242" t="n">
-        <v>0.007724333333333334</v>
+        <v>0.03041333333333333</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
-        <v>43416</v>
+        <v>45103</v>
       </c>
       <c r="B243" t="n">
-        <v>60.69666666666667</v>
+        <v>82.18333333333332</v>
       </c>
       <c r="C243" t="n">
-        <v>24.51622580645161</v>
+        <v>30.62070967741936</v>
       </c>
       <c r="D243" t="n">
-        <v>309.1</v>
+        <v>351.0666666666667</v>
       </c>
       <c r="E243" t="n">
-        <v>0.01434866666666667</v>
+        <v>0.035163</v>
       </c>
       <c r="F243" t="n">
-        <v>0.007468709677419355</v>
+        <v>0.0308241935483871</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
-        <v>43437</v>
+        <v>45131</v>
       </c>
       <c r="B244" t="n">
-        <v>51.58666666666667</v>
+        <v>84.57333333333332</v>
       </c>
       <c r="C244" t="n">
-        <v>22.68109677419355</v>
+        <v>32.66470967741936</v>
       </c>
       <c r="D244" t="n">
-        <v>314.55</v>
+        <v>375.9033333333333</v>
       </c>
       <c r="E244" t="n">
-        <v>0.01413066666666667</v>
+        <v>0.03695966666666667</v>
       </c>
       <c r="F244" t="n">
-        <v>0.00724516129032258</v>
+        <v>0.03084612903225806</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
-        <v>43458</v>
+        <v>45159</v>
       </c>
       <c r="B245" t="n">
-        <v>59.48666666666666</v>
+        <v>94.26333333333334</v>
       </c>
       <c r="C245" t="n">
-        <v>21.08877419354839</v>
+        <v>39.03279310344828</v>
       </c>
       <c r="D245" t="n">
-        <v>316.0266666666667</v>
+        <v>392.65</v>
       </c>
       <c r="E245" t="n">
-        <v>0.013941</v>
+        <v>0.037686</v>
       </c>
       <c r="F245" t="n">
-        <v>0.006694516129032258</v>
+        <v>0.03303931034482759</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
-        <v>43479</v>
+        <v>45187</v>
       </c>
       <c r="B246" t="n">
-        <v>62.59</v>
+        <v>90.06333333333333</v>
       </c>
       <c r="C246" t="n">
-        <v>19.63364285714286</v>
+        <v>44.9325</v>
       </c>
       <c r="D246" t="n">
-        <v>312.1733333333333</v>
+        <v>380.6933333333333</v>
       </c>
       <c r="E246" t="n">
-        <v>0.012601</v>
+        <v>0.03784633333333334</v>
       </c>
       <c r="F246" t="n">
-        <v>0.006071428571428571</v>
+        <v>0.03462</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
-        <v>43500</v>
+        <v>45215</v>
       </c>
       <c r="B247" t="n">
-        <v>65.54666666666667</v>
+        <v>82.15666666666667</v>
       </c>
       <c r="C247" t="n">
-        <v>18.10514285714286</v>
+        <v>45.64</v>
       </c>
       <c r="D247" t="n">
-        <v>312.8566666666667</v>
+        <v>358.85</v>
       </c>
       <c r="E247" t="n">
-        <v>0.01143066666666667</v>
+        <v>0.03725466666666667</v>
       </c>
       <c r="F247" t="n">
-        <v>0.006221428571428571</v>
+        <v>0.033168</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
-        <v>43521</v>
+        <v>45243</v>
       </c>
       <c r="B248" t="n">
-        <v>67.41333333333334</v>
+        <v>75.96666666666667</v>
       </c>
       <c r="C248" t="n">
-        <v>15.70306896551724</v>
+        <v>38.73203448275862</v>
       </c>
       <c r="D248" t="n">
-        <v>313.32</v>
+        <v>364.47</v>
       </c>
       <c r="E248" t="n">
-        <v>0.01074533333333333</v>
+        <v>0.03297333333333333</v>
       </c>
       <c r="F248" t="n">
-        <v>0.004860689655172414</v>
+        <v>0.02945551724137931</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
-        <v>43542</v>
+        <v>45271</v>
       </c>
       <c r="B249" t="n">
-        <v>70.84666666666666</v>
+        <v>77</v>
       </c>
       <c r="C249" t="n">
-        <v>14.2625</v>
+        <v>31.77318181818182</v>
       </c>
       <c r="D249" t="n">
-        <v>321.6533333333333</v>
+        <v>362.0133333333333</v>
       </c>
       <c r="E249" t="n">
-        <v>0.009608333333333333</v>
+        <v>0.031697</v>
       </c>
       <c r="F249" t="n">
-        <v>0.0039671875</v>
+        <v>0.02676363636363636</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
-        <v>43563</v>
+        <v>45299</v>
       </c>
       <c r="B250" t="n">
-        <v>72.07666666666667</v>
+        <v>77.77</v>
       </c>
       <c r="C250" t="n">
-        <v>14.378</v>
+        <v>29.49431034482759</v>
       </c>
       <c r="D250" t="n">
-        <v>323.0133333333333</v>
+        <v>393.81</v>
       </c>
       <c r="E250" t="n">
-        <v>0.008746333333333333</v>
+        <v>0.03284933333333333</v>
       </c>
       <c r="F250" t="n">
-        <v>0.004170625</v>
+        <v>0.0276151724137931</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
-        <v>43584</v>
+        <v>45327</v>
       </c>
       <c r="B251" t="n">
-        <v>72.05</v>
+        <v>83.05</v>
       </c>
       <c r="C251" t="n">
-        <v>12.43751612903226</v>
+        <v>25.12103448275862</v>
       </c>
       <c r="D251" t="n">
-        <v>316.2766666666666</v>
+        <v>376.8666666666667</v>
       </c>
       <c r="E251" t="n">
-        <v>0.008503</v>
+        <v>0.033953</v>
       </c>
       <c r="F251" t="n">
-        <v>0.003086774193548387</v>
+        <v>0.02907551724137931</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
-        <v>43605</v>
+        <v>45355</v>
       </c>
       <c r="B252" t="n">
-        <v>62.62333333333333</v>
+        <v>87.435</v>
       </c>
       <c r="C252" t="n">
-        <v>10.85528571428572</v>
+        <v>27.451125</v>
       </c>
       <c r="D252" t="n">
-        <v>325.9033333333334</v>
+        <v>376.8833333333333</v>
       </c>
       <c r="E252" t="n">
-        <v>0.007746</v>
+        <v>0.0329024</v>
       </c>
       <c r="F252" t="n">
-        <v>0.001833928571428571</v>
+        <v>0.0280825</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
-        <v>43626</v>
+        <v>45383</v>
       </c>
       <c r="B253" t="n">
-        <v>65.55666666666667</v>
+        <v>88.76666666666667</v>
       </c>
       <c r="C253" t="n">
-        <v>10.17039393939394</v>
+        <v>29.006875</v>
       </c>
       <c r="D253" t="n">
-        <v>331.7733333333333</v>
+        <v>374.48</v>
       </c>
       <c r="E253" t="n">
-        <v>0.005529</v>
+        <v>0.03459333333333333</v>
       </c>
       <c r="F253" t="n">
-        <v>0.0005612121212121212</v>
+        <v>0.0304975</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n">
-        <v>43647</v>
+        <v>45411</v>
       </c>
       <c r="B254" t="n">
-        <v>62.99666666666666</v>
+        <v>82.77333333333333</v>
       </c>
       <c r="C254" t="n">
-        <v>10.7310303030303</v>
+        <v>33.39961290322581</v>
       </c>
       <c r="D254" t="n">
-        <v>338.0866666666666</v>
+        <v>398.9533333333333</v>
       </c>
       <c r="E254" t="n">
-        <v>0.004748666666666667</v>
+        <v>0.035068</v>
       </c>
       <c r="F254" t="n">
-        <v>-0.0004760606060606059</v>
+        <v>0.03067</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n">
-        <v>43668</v>
+        <v>45439</v>
       </c>
       <c r="B255" t="n">
-        <v>58.55666666666666</v>
+        <v>85.75333333333333</v>
       </c>
       <c r="C255" t="n">
-        <v>11.65763333333333</v>
+        <v>34.43410714285714</v>
       </c>
       <c r="D255" t="n">
-        <v>341.6866666666667</v>
+        <v>413.59</v>
       </c>
       <c r="E255" t="n">
-        <v>0.002659</v>
+        <v>0.034574</v>
       </c>
       <c r="F255" t="n">
-        <v>-0.001993</v>
+        <v>0.03070285714285714</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
-        <v>43689</v>
+        <v>45467</v>
       </c>
       <c r="B256" t="n">
-        <v>59.25</v>
+        <v>82.47666666666667</v>
       </c>
       <c r="C256" t="n">
-        <v>13.02893548387097</v>
+        <v>35.44739393939394</v>
       </c>
       <c r="D256" t="n">
-        <v>342.4166666666667</v>
+        <v>405.29</v>
       </c>
       <c r="E256" t="n">
-        <v>0.001826</v>
+        <v>0.034317</v>
       </c>
       <c r="F256" t="n">
-        <v>-0.003681935483870967</v>
+        <v>0.02900939393939394</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n">
-        <v>43710</v>
+        <v>45495</v>
       </c>
       <c r="B257" t="n">
-        <v>64.60666666666667</v>
+        <v>78.33333333333333</v>
       </c>
       <c r="C257" t="n">
-        <v>15.46425806451613</v>
+        <v>38.241</v>
       </c>
       <c r="D257" t="n">
-        <v>340.88</v>
+        <v>392.6666666666667</v>
       </c>
       <c r="E257" t="n">
-        <v>0.003577333333333333</v>
+        <v>0.03270866666666666</v>
       </c>
       <c r="F257" t="n">
-        <v>-0.002862258064516129</v>
+        <v>0.027988</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
-        <v>43731</v>
+        <v>45523</v>
       </c>
       <c r="B258" t="n">
-        <v>59.73666666666666</v>
+        <v>72.37</v>
       </c>
       <c r="C258" t="n">
-        <v>16.28338709677419</v>
+        <v>39.42093548387096</v>
       </c>
       <c r="D258" t="n">
-        <v>357.51</v>
+        <v>378.5766666666667</v>
       </c>
       <c r="E258" t="n">
-        <v>0.004267333333333333</v>
+        <v>0.03183833333333333</v>
       </c>
       <c r="F258" t="n">
-        <v>-0.00177</v>
+        <v>0.02719612903225806</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n">
-        <v>43752</v>
+        <v>45551</v>
       </c>
       <c r="B259" t="n">
-        <v>61.98333333333333</v>
+        <v>77.98666666666666</v>
       </c>
       <c r="C259" t="n">
-        <v>16.15337931034483</v>
+        <v>39.69148387096774</v>
       </c>
       <c r="D259" t="n">
-        <v>384.1266666666667</v>
+        <v>375.1633333333333</v>
       </c>
       <c r="E259" t="n">
-        <v>0.004251</v>
+        <v>0.03286266666666667</v>
       </c>
       <c r="F259" t="n">
-        <v>-0.0006393103448275862</v>
+        <v>0.02735967741935484</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n">
-        <v>43773</v>
+        <v>45579</v>
       </c>
       <c r="B260" t="n">
-        <v>63.56333333333333</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="C260" t="n">
-        <v>16.29603448275862</v>
+        <v>43.07868965517241</v>
       </c>
       <c r="D260" t="n">
-        <v>402.1966666666667</v>
+        <v>384.5666666666667</v>
       </c>
       <c r="E260" t="n">
-        <v>0.00491</v>
+        <v>0.03281633333333333</v>
       </c>
       <c r="F260" t="n">
-        <v>-0.0002844827586206896</v>
+        <v>0.02755620689655172</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n">
-        <v>43794</v>
+        <v>45607</v>
       </c>
       <c r="B261" t="n">
-        <v>65.3</v>
+        <v>71.8</v>
       </c>
       <c r="C261" t="n">
-        <v>14.1905</v>
+        <v>48.1141875</v>
       </c>
       <c r="D261" t="n">
-        <v>384.8633333333333</v>
+        <v>407.34</v>
       </c>
       <c r="E261" t="n">
-        <v>0.005252000000000001</v>
+        <v>0.03060933333333333</v>
       </c>
       <c r="F261" t="n">
-        <v>0.00055</v>
+        <v>0.0265865625</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n">
-        <v>43815</v>
+        <v>45635</v>
       </c>
       <c r="B262" t="n">
-        <v>68.80666666666666</v>
+        <v>76.37</v>
       </c>
       <c r="C262" t="n">
-        <v>11.68067741935484</v>
+        <v>49.59029032258065</v>
       </c>
       <c r="D262" t="n">
-        <v>308.41</v>
+        <v>431.8233333333333</v>
       </c>
       <c r="E262" t="n">
-        <v>0.004964333333333334</v>
+        <v>0.03368133333333333</v>
       </c>
       <c r="F262" t="n">
-        <v>0.0008596774193548387</v>
+        <v>0.02813258064516129</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n">
-        <v>43836</v>
+        <v>45663</v>
       </c>
       <c r="B263" t="n">
-        <v>59.77666666666666</v>
+        <v>76.22666666666666</v>
       </c>
       <c r="C263" t="n">
-        <v>10.12532258064516</v>
+        <v>52.60007142857143</v>
       </c>
       <c r="D263" t="n">
-        <v>302.4133333333334</v>
+        <v>443.7833333333334</v>
       </c>
       <c r="E263" t="n">
-        <v>0.003802666666666666</v>
+        <v>0.032465</v>
       </c>
       <c r="F263" t="n">
-        <v>-0.0009896774193548386</v>
+        <v>0.02846785714285714</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n">
-        <v>43857</v>
+        <v>45691</v>
       </c>
       <c r="B264" t="n">
-        <v>57.55333333333333</v>
+        <v>72.14</v>
       </c>
       <c r="C264" t="n">
-        <v>9.251571428571429</v>
+        <v>44.08432258064516</v>
       </c>
       <c r="D264" t="n">
-        <v>315.0666666666667</v>
+        <v>446.59</v>
       </c>
       <c r="E264" t="n">
-        <v>0.003469333333333333</v>
+        <v>0.03199033333333333</v>
       </c>
       <c r="F264" t="n">
-        <v>-0.002087142857142857</v>
+        <v>0.02814</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="n">
-        <v>43878</v>
+        <v>45719</v>
       </c>
       <c r="B265" t="n">
-        <v>37.99666666666667</v>
+        <v>74.36999999999999</v>
       </c>
       <c r="C265" t="n">
-        <v>8.319375000000001</v>
+        <v>40.78483870967742</v>
       </c>
       <c r="D265" t="n">
-        <v>339.8033333333333</v>
+        <v>441.5366666666666</v>
       </c>
       <c r="E265" t="n">
-        <v>0.003203</v>
+        <v>0.03409966666666667</v>
       </c>
       <c r="F265" t="n">
-        <v>-0.00169125</v>
+        <v>0.03122</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n">
-        <v>43899</v>
+        <v>45747</v>
       </c>
       <c r="B266" t="n">
-        <v>23.48333333333333</v>
+        <v>66.19666666666667</v>
       </c>
       <c r="C266" t="n">
-        <v>7.02525</v>
+        <v>33.152</v>
       </c>
       <c r="D266" t="n">
-        <v>351.8</v>
+        <v>434.94</v>
       </c>
       <c r="E266" t="n">
-        <v>0.01253733333333333</v>
+        <v>0.03284166666666666</v>
       </c>
       <c r="F266" t="n">
-        <v>0.0003825</v>
+        <v>0.029494</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n">
-        <v>43920</v>
+        <v>45775</v>
       </c>
       <c r="B267" t="n">
-        <v>26.40666666666667</v>
+        <v>64.75333333333333</v>
       </c>
       <c r="C267" t="n">
-        <v>6.4707</v>
+        <v>33.9095</v>
       </c>
       <c r="D267" t="n">
-        <v>353.7666666666667</v>
+        <v>427.7933333333334</v>
       </c>
       <c r="E267" t="n">
-        <v>0.010108</v>
+        <v>0.03404666666666667</v>
       </c>
       <c r="F267" t="n">
-        <v>-0.0003446666666666666</v>
+        <v>0.02952333333333333</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n">
-        <v>43941</v>
+        <v>45803</v>
       </c>
       <c r="B268" t="n">
-        <v>30.07666666666666</v>
+        <v>73.32333333333334</v>
       </c>
       <c r="C268" t="n">
-        <v>5.587896551724138</v>
+        <v>33.24122580645162</v>
       </c>
       <c r="D268" t="n">
-        <v>358.86</v>
+        <v>450.0766666666667</v>
       </c>
       <c r="E268" t="n">
-        <v>0.007742333333333334</v>
+        <v>0.034136</v>
       </c>
       <c r="F268" t="n">
-        <v>-0.0008317241379310345</v>
+        <v>0.03007451612903226</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n">
-        <v>43962</v>
+        <v>45831</v>
       </c>
       <c r="B269" t="n">
-        <v>37.32333333333333</v>
+        <v>69.23333333333333</v>
       </c>
       <c r="C269" t="n">
-        <v>4.496125</v>
+        <v>34.43412903225807</v>
       </c>
       <c r="D269" t="n">
-        <v>355.4766666666667</v>
+        <v>478.49</v>
       </c>
       <c r="E269" t="n">
-        <v>0.007699333333333333</v>
+        <v>0.03407133333333334</v>
       </c>
       <c r="F269" t="n">
-        <v>-0.0007943749999999999</v>
+        <v>0.0304241935483871</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n">
-        <v>43983</v>
+        <v>45859</v>
       </c>
       <c r="B270" t="n">
-        <v>42.78333333333333</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="C270" t="n">
-        <v>5.6629375</v>
+        <v>33.13524137931034</v>
       </c>
       <c r="D270" t="n">
-        <v>346.1266666666667</v>
+        <v>484.06</v>
       </c>
       <c r="E270" t="n">
-        <v>0.005242333333333333</v>
+        <v>0.03482166666666667</v>
       </c>
       <c r="F270" t="n">
-        <v>-0.0013653125</v>
+        <v>0.03070172413793104</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="n">
-        <v>44004</v>
+        <v>45887</v>
       </c>
       <c r="B271" t="n">
-        <v>42.89333333333333</v>
+        <v>67.28999999999999</v>
       </c>
       <c r="C271" t="n">
-        <v>6.108806451612903</v>
+        <v>31.5165</v>
       </c>
       <c r="D271" t="n">
-        <v>354.3</v>
+        <v>495.3366666666666</v>
       </c>
       <c r="E271" t="n">
-        <v>0.005683333333333334</v>
+        <v>0.034548</v>
       </c>
       <c r="F271" t="n">
-        <v>-0.001803548387096774</v>
+        <v>0.03085</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n">
-        <v>44025</v>
+        <v>45915</v>
       </c>
       <c r="B272" t="n">
-        <v>43.86666666666667</v>
+        <v>63.12333333333333</v>
       </c>
       <c r="C272" t="n">
-        <v>6.359516129032258</v>
+        <v>31.29912903225807</v>
       </c>
       <c r="D272" t="n">
-        <v>355.1633333333334</v>
+        <v>524.8533333333334</v>
       </c>
       <c r="E272" t="n">
-        <v>0.003734</v>
+        <v>0.03399733333333334</v>
       </c>
       <c r="F272" t="n">
-        <v>-0.002039032258064516</v>
+        <v>0.03063387096774194</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n">
-        <v>44046</v>
+        <v>45943</v>
       </c>
       <c r="B273" t="n">
-        <v>44.87</v>
+        <v>63.91666666666667</v>
       </c>
       <c r="C273" t="n">
-        <v>9.892935483870968</v>
+        <v>30.38110714285714</v>
       </c>
       <c r="D273" t="n">
-        <v>374.46</v>
+        <v>569.5266666666666</v>
       </c>
       <c r="E273" t="n">
-        <v>0.003201666666666666</v>
+        <v>0.03446766666666667</v>
       </c>
       <c r="F273" t="n">
-        <v>-0.001293870967741936</v>
+        <v>0.03043357142857143</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n">
-        <v>44067</v>
+        <v>45971</v>
       </c>
       <c r="B274" t="n">
-        <v>39.68333333333333</v>
+        <v>62.91</v>
       </c>
       <c r="C274" t="n">
-        <v>12.12603333333333</v>
+        <v>28.63809090909091</v>
       </c>
       <c r="D274" t="n">
-        <v>368.5533333333333</v>
+        <v>548.14</v>
       </c>
       <c r="E274" t="n">
-        <v>0.003331666666666667</v>
+        <v>0.03630533333333333</v>
       </c>
       <c r="F274" t="n">
-        <v>-0.001434666666666667</v>
+        <v>0.03114090909090909</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n">
-        <v>44088</v>
+        <v>45999</v>
       </c>
       <c r="B275" t="n">
-        <v>40.61666666666667</v>
+        <v>61.42333333333333</v>
       </c>
       <c r="C275" t="n">
-        <v>13.38933333333333</v>
-      </c>
-      <c r="D275" t="n">
-        <v>387.04</v>
-      </c>
+        <v>29.6442</v>
+      </c>
+      <c r="D275" t="inlineStr"/>
       <c r="E275" t="n">
-        <v>0.003055666666666667</v>
+        <v>0.03672766666666667</v>
       </c>
       <c r="F275" t="n">
-        <v>-0.002182</v>
+        <v>0.03196466666666667</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n">
-        <v>44109</v>
+        <v>46027</v>
       </c>
       <c r="B276" t="n">
-        <v>40.89666666666667</v>
+        <v>67.76333333333334</v>
       </c>
       <c r="C276" t="n">
-        <v>13.93183333333333</v>
-      </c>
-      <c r="D276" t="n">
-        <v>393.8733333333333</v>
-      </c>
+        <v>38.76171428571428</v>
+      </c>
+      <c r="D276" t="inlineStr"/>
       <c r="E276" t="n">
-        <v>0.002086</v>
+        <v>0.03590266666666667</v>
       </c>
       <c r="F276" t="n">
-        <v>-0.00319</v>
+        <v>0.03127285714285714</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n">
-        <v>44130</v>
+        <v>46055</v>
       </c>
       <c r="B277" t="n">
-        <v>43.47333333333334</v>
+        <v>75.98666666666666</v>
       </c>
       <c r="C277" t="n">
-        <v>14.61687096774194</v>
-      </c>
-      <c r="D277" t="n">
-        <v>375.3733333333333</v>
-      </c>
+        <v>33.77028</v>
+      </c>
+      <c r="D277" t="inlineStr"/>
       <c r="E277" t="n">
-        <v>0.001583333333333334</v>
+        <v>0.03484</v>
       </c>
       <c r="F277" t="n">
-        <v>-0.00366741935483871</v>
+        <v>0.02986083333333333</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n">
-        <v>44151</v>
+        <v>46083</v>
       </c>
       <c r="B278" t="n">
-        <v>48.94333333333334</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="C278" t="n">
-        <v>15.90929032258065</v>
-      </c>
-      <c r="D278" t="n">
-        <v>351.31</v>
-      </c>
+        <v>54.6</v>
+      </c>
+      <c r="D278" t="inlineStr"/>
       <c r="E278" t="n">
-        <v>0.001334333333333333</v>
+        <v>0.036821</v>
       </c>
       <c r="F278" t="n">
-        <v>-0.003920967741935484</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" s="2" t="n">
-        <v>44172</v>
-      </c>
-      <c r="B279" t="n">
-        <v>50.9675</v>
-      </c>
-      <c r="C279" t="n">
-        <v>18.6088064516129</v>
-      </c>
-      <c r="D279" t="n">
-        <v>375.57</v>
-      </c>
-      <c r="E279" t="n">
-        <v>0.0016925</v>
-      </c>
-      <c r="F279" t="n">
-        <v>-0.004029354838709678</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" s="2" t="n">
-        <v>44193</v>
-      </c>
-      <c r="B280" t="n">
-        <v>54.86666666666667</v>
-      </c>
-      <c r="C280" t="n">
-        <v>19.531</v>
-      </c>
-      <c r="D280" t="n">
-        <v>389.62</v>
-      </c>
-      <c r="E280" t="n">
-        <v>0.001408</v>
-      </c>
-      <c r="F280" t="n">
-        <v>-0.00371</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="2" t="n">
-        <v>44214</v>
-      </c>
-      <c r="B281" t="n">
-        <v>60.15333333333334</v>
-      </c>
-      <c r="C281" t="n">
-        <v>18.49310714285714</v>
-      </c>
-      <c r="D281" t="n">
-        <v>383.29</v>
-      </c>
-      <c r="E281" t="n">
-        <v>0.002125333333333334</v>
-      </c>
-      <c r="F281" t="n">
-        <v>-0.002624642857142857</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="2" t="n">
-        <v>44235</v>
-      </c>
-      <c r="B282" t="n">
-        <v>64.50333333333333</v>
-      </c>
-      <c r="C282" t="n">
-        <v>15.894</v>
-      </c>
-      <c r="D282" t="n">
-        <v>387.0466666666667</v>
-      </c>
-      <c r="E282" t="n">
-        <v>0.003493333333333333</v>
-      </c>
-      <c r="F282" t="n">
-        <v>-0.0008315151515151516</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" s="2" t="n">
-        <v>44256</v>
-      </c>
-      <c r="B283" t="n">
-        <v>64.59</v>
-      </c>
-      <c r="C283" t="n">
-        <v>17.994</v>
-      </c>
-      <c r="D283" t="n">
-        <v>386.0266666666666</v>
-      </c>
-      <c r="E283" t="n">
-        <v>0.003452666666666667</v>
-      </c>
-      <c r="F283" t="n">
-        <v>-0.0007424242424242425</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" s="2" t="n">
-        <v>44277</v>
-      </c>
-      <c r="B284" t="n">
-        <v>63.17</v>
-      </c>
-      <c r="C284" t="n">
-        <v>20.56736666666666</v>
-      </c>
-      <c r="D284" t="n">
-        <v>381.975</v>
-      </c>
-      <c r="E284" t="n">
-        <v>0.003639666666666666</v>
-      </c>
-      <c r="F284" t="n">
-        <v>-0.000392</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" s="2" t="n">
-        <v>44298</v>
-      </c>
-      <c r="B285" t="n">
-        <v>67.45666666666666</v>
-      </c>
-      <c r="C285" t="n">
-        <v>23.40358064516129</v>
-      </c>
-      <c r="D285" t="n">
-        <v>382.9966666666667</v>
-      </c>
-      <c r="E285" t="n">
-        <v>0.004332666666666667</v>
-      </c>
-      <c r="F285" t="n">
-        <v>0.0001748387096774194</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" s="2" t="n">
-        <v>44319</v>
-      </c>
-      <c r="B286" t="n">
-        <v>67.78666666666666</v>
-      </c>
-      <c r="C286" t="n">
-        <v>24.64867741935484</v>
-      </c>
-      <c r="D286" t="n">
-        <v>394.0866666666666</v>
-      </c>
-      <c r="E286" t="n">
-        <v>0.005069666666666667</v>
-      </c>
-      <c r="F286" t="n">
-        <v>0.0005406451612903226</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" s="2" t="n">
-        <v>44340</v>
-      </c>
-      <c r="B287" t="n">
-        <v>72.80333333333333</v>
-      </c>
-      <c r="C287" t="n">
-        <v>29.23923333333333</v>
-      </c>
-      <c r="D287" t="n">
-        <v>389.73</v>
-      </c>
-      <c r="E287" t="n">
-        <v>0.004084333333333333</v>
-      </c>
-      <c r="F287" t="n">
-        <v>0.000615</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" s="2" t="n">
-        <v>44361</v>
-      </c>
-      <c r="B288" t="n">
-        <v>76.83</v>
-      </c>
-      <c r="C288" t="n">
-        <v>35.43986666666667</v>
-      </c>
-      <c r="D288" t="n">
-        <v>365.14</v>
-      </c>
-      <c r="E288" t="n">
-        <v>0.004342666666666667</v>
-      </c>
-      <c r="F288" t="n">
-        <v>0.000246</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" s="2" t="n">
-        <v>44382</v>
-      </c>
-      <c r="B289" t="n">
-        <v>74.36666666666666</v>
-      </c>
-      <c r="C289" t="n">
-        <v>39.73366666666666</v>
-      </c>
-      <c r="D289" t="n">
-        <v>382.31</v>
-      </c>
-      <c r="E289" t="n">
-        <v>0.002676</v>
-      </c>
-      <c r="F289" t="n">
-        <v>-0.001245</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" s="2" t="n">
-        <v>44403</v>
-      </c>
-      <c r="B290" t="n">
-        <v>69.87</v>
-      </c>
-      <c r="C290" t="n">
-        <v>45.547</v>
-      </c>
-      <c r="D290" t="n">
-        <v>386.8633333333333</v>
-      </c>
-      <c r="E290" t="n">
-        <v>0.002305</v>
-      </c>
-      <c r="F290" t="n">
-        <v>-0.00142</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="2" t="n">
-        <v>44424</v>
-      </c>
-      <c r="B291" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="C291" t="n">
-        <v>58.244</v>
-      </c>
-      <c r="D291" t="n">
-        <v>386.2866666666667</v>
-      </c>
-      <c r="E291" t="n">
-        <v>0.003327</v>
-      </c>
-      <c r="F291" t="n">
-        <v>-0.0009283333333333333</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" s="2" t="n">
-        <v>44445</v>
-      </c>
-      <c r="B292" t="n">
-        <v>79.05</v>
-      </c>
-      <c r="C292" t="n">
-        <v>91.44919999999999</v>
-      </c>
-      <c r="D292" t="n">
-        <v>396.45</v>
-      </c>
-      <c r="E292" t="n">
-        <v>0.004749</v>
-      </c>
-      <c r="F292" t="n">
-        <v>0.0003806666666666667</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" s="2" t="n">
-        <v>44466</v>
-      </c>
-      <c r="B293" t="n">
-        <v>84.50666666666666</v>
-      </c>
-      <c r="C293" t="n">
-        <v>78.48193103448276</v>
-      </c>
-      <c r="D293" t="n">
-        <v>394.4233333333333</v>
-      </c>
-      <c r="E293" t="n">
-        <v>0.005678666666666666</v>
-      </c>
-      <c r="F293" t="n">
-        <v>0.001268965517241379</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" s="2" t="n">
-        <v>44487</v>
-      </c>
-      <c r="B294" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="C294" t="n">
-        <v>72.64028125</v>
-      </c>
-      <c r="D294" t="n">
-        <v>396.43</v>
-      </c>
-      <c r="E294" t="n">
-        <v>0.004699333333333333</v>
-      </c>
-      <c r="F294" t="n">
-        <v>0.001253125</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" s="2" t="n">
-        <v>44508</v>
-      </c>
-      <c r="B295" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="C295" t="n">
-        <v>90.78493750000001</v>
-      </c>
-      <c r="D295" t="n">
-        <v>378.7533333333333</v>
-      </c>
-      <c r="E295" t="n">
-        <v>0.006180333333333334</v>
-      </c>
-      <c r="F295" t="n">
-        <v>0.0001637500000000001</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" s="2" t="n">
-        <v>44529</v>
-      </c>
-      <c r="B296" t="n">
-        <v>72.18666666666667</v>
-      </c>
-      <c r="C296" t="n">
-        <v>78.92493548387097</v>
-      </c>
-      <c r="D296" t="n">
-        <v>378.4833333333333</v>
-      </c>
-      <c r="E296" t="n">
-        <v>0.004617</v>
-      </c>
-      <c r="F296" t="n">
-        <v>0.0009303225806451613</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" s="2" t="n">
-        <v>44550</v>
-      </c>
-      <c r="B297" t="n">
-        <v>81.16333333333334</v>
-      </c>
-      <c r="C297" t="n">
-        <v>74.50303225806452</v>
-      </c>
-      <c r="D297" t="n">
-        <v>397.44</v>
-      </c>
-      <c r="E297" t="n">
-        <v>0.007433333333333333</v>
-      </c>
-      <c r="F297" t="n">
-        <v>0.002028709677419355</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" s="2" t="n">
-        <v>44571</v>
-      </c>
-      <c r="B298" t="n">
-        <v>90.81666666666666</v>
-      </c>
-      <c r="C298" t="n">
-        <v>84.20977419354838</v>
-      </c>
-      <c r="D298" t="n">
-        <v>399.2333333333333</v>
-      </c>
-      <c r="E298" t="n">
-        <v>0.008683333333333335</v>
-      </c>
-      <c r="F298" t="n">
-        <v>0.003309032258064516</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" s="2" t="n">
-        <v>44592</v>
-      </c>
-      <c r="B299" t="n">
-        <v>94.77333333333334</v>
-      </c>
-      <c r="C299" t="n">
-        <v>94.617</v>
-      </c>
-      <c r="D299" t="n">
-        <v>396.2433333333333</v>
-      </c>
-      <c r="E299" t="n">
-        <v>0.01197166666666667</v>
-      </c>
-      <c r="F299" t="n">
-        <v>0.005770000000000001</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="2" t="n">
-        <v>44613</v>
-      </c>
-      <c r="B300" t="n">
-        <v>108.8233333333333</v>
-      </c>
-      <c r="C300" t="n">
-        <v>110.048</v>
-      </c>
-      <c r="D300" t="n">
-        <v>383.9933333333333</v>
-      </c>
-      <c r="E300" t="n">
-        <v>0.01527</v>
-      </c>
-      <c r="F300" t="n">
-        <v>0.008386451612903226</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" s="2" t="n">
-        <v>44634</v>
-      </c>
-      <c r="B301" t="n">
-        <v>106.4833333333333</v>
-      </c>
-      <c r="C301" t="n">
-        <v>123.1691724137931</v>
-      </c>
-      <c r="D301" t="n">
-        <v>354.22</v>
-      </c>
-      <c r="E301" t="n">
-        <v>0.016363</v>
-      </c>
-      <c r="F301" t="n">
-        <v>0.01116413793103448</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" s="2" t="n">
-        <v>44655</v>
-      </c>
-      <c r="B302" t="n">
-        <v>103.7633333333333</v>
-      </c>
-      <c r="C302" t="n">
-        <v>104.0113793103448</v>
-      </c>
-      <c r="D302" t="n">
-        <v>359.33</v>
-      </c>
-      <c r="E302" t="n">
-        <v>0.01990433333333333</v>
-      </c>
-      <c r="F302" t="n">
-        <v>0.01455310344827586</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" s="2" t="n">
-        <v>44676</v>
-      </c>
-      <c r="B303" t="n">
-        <v>113.3433333333333</v>
-      </c>
-      <c r="C303" t="n">
-        <v>96.727</v>
-      </c>
-      <c r="D303" t="n">
-        <v>381.1933333333333</v>
-      </c>
-      <c r="E303" t="n">
-        <v>0.02187066666666667</v>
-      </c>
-      <c r="F303" t="n">
-        <v>0.016165</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="2" t="n">
-        <v>44697</v>
-      </c>
-      <c r="B304" t="n">
-        <v>119.58</v>
-      </c>
-      <c r="C304" t="n">
-        <v>102.4223333333333</v>
-      </c>
-      <c r="D304" t="n">
-        <v>354.8833333333333</v>
-      </c>
-      <c r="E304" t="n">
-        <v>0.02586833333333333</v>
-      </c>
-      <c r="F304" t="n">
-        <v>0.01760166666666666</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="2" t="n">
-        <v>44718</v>
-      </c>
-      <c r="B305" t="n">
-        <v>114.4333333333333</v>
-      </c>
-      <c r="C305" t="n">
-        <v>137.7793333333333</v>
-      </c>
-      <c r="D305" t="n">
-        <v>355.82</v>
-      </c>
-      <c r="E305" t="n">
-        <v>0.030201</v>
-      </c>
-      <c r="F305" t="n">
-        <v>0.02025466666666667</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" s="2" t="n">
-        <v>44739</v>
-      </c>
-      <c r="B306" t="n">
-        <v>104.5666666666667</v>
-      </c>
-      <c r="C306" t="n">
-        <v>171.7145862068965</v>
-      </c>
-      <c r="D306" t="n">
-        <v>310.29</v>
-      </c>
-      <c r="E306" t="n">
-        <v>0.026411</v>
-      </c>
-      <c r="F306" t="n">
-        <v>0.01762379310344828</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" s="2" t="n">
-        <v>44760</v>
-      </c>
-      <c r="B307" t="n">
-        <v>96.07333333333334</v>
-      </c>
-      <c r="C307" t="n">
-        <v>204.2764545454546</v>
-      </c>
-      <c r="D307" t="n">
-        <v>342.01</v>
-      </c>
-      <c r="E307" t="n">
-        <v>0.02252666666666667</v>
-      </c>
-      <c r="F307" t="n">
-        <v>0.01745272727272727</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" s="2" t="n">
-        <v>44781</v>
-      </c>
-      <c r="B308" t="n">
-        <v>103.7233333333333</v>
-      </c>
-      <c r="C308" t="n">
-        <v>235.4531818181818</v>
-      </c>
-      <c r="D308" t="n">
-        <v>369.6866666666667</v>
-      </c>
-      <c r="E308" t="n">
-        <v>0.03009366666666667</v>
-      </c>
-      <c r="F308" t="n">
-        <v>0.02221909090909091</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" s="2" t="n">
-        <v>44802</v>
-      </c>
-      <c r="B309" t="n">
-        <v>91.78333333333333</v>
-      </c>
-      <c r="C309" t="n">
-        <v>209.2428</v>
-      </c>
-      <c r="D309" t="n">
-        <v>368.8533333333334</v>
-      </c>
-      <c r="E309" t="n">
-        <v>0.03388366666666667</v>
-      </c>
-      <c r="F309" t="n">
-        <v>0.02674</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" s="2" t="n">
-        <v>44823</v>
-      </c>
-      <c r="B310" t="n">
-        <v>96.76666666666667</v>
-      </c>
-      <c r="C310" t="n">
-        <v>169.7989677419355</v>
-      </c>
-      <c r="D310" t="n">
-        <v>367.4233333333333</v>
-      </c>
-      <c r="E310" t="n">
-        <v>0.03957433333333334</v>
-      </c>
-      <c r="F310" t="n">
-        <v>0.02931741935483871</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" s="2" t="n">
-        <v>44844</v>
-      </c>
-      <c r="B311" t="n">
-        <v>95.14333333333333</v>
-      </c>
-      <c r="C311" t="n">
-        <v>125.4632258064516</v>
-      </c>
-      <c r="D311" t="n">
-        <v>369.6533333333334</v>
-      </c>
-      <c r="E311" t="n">
-        <v>0.03926166666666667</v>
-      </c>
-      <c r="F311" t="n">
-        <v>0.02935806451612903</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" s="2" t="n">
-        <v>44865</v>
-      </c>
-      <c r="B312" t="n">
-        <v>87.50666666666667</v>
-      </c>
-      <c r="C312" t="n">
-        <v>138.7153333333333</v>
-      </c>
-      <c r="D312" t="n">
-        <v>370.5566666666667</v>
-      </c>
-      <c r="E312" t="n">
-        <v>0.03552133333333334</v>
-      </c>
-      <c r="F312" t="n">
-        <v>0.02718</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" s="2" t="n">
-        <v>44886</v>
-      </c>
-      <c r="B313" t="n">
-        <v>77.36</v>
-      </c>
-      <c r="C313" t="n">
-        <v>120.7002666666667</v>
-      </c>
-      <c r="D313" t="n">
-        <v>366.4133333333334</v>
-      </c>
-      <c r="E313" t="n">
-        <v>0.03354466666666667</v>
-      </c>
-      <c r="F313" t="n">
-        <v>0.028147</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" s="2" t="n">
-        <v>44907</v>
-      </c>
-      <c r="B314" t="n">
-        <v>85.91</v>
-      </c>
-      <c r="C314" t="n">
-        <v>75.1298125</v>
-      </c>
-      <c r="D314" t="n">
-        <v>383.5366666666666</v>
-      </c>
-      <c r="E314" t="n">
-        <v>0.03883233333333334</v>
-      </c>
-      <c r="F314" t="n">
-        <v>0.031530625</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="2" t="n">
-        <v>44928</v>
-      </c>
-      <c r="B315" t="n">
-        <v>88.00333333333333</v>
-      </c>
-      <c r="C315" t="n">
-        <v>62.68534375</v>
-      </c>
-      <c r="D315" t="n">
-        <v>397.21</v>
-      </c>
-      <c r="E315" t="n">
-        <v>0.03506833333333333</v>
-      </c>
-      <c r="F315" t="n">
-        <v>0.0297521875</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" s="2" t="n">
-        <v>44949</v>
-      </c>
-      <c r="B316" t="n">
-        <v>86.53666666666666</v>
-      </c>
-      <c r="C316" t="n">
-        <v>52.77185714285714</v>
-      </c>
-      <c r="D316" t="n">
-        <v>401.09</v>
-      </c>
-      <c r="E316" t="n">
-        <v>0.03593333333333333</v>
-      </c>
-      <c r="F316" t="n">
-        <v>0.03056714285714286</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" s="2" t="n">
-        <v>44970</v>
-      </c>
-      <c r="B317" t="n">
-        <v>86.06333333333333</v>
-      </c>
-      <c r="C317" t="n">
-        <v>46.855</v>
-      </c>
-      <c r="D317" t="n">
-        <v>387.4366666666667</v>
-      </c>
-      <c r="E317" t="n">
-        <v>0.038713</v>
-      </c>
-      <c r="F317" t="n">
-        <v>0.03223612903225806</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" s="2" t="n">
-        <v>44991</v>
-      </c>
-      <c r="B318" t="n">
-        <v>77.07666666666667</v>
-      </c>
-      <c r="C318" t="n">
-        <v>47.65300000000001</v>
-      </c>
-      <c r="D318" t="n">
-        <v>386.5333333333334</v>
-      </c>
-      <c r="E318" t="n">
-        <v>0.032597</v>
-      </c>
-      <c r="F318" t="n">
-        <v>0.03041387096774194</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" s="2" t="n">
-        <v>45012</v>
-      </c>
-      <c r="B319" t="n">
-        <v>85.27666666666667</v>
-      </c>
-      <c r="C319" t="n">
-        <v>42.52585714285714</v>
-      </c>
-      <c r="D319" t="n">
-        <v>380.6733333333333</v>
-      </c>
-      <c r="E319" t="n">
-        <v>0.03480866666666667</v>
-      </c>
-      <c r="F319" t="n">
-        <v>0.03012285714285715</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" s="2" t="n">
-        <v>45033</v>
-      </c>
-      <c r="B320" t="n">
-        <v>76.44</v>
-      </c>
-      <c r="C320" t="n">
-        <v>35.35090909090909</v>
-      </c>
-      <c r="D320" t="n">
-        <v>367.7166666666666</v>
-      </c>
-      <c r="E320" t="n">
-        <v>0.033303</v>
-      </c>
-      <c r="F320" t="n">
-        <v>0.03013454545454546</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" s="2" t="n">
-        <v>45054</v>
-      </c>
-      <c r="B321" t="n">
-        <v>77.03</v>
-      </c>
-      <c r="C321" t="n">
-        <v>27.91436363636364</v>
-      </c>
-      <c r="D321" t="n">
-        <v>377.0133333333333</v>
-      </c>
-      <c r="E321" t="n">
-        <v>0.03572566666666666</v>
-      </c>
-      <c r="F321" t="n">
-        <v>0.02991181818181818</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" s="2" t="n">
-        <v>45075</v>
-      </c>
-      <c r="B322" t="n">
-        <v>76.26333333333334</v>
-      </c>
-      <c r="C322" t="n">
-        <v>33.0026</v>
-      </c>
-      <c r="D322" t="n">
-        <v>375.9133333333333</v>
-      </c>
-      <c r="E322" t="n">
-        <v>0.03635766666666667</v>
-      </c>
-      <c r="F322" t="n">
-        <v>0.030264</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" s="2" t="n">
-        <v>45096</v>
-      </c>
-      <c r="B323" t="n">
-        <v>77.95</v>
-      </c>
-      <c r="C323" t="n">
-        <v>34.56645161290323</v>
-      </c>
-      <c r="D323" t="n">
-        <v>350.3333333333333</v>
-      </c>
-      <c r="E323" t="n">
-        <v>0.03768</v>
-      </c>
-      <c r="F323" t="n">
-        <v>0.03063903225806452</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" s="2" t="n">
-        <v>45117</v>
-      </c>
-      <c r="B324" t="n">
-        <v>85.37</v>
-      </c>
-      <c r="C324" t="n">
-        <v>28.64783870967742</v>
-      </c>
-      <c r="D324" t="n">
-        <v>357.1866666666667</v>
-      </c>
-      <c r="E324" t="n">
-        <v>0.03535733333333333</v>
-      </c>
-      <c r="F324" t="n">
-        <v>0.03091677419354839</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" s="2" t="n">
-        <v>45138</v>
-      </c>
-      <c r="B325" t="n">
-        <v>84.57333333333332</v>
-      </c>
-      <c r="C325" t="n">
-        <v>32.66470967741936</v>
-      </c>
-      <c r="D325" t="n">
-        <v>375.9033333333333</v>
-      </c>
-      <c r="E325" t="n">
-        <v>0.03695966666666667</v>
-      </c>
-      <c r="F325" t="n">
-        <v>0.03084612903225806</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" s="2" t="n">
-        <v>45159</v>
-      </c>
-      <c r="B326" t="n">
-        <v>90.64333333333333</v>
-      </c>
-      <c r="C326" t="n">
-        <v>37.38417241379311</v>
-      </c>
-      <c r="D326" t="n">
-        <v>391.5433333333334</v>
-      </c>
-      <c r="E326" t="n">
-        <v>0.03703633333333334</v>
-      </c>
-      <c r="F326" t="n">
-        <v>0.03211724137931034</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" s="2" t="n">
-        <v>45180</v>
-      </c>
-      <c r="B327" t="n">
-        <v>92.24333333333333</v>
-      </c>
-      <c r="C327" t="n">
-        <v>42.2431875</v>
-      </c>
-      <c r="D327" t="n">
-        <v>396.74</v>
-      </c>
-      <c r="E327" t="n">
-        <v>0.03865</v>
-      </c>
-      <c r="F327" t="n">
-        <v>0.03462</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" s="2" t="n">
-        <v>45201</v>
-      </c>
-      <c r="B328" t="n">
-        <v>90.60666666666667</v>
-      </c>
-      <c r="C328" t="n">
-        <v>46.27715625</v>
-      </c>
-      <c r="D328" t="n">
-        <v>374.6133333333333</v>
-      </c>
-      <c r="E328" t="n">
-        <v>0.03910466666666667</v>
-      </c>
-      <c r="F328" t="n">
-        <v>0.03462</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" s="2" t="n">
-        <v>45222</v>
-      </c>
-      <c r="B329" t="n">
-        <v>82.15666666666667</v>
-      </c>
-      <c r="C329" t="n">
-        <v>45.64</v>
-      </c>
-      <c r="D329" t="n">
-        <v>358.85</v>
-      </c>
-      <c r="E329" t="n">
-        <v>0.03725466666666667</v>
-      </c>
-      <c r="F329" t="n">
-        <v>0.033168</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" s="2" t="n">
-        <v>45243</v>
-      </c>
-      <c r="B330" t="n">
-        <v>78.31333333333333</v>
-      </c>
-      <c r="C330" t="n">
-        <v>41.08331034482759</v>
-      </c>
-      <c r="D330" t="n">
-        <v>367.5666666666667</v>
-      </c>
-      <c r="E330" t="n">
-        <v>0.03328866666666667</v>
-      </c>
-      <c r="F330" t="n">
-        <v>0.0305296551724138</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" s="2" t="n">
-        <v>45264</v>
-      </c>
-      <c r="B331" t="n">
-        <v>80.06999999999999</v>
-      </c>
-      <c r="C331" t="n">
-        <v>34.02948275862069</v>
-      </c>
-      <c r="D331" t="n">
-        <v>369.89</v>
-      </c>
-      <c r="E331" t="n">
-        <v>0.0292848</v>
-      </c>
-      <c r="F331" t="n">
-        <v>0.02730724137931034</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" s="2" t="n">
-        <v>45285</v>
-      </c>
-      <c r="B332" t="n">
-        <v>78.19666666666667</v>
-      </c>
-      <c r="C332" t="n">
-        <v>31.32454545454545</v>
-      </c>
-      <c r="D332" t="n">
-        <v>371.63</v>
-      </c>
-      <c r="E332" t="n">
-        <v>0.03205233333333334</v>
-      </c>
-      <c r="F332" t="n">
-        <v>0.02693757575757576</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" s="2" t="n">
-        <v>45306</v>
-      </c>
-      <c r="B333" t="n">
-        <v>77.77</v>
-      </c>
-      <c r="C333" t="n">
-        <v>29.49431034482759</v>
-      </c>
-      <c r="D333" t="n">
-        <v>393.81</v>
-      </c>
-      <c r="E333" t="n">
-        <v>0.03284933333333333</v>
-      </c>
-      <c r="F333" t="n">
-        <v>0.0276151724137931</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" s="2" t="n">
-        <v>45327</v>
-      </c>
-      <c r="B334" t="n">
-        <v>82.22666666666667</v>
-      </c>
-      <c r="C334" t="n">
-        <v>25.60568965517241</v>
-      </c>
-      <c r="D334" t="n">
-        <v>387.46</v>
-      </c>
-      <c r="E334" t="n">
-        <v>0.033935</v>
-      </c>
-      <c r="F334" t="n">
-        <v>0.0289548275862069</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" s="2" t="n">
-        <v>45348</v>
-      </c>
-      <c r="B335" t="n">
-        <v>86.37333333333333</v>
-      </c>
-      <c r="C335" t="n">
-        <v>26.31586206896552</v>
-      </c>
-      <c r="D335" t="n">
-        <v>379.1433333333333</v>
-      </c>
-      <c r="E335" t="n">
-        <v>0.033847</v>
-      </c>
-      <c r="F335" t="n">
-        <v>0.02844793103448276</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="2" t="n">
-        <v>45369</v>
-      </c>
-      <c r="B336" t="n">
-        <v>90.64333333333333</v>
-      </c>
-      <c r="C336" t="n">
-        <v>27.8400625</v>
-      </c>
-      <c r="D336" t="n">
-        <v>377.6466666666666</v>
-      </c>
-      <c r="E336" t="n">
-        <v>0.03335666666666667</v>
-      </c>
-      <c r="F336" t="n">
-        <v>0.02868625</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" s="2" t="n">
-        <v>45390</v>
-      </c>
-      <c r="B337" t="n">
-        <v>88.76666666666667</v>
-      </c>
-      <c r="C337" t="n">
-        <v>29.006875</v>
-      </c>
-      <c r="D337" t="n">
-        <v>374.48</v>
-      </c>
-      <c r="E337" t="n">
-        <v>0.03459333333333333</v>
-      </c>
-      <c r="F337" t="n">
-        <v>0.0304975</v>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" s="2" t="n">
-        <v>45411</v>
-      </c>
-      <c r="B338" t="n">
-        <v>83.8</v>
-      </c>
-      <c r="C338" t="n">
-        <v>32.24687096774193</v>
-      </c>
-      <c r="D338" t="n">
-        <v>393.63</v>
-      </c>
-      <c r="E338" t="n">
-        <v>0.034715</v>
-      </c>
-      <c r="F338" t="n">
-        <v>0.03067</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" s="2" t="n">
-        <v>45432</v>
-      </c>
-      <c r="B339" t="n">
-        <v>80.95999999999999</v>
-      </c>
-      <c r="C339" t="n">
-        <v>34.30560714285714</v>
-      </c>
-      <c r="D339" t="n">
-        <v>414.69</v>
-      </c>
-      <c r="E339" t="n">
-        <v>0.03579566666666666</v>
-      </c>
-      <c r="F339" t="n">
-        <v>0.03068285714285714</v>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" s="2" t="n">
-        <v>45453</v>
-      </c>
-      <c r="B340" t="n">
-        <v>86.53666666666666</v>
-      </c>
-      <c r="C340" t="n">
-        <v>34.56412121212121</v>
-      </c>
-      <c r="D340" t="n">
-        <v>400.43</v>
-      </c>
-      <c r="E340" t="n">
-        <v>0.03557233333333333</v>
-      </c>
-      <c r="F340" t="n">
-        <v>0.03056212121212121</v>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" s="2" t="n">
-        <v>45474</v>
-      </c>
-      <c r="B341" t="n">
-        <v>82.47666666666667</v>
-      </c>
-      <c r="C341" t="n">
-        <v>35.44739393939394</v>
-      </c>
-      <c r="D341" t="n">
-        <v>405.29</v>
-      </c>
-      <c r="E341" t="n">
-        <v>0.034317</v>
-      </c>
-      <c r="F341" t="n">
-        <v>0.02900939393939394</v>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" s="2" t="n">
-        <v>45495</v>
-      </c>
-      <c r="B342" t="n">
-        <v>81.42</v>
-      </c>
-      <c r="C342" t="n">
-        <v>37.31816666666667</v>
-      </c>
-      <c r="D342" t="n">
-        <v>389.9233333333333</v>
-      </c>
-      <c r="E342" t="n">
-        <v>0.032527</v>
-      </c>
-      <c r="F342" t="n">
-        <v>0.02809766666666667</v>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" s="2" t="n">
-        <v>45516</v>
-      </c>
-      <c r="B343" t="n">
-        <v>77.94666666666666</v>
-      </c>
-      <c r="C343" t="n">
-        <v>39.77274193548387</v>
-      </c>
-      <c r="D343" t="n">
-        <v>390.6166666666667</v>
-      </c>
-      <c r="E343" t="n">
-        <v>0.03324466666666667</v>
-      </c>
-      <c r="F343" t="n">
-        <v>0.02772451612903225</v>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" s="2" t="n">
-        <v>45537</v>
-      </c>
-      <c r="B344" t="n">
-        <v>74.09666666666666</v>
-      </c>
-      <c r="C344" t="n">
-        <v>39.24503225806451</v>
-      </c>
-      <c r="D344" t="n">
-        <v>389.3733333333333</v>
-      </c>
-      <c r="E344" t="n">
-        <v>0.03204433333333333</v>
-      </c>
-      <c r="F344" t="n">
-        <v>0.02693193548387096</v>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" s="2" t="n">
-        <v>45558</v>
-      </c>
-      <c r="B345" t="n">
-        <v>77.98666666666666</v>
-      </c>
-      <c r="C345" t="n">
-        <v>39.69148387096774</v>
-      </c>
-      <c r="D345" t="n">
-        <v>375.1633333333333</v>
-      </c>
-      <c r="E345" t="n">
-        <v>0.03286266666666667</v>
-      </c>
-      <c r="F345" t="n">
-        <v>0.02735967741935484</v>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" s="2" t="n">
-        <v>45579</v>
-      </c>
-      <c r="B346" t="n">
-        <v>74.42</v>
-      </c>
-      <c r="C346" t="n">
-        <v>41.33520689655172</v>
-      </c>
-      <c r="D346" t="n">
-        <v>382.64</v>
-      </c>
-      <c r="E346" t="n">
-        <v>0.033662</v>
-      </c>
-      <c r="F346" t="n">
-        <v>0.02812586206896552</v>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" s="2" t="n">
-        <v>45600</v>
-      </c>
-      <c r="B347" t="n">
-        <v>73.73</v>
-      </c>
-      <c r="C347" t="n">
-        <v>46.56565517241379</v>
-      </c>
-      <c r="D347" t="n">
-        <v>388.0566666666667</v>
-      </c>
-      <c r="E347" t="n">
-        <v>0.03197533333333333</v>
-      </c>
-      <c r="F347" t="n">
-        <v>0.02641689655172414</v>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" s="2" t="n">
-        <v>45621</v>
-      </c>
-      <c r="B348" t="n">
-        <v>74.10333333333332</v>
-      </c>
-      <c r="C348" t="n">
-        <v>48.35</v>
-      </c>
-      <c r="D348" t="n">
-        <v>418.11</v>
-      </c>
-      <c r="E348" t="n">
-        <v>0.031519</v>
-      </c>
-      <c r="F348" t="n">
-        <v>0.027035</v>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" s="2" t="n">
-        <v>45642</v>
-      </c>
-      <c r="B349" t="n">
-        <v>76.37</v>
-      </c>
-      <c r="C349" t="n">
-        <v>49.59029032258065</v>
-      </c>
-      <c r="D349" t="n">
-        <v>431.8233333333333</v>
-      </c>
-      <c r="E349" t="n">
-        <v>0.03368133333333333</v>
-      </c>
-      <c r="F349" t="n">
-        <v>0.02813258064516129</v>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" s="2" t="n">
-        <v>45663</v>
-      </c>
-      <c r="B350" t="n">
-        <v>77.55333333333333</v>
-      </c>
-      <c r="C350" t="n">
-        <v>52.53570967741936</v>
-      </c>
-      <c r="D350" t="n">
-        <v>423.39</v>
-      </c>
-      <c r="E350" t="n">
-        <v>0.034249</v>
-      </c>
-      <c r="F350" t="n">
-        <v>0.02843741935483871</v>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" s="2" t="n">
-        <v>45684</v>
-      </c>
-      <c r="B351" t="n">
-        <v>75.06</v>
-      </c>
-      <c r="C351" t="n">
-        <v>48.14157142857143</v>
-      </c>
-      <c r="D351" t="n">
-        <v>442.5333333333333</v>
-      </c>
-      <c r="E351" t="n">
-        <v>0.032655</v>
-      </c>
-      <c r="F351" t="n">
-        <v>0.02817285714285714</v>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" s="2" t="n">
-        <v>45705</v>
-      </c>
-      <c r="B352" t="n">
-        <v>69.64</v>
-      </c>
-      <c r="C352" t="n">
-        <v>43.25945161290323</v>
-      </c>
-      <c r="D352" t="n">
-        <v>453.04</v>
-      </c>
-      <c r="E352" t="n">
-        <v>0.03466033333333333</v>
-      </c>
-      <c r="F352" t="n">
-        <v>0.02891</v>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" s="2" t="n">
-        <v>45726</v>
-      </c>
-      <c r="B353" t="n">
-        <v>74.36999999999999</v>
-      </c>
-      <c r="C353" t="n">
-        <v>40.78483870967742</v>
-      </c>
-      <c r="D353" t="n">
-        <v>441.5366666666666</v>
-      </c>
-      <c r="E353" t="n">
-        <v>0.03409966666666667</v>
-      </c>
-      <c r="F353" t="n">
-        <v>0.03122</v>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" s="2" t="n">
-        <v>45747</v>
-      </c>
-      <c r="B354" t="n">
-        <v>66.685</v>
-      </c>
-      <c r="C354" t="n">
-        <v>35.10033333333333</v>
-      </c>
-      <c r="D354" t="n">
-        <v>442.7066666666666</v>
-      </c>
-      <c r="E354" t="n">
-        <v>0.0325604</v>
-      </c>
-      <c r="F354" t="n">
-        <v>0.02997</v>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" s="2" t="n">
-        <v>45768</v>
-      </c>
-      <c r="B355" t="n">
-        <v>64.61</v>
-      </c>
-      <c r="C355" t="n">
-        <v>33.0177</v>
-      </c>
-      <c r="D355" t="n">
-        <v>438.9233333333333</v>
-      </c>
-      <c r="E355" t="n">
-        <v>0.034343</v>
-      </c>
-      <c r="F355" t="n">
-        <v>0.02939266666666666</v>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" s="2" t="n">
-        <v>45789</v>
-      </c>
-      <c r="B356" t="n">
-        <v>64.38666666666666</v>
-      </c>
-      <c r="C356" t="n">
-        <v>34.1421935483871</v>
-      </c>
-      <c r="D356" t="n">
-        <v>432.2266666666666</v>
-      </c>
-      <c r="E356" t="n">
-        <v>0.03364966666666667</v>
-      </c>
-      <c r="F356" t="n">
-        <v>0.02961387096774194</v>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" s="2" t="n">
-        <v>45810</v>
-      </c>
-      <c r="B357" t="n">
-        <v>73.32333333333334</v>
-      </c>
-      <c r="C357" t="n">
-        <v>33.24122580645162</v>
-      </c>
-      <c r="D357" t="n">
-        <v>450.0766666666667</v>
-      </c>
-      <c r="E357" t="n">
-        <v>0.034136</v>
-      </c>
-      <c r="F357" t="n">
-        <v>0.03007451612903226</v>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" s="2" t="n">
-        <v>45831</v>
-      </c>
-      <c r="B358" t="n">
-        <v>69.59333333333333</v>
-      </c>
-      <c r="C358" t="n">
-        <v>33.89648387096774</v>
-      </c>
-      <c r="D358" t="n">
-        <v>473.3466666666666</v>
-      </c>
-      <c r="E358" t="n">
-        <v>0.034963</v>
-      </c>
-      <c r="F358" t="n">
-        <v>0.03036322580645161</v>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" s="2" t="n">
-        <v>45852</v>
-      </c>
-      <c r="B359" t="n">
-        <v>69.06333333333333</v>
-      </c>
-      <c r="C359" t="n">
-        <v>34.90068965517241</v>
-      </c>
-      <c r="D359" t="n">
-        <v>486.4233333333333</v>
-      </c>
-      <c r="E359" t="n">
-        <v>0.03400533333333333</v>
-      </c>
-      <c r="F359" t="n">
-        <v>0.03055206896551724</v>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" s="2" t="n">
-        <v>45873</v>
-      </c>
-      <c r="B360" t="n">
-        <v>68.44333333333333</v>
-      </c>
-      <c r="C360" t="n">
-        <v>32.25251724137931</v>
-      </c>
-      <c r="D360" t="n">
-        <v>479.9166666666667</v>
-      </c>
-      <c r="E360" t="n">
-        <v>0.03474333333333333</v>
-      </c>
-      <c r="F360" t="n">
-        <v>0.03077655172413793</v>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" s="2" t="n">
-        <v>45894</v>
-      </c>
-      <c r="B361" t="n">
-        <v>67.28999999999999</v>
-      </c>
-      <c r="C361" t="n">
-        <v>31.5165</v>
-      </c>
-      <c r="D361" t="n">
-        <v>495.3366666666666</v>
-      </c>
-      <c r="E361" t="n">
-        <v>0.034548</v>
-      </c>
-      <c r="F361" t="n">
-        <v>0.03085</v>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" s="2" t="n">
-        <v>45915</v>
-      </c>
-      <c r="B362" t="n">
-        <v>65.15666666666667</v>
-      </c>
-      <c r="C362" t="n">
-        <v>31.36438709677419</v>
-      </c>
-      <c r="D362" t="n">
-        <v>507.8033333333333</v>
-      </c>
-      <c r="E362" t="n">
-        <v>0.034519</v>
-      </c>
-      <c r="F362" t="n">
-        <v>0.03077161290322581</v>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" s="2" t="n">
-        <v>45936</v>
-      </c>
-      <c r="B363" t="n">
-        <v>65.72666666666667</v>
-      </c>
-      <c r="C363" t="n">
-        <v>31.16861290322581</v>
-      </c>
-      <c r="D363" t="n">
-        <v>547.9166666666666</v>
-      </c>
-      <c r="E363" t="n">
-        <v>0.03382866666666667</v>
-      </c>
-      <c r="F363" t="n">
-        <v>0.03035838709677419</v>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" s="2" t="n">
-        <v>45957</v>
-      </c>
-      <c r="B364" t="n">
-        <v>64.26333333333334</v>
-      </c>
-      <c r="C364" t="n">
-        <v>29.80485714285714</v>
-      </c>
-      <c r="D364" t="n">
-        <v>548.14</v>
-      </c>
-      <c r="E364" t="n">
-        <v>0.03498233333333333</v>
-      </c>
-      <c r="F364" t="n">
-        <v>0.03056857142857143</v>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" s="2" t="n">
-        <v>45978</v>
-      </c>
-      <c r="B365" t="n">
-        <v>62.91</v>
-      </c>
-      <c r="C365" t="n">
-        <v>28.63809090909091</v>
-      </c>
-      <c r="D365" t="inlineStr"/>
-      <c r="E365" t="n">
-        <v>0.03630533333333333</v>
-      </c>
-      <c r="F365" t="n">
-        <v>0.03114090909090909</v>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" s="2" t="n">
-        <v>45999</v>
-      </c>
-      <c r="B366" t="n">
-        <v>61.50666666666667</v>
-      </c>
-      <c r="C366" t="n">
-        <v>28.22063636363637</v>
-      </c>
-      <c r="D366" t="inlineStr"/>
-      <c r="E366" t="n">
-        <v>0.0363226</v>
-      </c>
-      <c r="F366" t="n">
-        <v>0.03193636363636364</v>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" s="2" t="n">
-        <v>46020</v>
-      </c>
-      <c r="B367" t="n">
-        <v>64.00333333333333</v>
-      </c>
-      <c r="C367" t="n">
-        <v>34.8354</v>
-      </c>
-      <c r="D367" t="inlineStr"/>
-      <c r="E367" t="n">
-        <v>0.03596633333333333</v>
-      </c>
-      <c r="F367" t="n">
-        <v>0.031666</v>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" s="2" t="n">
-        <v>46041</v>
-      </c>
-      <c r="B368" t="n">
-        <v>68.71000000000001</v>
-      </c>
-      <c r="C368" t="n">
-        <v>36.93021428571429</v>
-      </c>
-      <c r="D368" t="inlineStr"/>
-      <c r="E368" t="n">
-        <v>0.03561666666666667</v>
-      </c>
-      <c r="F368" t="n">
-        <v>0.03079285714285714</v>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" s="2" t="n">
-        <v>46062</v>
-      </c>
-      <c r="B369" t="n">
-        <v>75.98666666666666</v>
-      </c>
-      <c r="C369" t="n">
-        <v>33.77028</v>
-      </c>
-      <c r="D369" t="inlineStr"/>
-      <c r="E369" t="n">
-        <v>0.03484</v>
-      </c>
-      <c r="F369" t="n">
-        <v>0.02986083333333333</v>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" s="2" t="n">
-        <v>46083</v>
-      </c>
-      <c r="B370" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="C370" t="n">
-        <v>52.78872</v>
-      </c>
-      <c r="D370" t="inlineStr"/>
-      <c r="E370" t="n">
-        <v>0.036821</v>
-      </c>
-      <c r="F370" t="n">
-        <v>0.03375458333333333</v>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" s="2" t="n">
-        <v>46104</v>
-      </c>
-      <c r="B371" t="inlineStr"/>
-      <c r="C371" t="n">
-        <v>54.6</v>
-      </c>
-      <c r="D371" t="inlineStr"/>
-      <c r="E371" t="inlineStr"/>
-      <c r="F371" t="n">
         <v>0.03394</v>
       </c>
     </row>
